--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 4112-2025</t>
+          <t>A 5927-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45684</v>
+        <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1300,22 +1300,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>11.4</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1324,21 +1324,237 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Hussvala
+Ladusvala
+Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 5927-2023 artfynd.xlsx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 5927-2023 karta.png", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 5927-2023 georefererad karta.tif", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 5927-2023 FSC-klagomål.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 5927-2023 FSC-klagomål mail.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 5927-2023 tillsynsbegäran.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 5927-2023 tillsynsbegäran mail.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 39622-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Dvärghäxört
+Skogsödla
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 39622-2023 artfynd.xlsx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 39622-2023 karta.png", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 39622-2023 georefererad karta.tif", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 39622-2023 FSC-klagomål.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 39622-2023 FSC-klagomål mail.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 39622-2023 tillsynsbegäran.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 39622-2023 tillsynsbegäran mail.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 4112-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
         <v>6</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U10" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Gröngöling
@@ -1346,248 +1562,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 4112-2025 artfynd.xlsx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 4112-2025 karta.png", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 4112-2025 georefererad karta.tif", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 4112-2025 FSC-klagomål.docx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 4112-2025 FSC-klagomål mail.docx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 4112-2025 tillsynsbegäran.docx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 4112-2025 tillsynsbegäran mail.docx", "A 4112-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 39622-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Dvärghäxört
-Skogsödla
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 39622-2023 artfynd.xlsx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 39622-2023 karta.png", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 39622-2023 georefererad karta.tif", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 39622-2023 FSC-klagomål.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 39622-2023 FSC-klagomål mail.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 39622-2023 tillsynsbegäran.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 39622-2023 tillsynsbegäran mail.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 5927-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44963</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Hussvala
-Ladusvala
-Svart skogssnigel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 5927-2023 artfynd.xlsx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 5927-2023 karta.png", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 5927-2023 georefererad karta.tif", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 5927-2023 FSC-klagomål.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 5927-2023 FSC-klagomål mail.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 5927-2023 tillsynsbegäran.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 5927-2023 tillsynsbegäran mail.docx", "A 5927-2023")</f>
         <v/>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25960-2023</t>
+          <t>A 31926-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45090</v>
+        <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1768,151 +1768,151 @@
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Havstulpanlav
+Klippfrullania
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 31926-2024 artfynd.xlsx", "A 31926-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 31926-2024 karta.png", "A 31926-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 31926-2024 georefererad karta.tif", "A 31926-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 31926-2024 FSC-klagomål.docx", "A 31926-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 31926-2024 FSC-klagomål mail.docx", "A 31926-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 31926-2024 tillsynsbegäran.docx", "A 31926-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 31926-2024 tillsynsbegäran mail.docx", "A 31926-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 25960-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45090</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Bokkantlav
 Guldlockmossa
 Platt fjädermossa</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 25960-2023 artfynd.xlsx", "A 25960-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 25960-2023 karta.png", "A 25960-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 25960-2023 georefererad karta.tif", "A 25960-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 25960-2023 FSC-klagomål.docx", "A 25960-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 25960-2023 FSC-klagomål mail.docx", "A 25960-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 25960-2023 tillsynsbegäran.docx", "A 25960-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 25960-2023 tillsynsbegäran mail.docx", "A 25960-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 31926-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45510</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>9</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Havstulpanlav
-Klippfrullania
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 31926-2024 artfynd.xlsx", "A 31926-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 31926-2024 karta.png", "A 31926-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 31926-2024 georefererad karta.tif", "A 31926-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 31926-2024 FSC-klagomål.docx", "A 31926-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 31926-2024 FSC-klagomål mail.docx", "A 31926-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 31926-2024 tillsynsbegäran.docx", "A 31926-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 31926-2024 tillsynsbegäran mail.docx", "A 31926-2024")</f>
         <v/>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45945</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>46183</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45642</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6137-2024</t>
+          <t>A 1604-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45337</v>
+        <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2919,8 +2919,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>11.7</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2932,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2960,42 +2965,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Skorpplätt</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 6137-2024 artfynd.xlsx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 1604-2025 artfynd.xlsx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 6137-2024 karta.png", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 1604-2025 karta.png", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 6137-2024 georefererad karta.tif", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 1604-2025 georefererad karta.tif", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 6137-2024 FSC-klagomål.docx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 1604-2025 FSC-klagomål.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 6137-2024 FSC-klagomål mail.docx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 1604-2025 FSC-klagomål mail.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 6137-2024 tillsynsbegäran.docx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 1604-2025 tillsynsbegäran.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 6137-2024 tillsynsbegäran mail.docx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 1604-2025 tillsynsbegäran mail.docx", "A 1604-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 10496-2026</t>
+          <t>A 6137-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3009,10 +3014,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46076</v>
+        <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3025,23 +3030,23 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>11.7</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
@@ -3049,10 +3054,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3061,46 +3066,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Skorpplätt</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 10496-2026 artfynd.xlsx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 6137-2024 artfynd.xlsx", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 10496-2026 karta.png", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 6137-2024 karta.png", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 10496-2026 georefererad karta.tif", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 6137-2024 georefererad karta.tif", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 10496-2026 FSC-klagomål.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 6137-2024 FSC-klagomål.docx", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 10496-2026 FSC-klagomål mail.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 6137-2024 FSC-klagomål mail.docx", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 10496-2026 tillsynsbegäran.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 6137-2024 tillsynsbegäran.docx", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 10496-2026 tillsynsbegäran mail.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 6137-2024 tillsynsbegäran mail.docx", "A 6137-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 57429-2025</t>
+          <t>A 10496-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3114,10 +3119,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45980</v>
+        <v>46076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3130,10 +3135,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3142,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3154,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3170,42 +3175,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 57429-2025 artfynd.xlsx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 10496-2026 artfynd.xlsx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 57429-2025 karta.png", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 10496-2026 karta.png", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 57429-2025 georefererad karta.tif", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 10496-2026 georefererad karta.tif", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 57429-2025 FSC-klagomål.docx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 10496-2026 FSC-klagomål.docx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 57429-2025 FSC-klagomål mail.docx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 10496-2026 FSC-klagomål mail.docx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 57429-2025 tillsynsbegäran.docx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 10496-2026 tillsynsbegäran.docx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 57429-2025 tillsynsbegäran mail.docx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 10496-2026 tillsynsbegäran mail.docx", "A 10496-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22410-2024</t>
+          <t>A 57429-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3219,10 +3224,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45446</v>
+        <v>45980</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3235,20 +3240,20 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
@@ -3259,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3275,42 +3280,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 22410-2024 artfynd.xlsx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 57429-2025 artfynd.xlsx", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 22410-2024 karta.png", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 57429-2025 karta.png", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 22410-2024 georefererad karta.tif", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 57429-2025 georefererad karta.tif", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 22410-2024 FSC-klagomål.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 57429-2025 FSC-klagomål.docx", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 22410-2024 FSC-klagomål mail.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 57429-2025 FSC-klagomål mail.docx", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 22410-2024 tillsynsbegäran.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 57429-2025 tillsynsbegäran.docx", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 22410-2024 tillsynsbegäran mail.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 57429-2025 tillsynsbegäran mail.docx", "A 57429-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1604-2025</t>
+          <t>A 15068-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3324,10 +3329,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45670</v>
+        <v>45015</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3339,25 +3344,20 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>9.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3385,42 +3385,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 1604-2025 artfynd.xlsx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 15068-2023 artfynd.xlsx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 1604-2025 karta.png", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 15068-2023 karta.png", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 1604-2025 georefererad karta.tif", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 15068-2023 georefererad karta.tif", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 1604-2025 FSC-klagomål.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 15068-2023 FSC-klagomål.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 1604-2025 FSC-klagomål mail.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 15068-2023 FSC-klagomål mail.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 1604-2025 tillsynsbegäran.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 15068-2023 tillsynsbegäran.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 1604-2025 tillsynsbegäran mail.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 15068-2023 tillsynsbegäran mail.docx", "A 15068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15068-2023</t>
+          <t>A 22410-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45015</v>
+        <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3450,13 +3450,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>9.9</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3486,39 +3486,39 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 15068-2023 artfynd.xlsx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 22410-2024 artfynd.xlsx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 15068-2023 karta.png", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 22410-2024 karta.png", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 15068-2023 georefererad karta.tif", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 22410-2024 georefererad karta.tif", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 15068-2023 FSC-klagomål.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 22410-2024 FSC-klagomål.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 15068-2023 FSC-klagomål mail.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 22410-2024 FSC-klagomål mail.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 15068-2023 tillsynsbegäran.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 22410-2024 tillsynsbegäran.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 15068-2023 tillsynsbegäran mail.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 22410-2024 tillsynsbegäran mail.docx", "A 22410-2024")</f>
         <v/>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
         <v>45784</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S 2731-2022</t>
+          <t>S 2910-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3640,14 +3640,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44704</v>
+        <v>45503</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3659,13 +3659,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>24.7</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3701,46 +3696,50 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2731-2022 artfynd.xlsx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2910-2024 artfynd.xlsx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2731-2022 karta.png", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2910-2024 karta.png", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2731-2022 georefererad karta.tif", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2910-2024 georefererad karta.tif", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2731-2022 FSC-klagomål.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2910-2024 FSC-klagomål.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2731-2022 FSC-klagomål mail.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2910-2024 FSC-klagomål mail.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2731-2022 tillsynsbegäran.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2910-2024 tillsynsbegäran.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2731-2022 tillsynsbegäran mail.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2910-2024 tillsynsbegäran mail.docx", "S 2910-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/S 2910-2024 prioriterade fågelarter.docx", "S 2910-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S 2910-2024</t>
+          <t>S 4056-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3750,14 +3749,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45503</v>
+        <v>45243</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3770,7 +3769,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.4</v>
+        <v>7.1</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3810,46 +3809,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2910-2024 artfynd.xlsx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 4056-2023 artfynd.xlsx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2910-2024 karta.png", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 4056-2023 karta.png", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2910-2024 georefererad karta.tif", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 4056-2023 georefererad karta.tif", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2910-2024 FSC-klagomål.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 4056-2023 FSC-klagomål.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2910-2024 FSC-klagomål mail.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 4056-2023 FSC-klagomål mail.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2910-2024 tillsynsbegäran.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 4056-2023 tillsynsbegäran.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2910-2024 tillsynsbegäran mail.docx", "S 2910-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/S 2910-2024 prioriterade fågelarter.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 4056-2023 tillsynsbegäran mail.docx", "S 4056-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S 4056-2023</t>
+          <t>S 2731-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3863,10 +3858,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45243</v>
+        <v>44704</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3878,8 +3873,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>7.1</v>
+        <v>24.7</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3915,39 +3915,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 4056-2023 artfynd.xlsx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2731-2022 artfynd.xlsx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 4056-2023 karta.png", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2731-2022 karta.png", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 4056-2023 georefererad karta.tif", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2731-2022 georefererad karta.tif", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 4056-2023 FSC-klagomål.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2731-2022 FSC-klagomål.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 4056-2023 FSC-klagomål mail.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2731-2022 FSC-klagomål mail.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 4056-2023 tillsynsbegäran.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2731-2022 tillsynsbegäran.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 4056-2023 tillsynsbegäran mail.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2731-2022 tillsynsbegäran mail.docx", "S 2731-2022")</f>
         <v/>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56006-2021</t>
+          <t>A 45968-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44477</v>
+        <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4692,7 +4692,7 @@
         <v>44752</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 45968-2022</t>
+          <t>A 56006-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44846</v>
+        <v>44477</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44841</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26178-2023</t>
+          <t>A 6020-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45091</v>
+        <v>44599</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26179-2023</t>
+          <t>A 73830-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45091</v>
+        <v>44552</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5561,7 +5561,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9773-2024</t>
+          <t>A 19390-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45362</v>
+        <v>45048</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9748-2024</t>
+          <t>A 44814-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45362</v>
+        <v>44841</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 24154-2023</t>
+          <t>A 9748-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45079</v>
+        <v>45362</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5780,7 +5780,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62180-2022</t>
+          <t>A 52876-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44915</v>
+        <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5809,13 +5809,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5858,7 +5853,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 21023-2024</t>
+          <t>A 10379-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5872,10 +5867,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45439</v>
+        <v>45365</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5888,7 +5883,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5931,7 +5926,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 58130-2022</t>
+          <t>A 23740-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5945,10 +5940,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44900</v>
+        <v>45077</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5961,7 +5956,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>23.2</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6004,7 +5999,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19643-2024</t>
+          <t>A 72261-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6018,10 +6013,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45432</v>
+        <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6033,13 +6028,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6082,7 +6072,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22406-2024</t>
+          <t>A 17737-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6096,10 +6086,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45446</v>
+        <v>45037</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6112,7 +6102,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6155,7 +6145,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26058-2024</t>
+          <t>A 54669-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6169,10 +6159,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45468</v>
+        <v>45235</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6185,7 +6175,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6228,7 +6218,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47871-2022</t>
+          <t>A 9359-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6242,10 +6232,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44855</v>
+        <v>45715</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6258,7 +6248,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6301,7 +6291,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44880-2022</t>
+          <t>A 23469-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6315,10 +6305,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44841</v>
+        <v>45792</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6331,7 +6321,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6374,7 +6364,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57208-2022</t>
+          <t>A 25589-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6388,10 +6378,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44895</v>
+        <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6404,7 +6394,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6447,7 +6437,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 64091-2023</t>
+          <t>A 47890-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6461,10 +6451,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45279</v>
+        <v>44855</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6477,7 +6467,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6520,7 +6510,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 40814-2023</t>
+          <t>A 26032-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6534,10 +6524,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45171</v>
+        <v>45804</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6550,7 +6540,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6593,7 +6583,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40017-2023</t>
+          <t>A 26020-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6607,10 +6597,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45168</v>
+        <v>45804</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6623,7 +6613,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6666,7 +6656,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 33796-2023</t>
+          <t>A 23898-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6680,10 +6670,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45133</v>
+        <v>45078</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6696,7 +6686,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6739,7 +6729,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2088-2023</t>
+          <t>A 52243-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6753,10 +6743,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44939</v>
+        <v>45953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6769,7 +6759,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6812,7 +6802,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2092-2023</t>
+          <t>A 53163-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6826,10 +6816,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44939</v>
+        <v>45958</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6842,7 +6832,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6885,7 +6875,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52528-2021</t>
+          <t>A 31399-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6899,10 +6889,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44466</v>
+        <v>45833</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6915,7 +6905,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6958,7 +6948,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36838-2024</t>
+          <t>A 52246-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6972,10 +6962,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45538</v>
+        <v>45953</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6988,7 +6978,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7031,7 +7021,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34279-2023</t>
+          <t>A 7915-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7045,10 +7035,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45138</v>
+        <v>45707</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7061,7 +7051,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7104,7 +7094,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 57795-2022</t>
+          <t>A 31704-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7118,10 +7108,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44897</v>
+        <v>45117</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7134,7 +7124,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.3</v>
+        <v>6.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7177,7 +7167,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 73830-2021</t>
+          <t>A 27523-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7191,10 +7181,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44552</v>
+        <v>45813</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7207,7 +7197,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7250,7 +7240,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6020-2022</t>
+          <t>A 14912-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7260,14 +7250,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44599</v>
+        <v>45398</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7280,7 +7270,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7323,7 +7313,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1783-2025</t>
+          <t>A 1225-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7337,10 +7327,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45671</v>
+        <v>46031</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7353,7 +7343,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7396,7 +7386,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21146-2022</t>
+          <t>A 15478-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7410,10 +7400,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44704</v>
+        <v>45747</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7426,7 +7416,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.4</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7469,7 +7459,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28693-2025</t>
+          <t>A 21146-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7483,10 +7473,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45819</v>
+        <v>44704</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7499,7 +7489,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7542,7 +7532,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8024-2026</t>
+          <t>A 2537-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7556,10 +7546,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46063</v>
+        <v>46037</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7571,13 +7561,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7620,7 +7605,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13068-2023</t>
+          <t>A 28693-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7634,10 +7619,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45002</v>
+        <v>45819</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7650,7 +7635,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7693,7 +7678,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29642-2025</t>
+          <t>A 2474-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7707,10 +7692,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45825</v>
+        <v>46037</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7723,7 +7708,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>8.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7766,7 +7751,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 9292-2026</t>
+          <t>A 41912-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7780,10 +7765,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46070</v>
+        <v>45903</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7796,7 +7781,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7839,7 +7824,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9125-2026</t>
+          <t>A 29642-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7853,10 +7838,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46069</v>
+        <v>45825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7869,7 +7854,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7912,7 +7897,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9105-2026</t>
+          <t>A 41926-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7926,10 +7911,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46069</v>
+        <v>45903</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7942,7 +7927,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7985,7 +7970,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 9127-2026</t>
+          <t>A 54667-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7999,10 +7984,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46069</v>
+        <v>45235</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8015,7 +8000,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8058,7 +8043,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 17737-2023</t>
+          <t>A 3934-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8072,10 +8057,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45037</v>
+        <v>46043</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8088,7 +8073,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8131,7 +8116,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31399-2025</t>
+          <t>A 42708-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8145,10 +8130,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45833</v>
+        <v>45908</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8161,7 +8146,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8204,7 +8189,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 38897-2025</t>
+          <t>A 42728-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8218,10 +8203,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45887</v>
+        <v>45908</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8234,7 +8219,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8277,7 +8262,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7915-2025</t>
+          <t>A 4989-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8291,10 +8276,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45707</v>
+        <v>46049</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8307,7 +8292,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8350,7 +8335,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17270-2025</t>
+          <t>A 5002-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8364,10 +8349,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45756</v>
+        <v>46049</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8380,7 +8365,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8423,7 +8408,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12038-2025</t>
+          <t>A 13797-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8437,10 +8422,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45728</v>
+        <v>45737</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8453,7 +8438,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8496,7 +8481,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 32704-2025</t>
+          <t>A 12038-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8510,10 +8495,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45839</v>
+        <v>45728</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8526,7 +8511,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8569,7 +8554,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 20492-2024</t>
+          <t>A 43990-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8583,10 +8568,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45435</v>
+        <v>45915</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8642,7 +8627,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22975-2023</t>
+          <t>A 25963-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8656,10 +8641,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45072</v>
+        <v>45090</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8672,7 +8657,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8715,7 +8700,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 41912-2025</t>
+          <t>A 40814-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8729,10 +8714,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45903</v>
+        <v>45171</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8745,7 +8730,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8788,7 +8773,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18285-2025</t>
+          <t>A 32855-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8802,10 +8787,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45762</v>
+        <v>45124</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8818,7 +8803,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8861,7 +8846,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61602-2024</t>
+          <t>A 17270-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8875,10 +8860,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45646</v>
+        <v>45756</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8891,7 +8876,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8934,7 +8919,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 41926-2025</t>
+          <t>A 1492-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8948,10 +8933,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45903</v>
+        <v>45305</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8964,7 +8949,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9007,7 +8992,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 42728-2025</t>
+          <t>A 1493-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9021,10 +9006,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45908</v>
+        <v>45305</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9037,7 +9022,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9080,7 +9065,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38928-2024</t>
+          <t>A 21910-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9094,10 +9079,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45548</v>
+        <v>45443</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9110,7 +9095,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9153,7 +9138,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 42708-2025</t>
+          <t>A 32704-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9167,10 +9152,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45908</v>
+        <v>45839</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9183,7 +9168,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9226,7 +9211,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 63783-2023</t>
+          <t>A 44897-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9240,10 +9225,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45278</v>
+        <v>45918</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9256,7 +9241,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9299,7 +9284,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 9359-2025</t>
+          <t>A 44890-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9313,10 +9298,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45715</v>
+        <v>45918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9329,7 +9314,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9372,7 +9357,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 13797-2025</t>
+          <t>A 57703-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9386,10 +9371,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45737</v>
+        <v>44897</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9402,7 +9387,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9445,7 +9430,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 10466-2026</t>
+          <t>A 26058-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9459,10 +9444,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46077</v>
+        <v>45468</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9475,7 +9460,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9518,7 +9503,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 10473-2026</t>
+          <t>A 63783-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9532,10 +9517,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46077</v>
+        <v>45278</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9548,7 +9533,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9591,7 +9576,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 10480-2026</t>
+          <t>A 7242-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9605,10 +9590,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46077</v>
+        <v>46058</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9621,7 +9606,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9664,7 +9649,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 43990-2025</t>
+          <t>A 1397-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9678,10 +9663,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45915</v>
+        <v>44936</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9737,7 +9722,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 44890-2025</t>
+          <t>A 8024-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9751,10 +9736,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45918</v>
+        <v>46063</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9766,8 +9751,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9810,7 +9800,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 44897-2025</t>
+          <t>A 9105-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9824,10 +9814,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45918</v>
+        <v>46069</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9840,7 +9830,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9883,7 +9873,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 52876-2024</t>
+          <t>A 18285-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9897,10 +9887,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45610</v>
+        <v>45762</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9956,7 +9946,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 42177-2023</t>
+          <t>A 9127-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9970,10 +9960,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45178</v>
+        <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9986,7 +9976,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10029,7 +10019,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 30638-2023</t>
+          <t>A 36543-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10043,10 +10033,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45112</v>
+        <v>44804</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10059,7 +10049,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10102,7 +10092,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 48672-2025</t>
+          <t>A 61602-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10116,10 +10106,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45936</v>
+        <v>45646</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10132,7 +10122,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10175,7 +10165,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28221-2023</t>
+          <t>A 13068-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10189,10 +10179,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45099</v>
+        <v>45002</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10205,7 +10195,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10248,7 +10238,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 44925-2025</t>
+          <t>A 9125-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10262,10 +10252,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45918</v>
+        <v>46069</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10278,7 +10268,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10321,7 +10311,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 171-2025</t>
+          <t>A 9292-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10335,10 +10325,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45659</v>
+        <v>46070</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10351,7 +10341,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10394,7 +10384,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 36280-2025</t>
+          <t>A 5954-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10404,14 +10394,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45867</v>
+        <v>45695</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10424,7 +10414,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10467,7 +10457,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 13283-2026</t>
+          <t>A 48672-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10481,10 +10471,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46093</v>
+        <v>45936</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10497,7 +10487,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>8.1</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10540,7 +10530,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 14734-2026</t>
+          <t>A 19643-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10554,10 +10544,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46101</v>
+        <v>45432</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10569,8 +10559,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10613,7 +10608,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 45192-2022</t>
+          <t>A 10473-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10627,10 +10622,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44844</v>
+        <v>46077</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10643,7 +10638,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10686,7 +10681,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 36543-2022</t>
+          <t>A 10466-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10700,10 +10695,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44804</v>
+        <v>46077</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10716,7 +10711,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10759,7 +10754,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 53142-2025</t>
+          <t>A 10480-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10773,10 +10768,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45958</v>
+        <v>46077</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10789,7 +10784,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10832,7 +10827,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 5941-2025</t>
+          <t>A 23692-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10846,10 +10841,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45695</v>
+        <v>45077</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10862,7 +10857,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10905,7 +10900,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15236-2026</t>
+          <t>A 44925-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10919,10 +10914,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46105</v>
+        <v>45918</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10935,7 +10930,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10978,7 +10973,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 15240-2026</t>
+          <t>A 37501-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10992,10 +10987,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46105</v>
+        <v>45541</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11008,7 +11003,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11051,7 +11046,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 40190-2022</t>
+          <t>A 44880-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11065,10 +11060,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44820</v>
+        <v>44841</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11081,7 +11076,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11124,7 +11119,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 15108-2026</t>
+          <t>A 171-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11138,10 +11133,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46105</v>
+        <v>45659</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11154,7 +11149,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11197,7 +11192,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 44814-2022</t>
+          <t>A 36280-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11207,14 +11202,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44841</v>
+        <v>45867</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11227,7 +11222,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11270,7 +11265,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 16363-2026</t>
+          <t>A 38897-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11284,10 +11279,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46111</v>
+        <v>45887</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11300,7 +11295,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11343,7 +11338,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 16283-2026</t>
+          <t>A 9691-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11357,10 +11352,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46111</v>
+        <v>44984</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11373,7 +11368,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11416,7 +11411,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1397-2023</t>
+          <t>A 17641-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11430,10 +11425,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44936</v>
+        <v>45035</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11446,7 +11441,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>7.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11489,7 +11484,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 17608-2026</t>
+          <t>A 39650-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11503,10 +11498,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46121</v>
+        <v>45167</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11519,7 +11514,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11562,7 +11557,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 23693-2023</t>
+          <t>A 13283-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11576,10 +11571,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45077</v>
+        <v>46093</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11592,7 +11587,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.5</v>
+        <v>8.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11635,7 +11630,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 56455-2025</t>
+          <t>A 24154-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11649,10 +11644,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45975</v>
+        <v>45079</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11665,7 +11660,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11708,7 +11703,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 57343-2025</t>
+          <t>A 65211-2021</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11722,10 +11717,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45980</v>
+        <v>44515</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11738,7 +11733,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11781,7 +11776,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 23990-2023</t>
+          <t>A 14734-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11795,10 +11790,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45078</v>
+        <v>46101</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11811,7 +11806,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11854,7 +11849,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 34591-2023</t>
+          <t>A 53142-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11868,10 +11863,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45140</v>
+        <v>45958</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11884,7 +11879,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11927,7 +11922,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 57790-2025</t>
+          <t>A 24765-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11941,10 +11936,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45981</v>
+        <v>45084</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11957,7 +11952,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12000,7 +11995,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 52372-2021</t>
+          <t>A 15240-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12014,10 +12009,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44465</v>
+        <v>46105</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12030,7 +12025,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12073,7 +12068,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 11126-2025</t>
+          <t>A 15236-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12087,10 +12082,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45723</v>
+        <v>46105</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12103,7 +12098,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12146,7 +12141,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 58347-2025</t>
+          <t>A 15108-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12160,10 +12155,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45985</v>
+        <v>46105</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12176,7 +12171,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12219,7 +12214,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 54667-2023</t>
+          <t>A 16363-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12233,10 +12228,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45235</v>
+        <v>46111</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12249,7 +12244,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12292,7 +12287,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 60789-2025</t>
+          <t>A 16283-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12306,10 +12301,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45999</v>
+        <v>46111</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12322,7 +12317,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12365,7 +12360,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 57703-2022</t>
+          <t>A 17608-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12379,10 +12374,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44897</v>
+        <v>46121</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12395,7 +12390,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12438,7 +12433,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 981-2023</t>
+          <t>A 56455-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12452,10 +12447,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44935</v>
+        <v>45975</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12468,7 +12463,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12511,7 +12506,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 2090-2023</t>
+          <t>A 35490-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12525,10 +12520,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44939</v>
+        <v>45855</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12541,7 +12536,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12584,7 +12579,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 25963-2023</t>
+          <t>A 13611-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12598,10 +12593,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45090</v>
+        <v>45736</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12614,7 +12609,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12657,7 +12652,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 8204-2023</t>
+          <t>A 57343-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12671,10 +12666,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44971</v>
+        <v>45980</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12687,7 +12682,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12730,7 +12725,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 52243-2025</t>
+          <t>A 57790-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12744,10 +12739,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45953</v>
+        <v>45981</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12760,7 +12755,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12803,7 +12798,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 53163-2025</t>
+          <t>A 981-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12817,10 +12812,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45958</v>
+        <v>44935</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12833,7 +12828,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12876,7 +12871,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 52246-2025</t>
+          <t>A 58347-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12890,10 +12885,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45953</v>
+        <v>45985</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12906,7 +12901,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12949,7 +12944,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 35490-2025</t>
+          <t>A 44864-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12963,10 +12958,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45855</v>
+        <v>45918</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12979,7 +12974,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13022,7 +13017,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 44864-2025</t>
+          <t>A 42177-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13036,10 +13031,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45918</v>
+        <v>45178</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13052,7 +13047,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13095,7 +13090,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 24765-2023</t>
+          <t>A 28221-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13109,10 +13104,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45084</v>
+        <v>45099</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13125,7 +13120,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13168,7 +13163,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 43992-2025</t>
+          <t>A 11605-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13182,10 +13177,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45915</v>
+        <v>44994</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13198,7 +13193,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13241,7 +13236,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 13611-2025</t>
+          <t>A 23693-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13255,10 +13250,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45736</v>
+        <v>45077</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13271,7 +13266,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13314,7 +13309,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 1225-2026</t>
+          <t>A 43992-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13328,10 +13323,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46031</v>
+        <v>45915</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13344,7 +13339,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13387,7 +13382,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 3205-2025</t>
+          <t>A 45192-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13401,10 +13396,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45679</v>
+        <v>44844</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13416,13 +13411,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>6.7</v>
+        <v>0.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13465,7 +13455,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 2474-2026</t>
+          <t>A 60789-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13479,10 +13469,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46037</v>
+        <v>45999</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13495,7 +13485,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>8.6</v>
+        <v>2.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13538,7 +13528,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 2537-2026</t>
+          <t>A 3205-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13552,10 +13542,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46037</v>
+        <v>45679</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13567,8 +13557,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>2.9</v>
+        <v>6.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13611,7 +13606,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 3934-2026</t>
+          <t>A 9573-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13625,10 +13620,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46043</v>
+        <v>45715</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13641,7 +13636,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13684,7 +13679,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 9691-2023</t>
+          <t>A 20671-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13698,10 +13693,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44984</v>
+        <v>46141</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13714,7 +13709,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13757,7 +13752,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 5002-2026</t>
+          <t>A 35168-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13771,10 +13766,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46049</v>
+        <v>45852</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13787,7 +13782,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13830,7 +13825,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 4989-2026</t>
+          <t>A 22975-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13844,10 +13839,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46049</v>
+        <v>45072</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13860,7 +13855,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13903,7 +13898,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 39650-2023</t>
+          <t>A 14430-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13917,10 +13912,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45167</v>
+        <v>45012</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13933,7 +13928,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13976,7 +13971,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 14912-2024</t>
+          <t>A 64091-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13986,14 +13981,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45398</v>
+        <v>45279</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14049,7 +14044,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 7242-2026</t>
+          <t>A 25962-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14063,10 +14058,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46058</v>
+        <v>45090</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14079,7 +14074,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14122,7 +14117,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 1935-2024</t>
+          <t>A 30136-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14136,10 +14131,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45308</v>
+        <v>44757</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14151,8 +14146,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14195,7 +14195,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 72261-2021</t>
+          <t>A 38214-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44545</v>
+        <v>45161</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14268,7 +14268,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 14254-2023</t>
+          <t>A 22550-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14282,10 +14282,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45009</v>
+        <v>46155</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14341,7 +14341,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 37620-2023</t>
+          <t>A 23739-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45159</v>
+        <v>45077</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14414,7 +14414,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 35168-2025</t>
+          <t>A 22552-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14428,10 +14428,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45852</v>
+        <v>46155</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14487,7 +14487,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 20671-2026</t>
+          <t>A 34631-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14501,10 +14501,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46141</v>
+        <v>45848</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14560,7 +14560,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 31704-2023</t>
+          <t>A 34591-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14574,10 +14574,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45117</v>
+        <v>45140</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14633,7 +14633,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 7707-2024</t>
+          <t>A 53676-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14647,10 +14647,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45349</v>
+        <v>45960</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14706,7 +14706,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 22550-2026</t>
+          <t>A 44846-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14720,10 +14720,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46155</v>
+        <v>45918</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14779,7 +14779,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 22552-2026</t>
+          <t>A 25674-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14793,10 +14793,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46155</v>
+        <v>46178</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14852,7 +14852,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34631-2025</t>
+          <t>A 25699-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14866,10 +14866,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45848</v>
+        <v>46178</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14925,7 +14925,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 2405-2025</t>
+          <t>A 25772-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14939,10 +14939,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45674</v>
+        <v>46178</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14998,7 +14998,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 25967-2023</t>
+          <t>A 25778-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15012,10 +15012,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45090</v>
+        <v>46178</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 9559-2022</t>
+          <t>A 25789-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15085,10 +15085,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44617</v>
+        <v>46178</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15144,7 +15144,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 48966-2023</t>
+          <t>A 25912-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15158,10 +15158,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45209</v>
+        <v>46178</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 50304-2023</t>
+          <t>A 25794-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15227,14 +15227,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45209</v>
+        <v>46178</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>17.9</v>
+        <v>1.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15290,7 +15290,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 53676-2025</t>
+          <t>A 25780-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15304,10 +15304,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45960</v>
+        <v>46178</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15363,7 +15363,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 26837-2022</t>
+          <t>A 25501-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15377,10 +15377,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44740</v>
+        <v>46177</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15436,7 +15436,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 44846-2025</t>
+          <t>A 25765-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15450,10 +15450,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45918</v>
+        <v>46178</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15509,7 +15509,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 29334-2022</t>
+          <t>A 26578-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15523,10 +15523,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44752</v>
+        <v>46183</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15538,13 +15538,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15587,7 +15582,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 27497-2024</t>
+          <t>A 26580-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15601,10 +15596,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45474</v>
+        <v>46183</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15617,7 +15612,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15660,7 +15655,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 25501-2026</t>
+          <t>A 26597-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15674,10 +15669,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15690,7 +15685,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15733,7 +15728,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 54646-2023</t>
+          <t>A 26564-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15747,10 +15742,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45235</v>
+        <v>46183</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15763,7 +15758,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15806,7 +15801,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 25778-2026</t>
+          <t>A 26593-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15820,10 +15815,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46178</v>
+        <v>46183</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15836,7 +15831,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15879,7 +15874,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 25789-2026</t>
+          <t>A 26583-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15893,10 +15888,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46178</v>
+        <v>46183</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15909,7 +15904,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15952,7 +15947,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 25674-2026</t>
+          <t>A 26594-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15966,10 +15961,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46178</v>
+        <v>46183</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15982,7 +15977,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16025,7 +16020,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 25699-2026</t>
+          <t>A 26596-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16039,10 +16034,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46178</v>
+        <v>46183</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16055,7 +16050,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16098,7 +16093,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 25765-2026</t>
+          <t>A 27146-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16112,10 +16107,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46178</v>
+        <v>46188</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16128,7 +16123,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16171,7 +16166,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 25772-2026</t>
+          <t>A 9559-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16185,10 +16180,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46178</v>
+        <v>44617</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16201,7 +16196,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16244,7 +16239,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 25912-2026</t>
+          <t>A 31925-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16258,10 +16253,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46178</v>
+        <v>45510</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16274,7 +16269,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16317,7 +16312,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 25780-2026</t>
+          <t>A 29401-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16331,10 +16326,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16347,7 +16342,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16390,7 +16385,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 25794-2026</t>
+          <t>A 29530-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16404,10 +16399,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16420,7 +16415,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16463,7 +16458,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 21910-2024</t>
+          <t>A 29528-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16477,10 +16472,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45443</v>
+        <v>46203</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16493,7 +16488,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16536,7 +16531,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 26580-2026</t>
+          <t>A 29529-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16550,10 +16545,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46183</v>
+        <v>46203</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16609,7 +16604,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 26597-2026</t>
+          <t>A 30638-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16623,10 +16618,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46183</v>
+        <v>45112</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16639,7 +16634,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16682,7 +16677,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 26564-2026</t>
+          <t>A 2088-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16696,10 +16691,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46183</v>
+        <v>44939</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16712,7 +16707,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16755,7 +16750,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 26596-2026</t>
+          <t>A 34919-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16769,10 +16764,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46183</v>
+        <v>46259</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16785,7 +16780,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16828,7 +16823,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 21152-2022</t>
+          <t>A 34770-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16842,10 +16837,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44704</v>
+        <v>46258</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16858,7 +16853,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16901,7 +16896,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 26583-2026</t>
+          <t>A 33183-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16915,10 +16910,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46183</v>
+        <v>46245</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16931,7 +16926,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16974,7 +16969,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 26594-2026</t>
+          <t>A 33180-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16988,10 +16983,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46183</v>
+        <v>46245</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17004,7 +16999,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17047,7 +17042,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 26578-2026</t>
+          <t>A 28980-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17061,10 +17056,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46183</v>
+        <v>46199</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17077,7 +17072,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17120,7 +17115,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 26593-2026</t>
+          <t>A 33182-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17134,10 +17129,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46183</v>
+        <v>46245</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17150,7 +17145,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17193,7 +17188,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 11121-2025</t>
+          <t>A 52528-2021</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17207,10 +17202,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45723</v>
+        <v>44466</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17223,7 +17218,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17266,7 +17261,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 1492-2024</t>
+          <t>A 35988-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17280,10 +17275,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45305</v>
+        <v>46266</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17296,7 +17291,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17339,7 +17334,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 1493-2024</t>
+          <t>A 36838-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17353,10 +17348,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45305</v>
+        <v>45538</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17369,7 +17364,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17412,7 +17407,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 9573-2025</t>
+          <t>A 1904-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17426,10 +17421,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45715</v>
+        <v>44939</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17442,7 +17437,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17485,7 +17480,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 55049-2023</t>
+          <t>A 8204-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17499,10 +17494,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45237</v>
+        <v>44971</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17515,7 +17510,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17558,7 +17553,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 10379-2024</t>
+          <t>A 11121-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17572,10 +17567,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45365</v>
+        <v>45723</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17588,7 +17583,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17631,7 +17626,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 54661-2023</t>
+          <t>A 3830-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17645,10 +17640,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45235</v>
+        <v>44587</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17661,7 +17656,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17704,7 +17699,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 27146-2026</t>
+          <t>A 37517-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17718,10 +17713,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46188</v>
+        <v>46276</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17734,7 +17729,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17777,7 +17772,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 11605-2023</t>
+          <t>A 21152-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17791,10 +17786,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44994</v>
+        <v>44704</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17807,7 +17802,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17850,7 +17845,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 37501-2024</t>
+          <t>A 58130-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17864,10 +17859,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45541</v>
+        <v>44900</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17880,7 +17875,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.5</v>
+        <v>23.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17923,7 +17918,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 15987-2025</t>
+          <t>A 2359-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17937,10 +17932,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45749</v>
+        <v>44942</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17953,7 +17948,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17996,7 +17991,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 50279-2023</t>
+          <t>A 55049-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18010,10 +18005,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45216</v>
+        <v>45237</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18026,7 +18021,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18069,7 +18064,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 30136-2022</t>
+          <t>A 15987-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18083,10 +18078,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44757</v>
+        <v>45749</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18098,13 +18093,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18147,7 +18137,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 32855-2023</t>
+          <t>A 57208-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18161,10 +18151,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45124</v>
+        <v>44895</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18177,7 +18167,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18237,7 +18227,7 @@
         <v>44951</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18293,7 +18283,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 29401-2026</t>
+          <t>A 25965-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18307,10 +18297,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46203</v>
+        <v>45090</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18323,7 +18313,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18366,7 +18356,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 58284-2023</t>
+          <t>A 38928-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18380,10 +18370,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45250</v>
+        <v>45548</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18396,7 +18386,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18439,7 +18429,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 2086-2023</t>
+          <t>A 7707-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18453,10 +18443,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44939</v>
+        <v>45349</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18469,7 +18459,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18512,7 +18502,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 29528-2026</t>
+          <t>A 14254-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18526,10 +18516,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46203</v>
+        <v>45009</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18542,7 +18532,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18585,7 +18575,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 2359-2023</t>
+          <t>A 47871-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18599,10 +18589,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44942</v>
+        <v>44855</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18615,7 +18605,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18658,7 +18648,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 29530-2026</t>
+          <t>A 40190-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18672,10 +18662,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46203</v>
+        <v>44820</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18688,7 +18678,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18731,7 +18721,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 29529-2026</t>
+          <t>A 40017-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18745,10 +18735,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46203</v>
+        <v>45168</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18761,7 +18751,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18804,7 +18794,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 57161-2022</t>
+          <t>A 34279-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18818,10 +18808,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44895</v>
+        <v>45138</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18834,7 +18824,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18877,7 +18867,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 27967-2024</t>
+          <t>A 54661-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18891,10 +18881,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45476</v>
+        <v>45235</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18907,7 +18897,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18950,7 +18940,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 47890-2022</t>
+          <t>A 54646-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18964,10 +18954,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44855</v>
+        <v>45235</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18980,7 +18970,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19023,7 +19013,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 31925-2024</t>
+          <t>A 2092-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19037,10 +19027,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45510</v>
+        <v>44939</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19053,7 +19043,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19096,7 +19086,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 2399-2025</t>
+          <t>A 21023-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19106,14 +19096,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45672</v>
+        <v>45439</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19126,7 +19116,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19169,7 +19159,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 29335-2022</t>
+          <t>A 62180-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19183,10 +19173,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44752</v>
+        <v>44915</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19200,11 +19190,11 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19247,7 +19237,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 22699-2024</t>
+          <t>A 23990-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19261,10 +19251,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45448</v>
+        <v>45078</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19277,7 +19267,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19320,7 +19310,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 25965-2023</t>
+          <t>A 1935-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19334,10 +19324,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45090</v>
+        <v>45308</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19350,7 +19340,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19393,7 +19383,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 19390-2023</t>
+          <t>A 52372-2021</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19407,10 +19397,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45048</v>
+        <v>44465</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19423,7 +19413,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19466,7 +19456,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 65211-2021</t>
+          <t>A 22406-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19480,10 +19470,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44515</v>
+        <v>45446</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19496,7 +19486,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19539,7 +19529,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 63029-2023</t>
+          <t>A 26179-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19553,10 +19543,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45272</v>
+        <v>45091</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19569,7 +19559,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19612,7 +19602,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 14430-2023</t>
+          <t>A 27967-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19626,10 +19616,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45012</v>
+        <v>45476</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19642,7 +19632,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19685,7 +19675,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 34770-2026</t>
+          <t>A 26837-2022</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19699,10 +19689,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46258</v>
+        <v>44740</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19715,7 +19705,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19758,7 +19748,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 23692-2023</t>
+          <t>A 25967-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19772,10 +19762,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45077</v>
+        <v>45090</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19788,7 +19778,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19831,7 +19821,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 23739-2023</t>
+          <t>A 29334-2022</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19845,10 +19835,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45077</v>
+        <v>44752</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19860,8 +19850,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I249" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19904,7 +19899,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 23740-2023</t>
+          <t>A 5941-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19918,10 +19913,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45077</v>
+        <v>45695</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19934,7 +19929,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19977,7 +19972,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 33183-2026</t>
+          <t>A 29335-2022</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19991,10 +19986,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46245</v>
+        <v>44752</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20006,8 +20001,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20050,7 +20050,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 34919-2026</t>
+          <t>A 44882-2022</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20064,10 +20064,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46259</v>
+        <v>44841</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20123,7 +20123,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 33182-2026</t>
+          <t>A 56460-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20137,10 +20137,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46245</v>
+        <v>45243</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20196,7 +20196,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 33180-2026</t>
+          <t>A 1783-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20210,10 +20210,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46245</v>
+        <v>45671</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>6.5</v>
+        <v>0.7</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20269,7 +20269,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 28980-2026</t>
+          <t>A 26178-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20283,10 +20283,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46199</v>
+        <v>45091</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20342,7 +20342,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 23898-2023</t>
+          <t>A 51577-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20356,10 +20356,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45078</v>
+        <v>45222</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20415,7 +20415,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 35988-2026</t>
+          <t>A 63029-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20429,10 +20429,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46266</v>
+        <v>45272</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20488,7 +20488,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 56460-2023</t>
+          <t>A 58284-2023</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45243</v>
+        <v>45250</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20561,7 +20561,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 5954-2025</t>
+          <t>A 27497-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20575,10 +20575,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45695</v>
+        <v>45474</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20634,7 +20634,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 38214-2023</t>
+          <t>A 48966-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20648,10 +20648,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45161</v>
+        <v>45209</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20707,7 +20707,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 27540-2024</t>
+          <t>A 2405-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20721,10 +20721,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45474</v>
+        <v>45674</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20780,7 +20780,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 9695-2023</t>
+          <t>A 27540-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20794,10 +20794,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>44984</v>
+        <v>45474</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 25962-2023</t>
+          <t>A 9773-2024</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20867,10 +20867,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45090</v>
+        <v>45362</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20926,7 +20926,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 1904-2023</t>
+          <t>A 57795-2022</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20940,10 +20940,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44939</v>
+        <v>44897</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20999,7 +20999,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 51577-2023</t>
+          <t>A 50279-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21013,10 +21013,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45222</v>
+        <v>45216</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21072,7 +21072,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 3830-2022</t>
+          <t>A 33796-2023</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44587</v>
+        <v>45133</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21145,7 +21145,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 17641-2023</t>
+          <t>A 2090-2023</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21159,10 +21159,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45035</v>
+        <v>44939</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>7.3</v>
+        <v>1.6</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21218,7 +21218,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 37517-2026</t>
+          <t>A 57161-2022</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21232,10 +21232,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>46276</v>
+        <v>44895</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21291,7 +21291,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 44882-2022</t>
+          <t>A 2086-2023</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21305,10 +21305,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>44841</v>
+        <v>44939</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21364,7 +21364,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 168-2025</t>
+          <t>A 50304-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21374,14 +21374,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45659</v>
+        <v>45209</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>6.9</v>
+        <v>17.9</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21437,7 +21437,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 49362-2024</t>
+          <t>A 11126-2025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21451,10 +21451,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45595</v>
+        <v>45723</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21510,7 +21510,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 22391-2024</t>
+          <t>A 37620-2023</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21524,10 +21524,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45446</v>
+        <v>45159</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21583,7 +21583,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 27486-2024</t>
+          <t>A 9695-2023</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21597,10 +21597,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45474</v>
+        <v>44984</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21656,7 +21656,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 25958-2023</t>
+          <t>A 2399-2025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21666,14 +21666,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45090</v>
+        <v>45672</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21729,7 +21729,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 17458-2023</t>
+          <t>A 22699-2024</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21743,10 +21743,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45034</v>
+        <v>45448</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21802,7 +21802,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 23469-2025</t>
+          <t>A 20492-2024</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21816,10 +21816,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45792</v>
+        <v>45435</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 54669-2023</t>
+          <t>A 49362-2024</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21889,10 +21889,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>45235</v>
+        <v>45595</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21948,7 +21948,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 11460-2025</t>
+          <t>A 168-2025</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21962,10 +21962,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45726</v>
+        <v>45659</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -22021,7 +22021,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 26032-2025</t>
+          <t>A 25958-2023</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -22035,10 +22035,10 @@
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>45804</v>
+        <v>45090</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -22094,7 +22094,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 25589-2025</t>
+          <t>A 27486-2024</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -22108,10 +22108,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>45803</v>
+        <v>45474</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 26020-2025</t>
+          <t>A 22391-2024</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -22181,10 +22181,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>45804</v>
+        <v>45446</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -22240,7 +22240,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 27523-2025</t>
+          <t>A 11460-2025</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22254,10 +22254,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>45813</v>
+        <v>45726</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -22313,7 +22313,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 15478-2025</t>
+          <t>A 17458-2023</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22327,10 +22327,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45747</v>
+        <v>45034</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -22403,7 +22403,7 @@
         <v>43957</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
     <row r="285" ht="15" customHeight="1">
       <c r="A285" t="inlineStr">
         <is>
-          <t>S 1259-2022</t>
+          <t>S 2857-2024</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -22469,14 +22469,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D285" s="1" t="n">
-        <v>44627</v>
+        <v>45496</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         </is>
       </c>
       <c r="I285" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -22532,7 +22532,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>S 1070-2022</t>
+          <t>S 9957-2021</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -22546,10 +22546,10 @@
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>44613</v>
+        <v>44536</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>46</v>
+        <v>26.1</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -22605,7 +22605,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>S 2857-2024</t>
+          <t>S 455-2023</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -22615,14 +22615,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>45496</v>
+        <v>44959</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>2.5</v>
+        <v>14.9</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -22678,7 +22678,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>S 9957-2021</t>
+          <t>S 5219-2022</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -22692,10 +22692,10 @@
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>44536</v>
+        <v>44820</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>26.1</v>
+        <v>22.7</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -22751,7 +22751,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>S 455-2023</t>
+          <t>S 2907-2024</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -22765,10 +22765,10 @@
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>44959</v>
+        <v>45503</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>14.9</v>
+        <v>72.5</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -22824,7 +22824,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>S 5219-2022</t>
+          <t>S 1259-2022</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -22834,14 +22834,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>44820</v>
+        <v>44627</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>22.7</v>
+        <v>0.7</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -22897,7 +22897,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>S 2907-2024</t>
+          <t>S 4069-2022</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -22911,10 +22911,10 @@
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>45503</v>
+        <v>44757</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>72.5</v>
+        <v>24.7</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -22970,7 +22970,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>S 4069-2022</t>
+          <t>S 1070-2022</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -22984,10 +22984,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>44757</v>
+        <v>44613</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>24.7</v>
+        <v>46</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -23060,7 +23060,7 @@
         <v>45484</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>44993</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45148</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>46057</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>46093</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>46097</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>46129</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>46134</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>46150</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE301"/>
+  <dimension ref="A1:AE302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 5927-2023</t>
+          <t>A 39622-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44963</v>
+        <v>45163</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1300,22 +1300,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>10.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1324,21 +1324,237 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
       </c>
       <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Dvärghäxört
+Skogsödla
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 39622-2023 artfynd.xlsx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 39622-2023 karta.png", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 39622-2023 georefererad karta.tif", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 39622-2023 FSC-klagomål.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 39622-2023 FSC-klagomål mail.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 39622-2023 tillsynsbegäran.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 39622-2023 tillsynsbegäran mail.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 4112-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Gröngöling
+Utter
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 4112-2025 artfynd.xlsx", "A 4112-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 4112-2025 karta.png", "A 4112-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 4112-2025 georefererad karta.tif", "A 4112-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 4112-2025 FSC-klagomål.docx", "A 4112-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 4112-2025 FSC-klagomål mail.docx", "A 4112-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 4112-2025 tillsynsbegäran.docx", "A 4112-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 4112-2025 tillsynsbegäran mail.docx", "A 4112-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 5927-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44963</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Hussvala
@@ -1346,248 +1562,32 @@
 Svart skogssnigel</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 5927-2023 artfynd.xlsx", "A 5927-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 5927-2023 karta.png", "A 5927-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 5927-2023 georefererad karta.tif", "A 5927-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 5927-2023 FSC-klagomål.docx", "A 5927-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 5927-2023 FSC-klagomål mail.docx", "A 5927-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 5927-2023 tillsynsbegäran.docx", "A 5927-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 5927-2023 tillsynsbegäran mail.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 39622-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Dvärghäxört
-Skogsödla
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 39622-2023 artfynd.xlsx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 39622-2023 karta.png", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 39622-2023 georefererad karta.tif", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 39622-2023 FSC-klagomål.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 39622-2023 FSC-klagomål mail.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 39622-2023 tillsynsbegäran.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 39622-2023 tillsynsbegäran mail.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 4112-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45684</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>6</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Gröngöling
-Utter
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 4112-2025 artfynd.xlsx", "A 4112-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 4112-2025 karta.png", "A 4112-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 4112-2025 georefererad karta.tif", "A 4112-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 4112-2025 FSC-klagomål.docx", "A 4112-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 4112-2025 FSC-klagomål mail.docx", "A 4112-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 4112-2025 tillsynsbegäran.docx", "A 4112-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 4112-2025 tillsynsbegäran mail.docx", "A 4112-2025")</f>
         <v/>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45945</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>46183</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45642</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 1604-2025</t>
+          <t>A 22410-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45670</v>
+        <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2919,16 +2919,11 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2937,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2949,10 +2944,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2961,39 +2956,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 1604-2025 artfynd.xlsx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 22410-2024 artfynd.xlsx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 1604-2025 karta.png", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 22410-2024 karta.png", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 1604-2025 georefererad karta.tif", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 22410-2024 georefererad karta.tif", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 1604-2025 FSC-klagomål.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 22410-2024 FSC-klagomål.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 1604-2025 FSC-klagomål mail.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 22410-2024 FSC-klagomål mail.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 1604-2025 tillsynsbegäran.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 22410-2024 tillsynsbegäran.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 1604-2025 tillsynsbegäran mail.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 22410-2024 tillsynsbegäran mail.docx", "A 22410-2024")</f>
         <v/>
       </c>
     </row>
@@ -3017,7 +3012,7 @@
         <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3105,7 +3100,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 10496-2026</t>
+          <t>A 57429-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3119,10 +3114,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46076</v>
+        <v>45980</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3135,20 +3130,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3159,10 +3154,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3175,42 +3170,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 10496-2026 artfynd.xlsx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 57429-2025 artfynd.xlsx", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 10496-2026 karta.png", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 57429-2025 karta.png", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 10496-2026 georefererad karta.tif", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 57429-2025 georefererad karta.tif", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 10496-2026 FSC-klagomål.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 57429-2025 FSC-klagomål.docx", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 10496-2026 FSC-klagomål mail.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 57429-2025 FSC-klagomål mail.docx", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 10496-2026 tillsynsbegäran.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 57429-2025 tillsynsbegäran.docx", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 10496-2026 tillsynsbegäran mail.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 57429-2025 tillsynsbegäran mail.docx", "A 57429-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 57429-2025</t>
+          <t>A 10496-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3224,10 +3219,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45980</v>
+        <v>46076</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3240,10 +3235,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3252,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3264,10 +3259,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3280,42 +3275,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 57429-2025 artfynd.xlsx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 10496-2026 artfynd.xlsx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 57429-2025 karta.png", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 10496-2026 karta.png", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 57429-2025 georefererad karta.tif", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 10496-2026 georefererad karta.tif", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 57429-2025 FSC-klagomål.docx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 10496-2026 FSC-klagomål.docx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 57429-2025 FSC-klagomål mail.docx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 10496-2026 FSC-klagomål mail.docx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 57429-2025 tillsynsbegäran.docx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 10496-2026 tillsynsbegäran.docx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 57429-2025 tillsynsbegäran mail.docx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 10496-2026 tillsynsbegäran mail.docx", "A 10496-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15068-2023</t>
+          <t>A 1604-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3329,10 +3324,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45015</v>
+        <v>45670</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3344,21 +3339,26 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>9.9</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3385,42 +3385,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 15068-2023 artfynd.xlsx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 1604-2025 artfynd.xlsx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 15068-2023 karta.png", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 1604-2025 karta.png", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 15068-2023 georefererad karta.tif", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 1604-2025 georefererad karta.tif", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 15068-2023 FSC-klagomål.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 1604-2025 FSC-klagomål.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 15068-2023 FSC-klagomål mail.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 1604-2025 FSC-klagomål mail.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 15068-2023 tillsynsbegäran.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 1604-2025 tillsynsbegäran.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 15068-2023 tillsynsbegäran mail.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 1604-2025 tillsynsbegäran mail.docx", "A 1604-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22410-2024</t>
+          <t>A 15068-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45446</v>
+        <v>45015</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3450,13 +3450,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3486,39 +3486,39 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 22410-2024 artfynd.xlsx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 15068-2023 artfynd.xlsx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 22410-2024 karta.png", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 15068-2023 karta.png", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 22410-2024 georefererad karta.tif", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 15068-2023 georefererad karta.tif", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 22410-2024 FSC-klagomål.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 15068-2023 FSC-klagomål.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 22410-2024 FSC-klagomål mail.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 15068-2023 FSC-klagomål mail.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 22410-2024 tillsynsbegäran.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 15068-2023 tillsynsbegäran.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 22410-2024 tillsynsbegäran mail.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 15068-2023 tillsynsbegäran mail.docx", "A 15068-2023")</f>
         <v/>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
         <v>45784</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S 2910-2024</t>
+          <t>S 2731-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3640,14 +3640,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45503</v>
+        <v>44704</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3659,8 +3659,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>24.7</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3696,50 +3701,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2910-2024 artfynd.xlsx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2731-2022 artfynd.xlsx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2910-2024 karta.png", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2731-2022 karta.png", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2910-2024 georefererad karta.tif", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2731-2022 georefererad karta.tif", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2910-2024 FSC-klagomål.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2731-2022 FSC-klagomål.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2910-2024 FSC-klagomål mail.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2731-2022 FSC-klagomål mail.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2910-2024 tillsynsbegäran.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2731-2022 tillsynsbegäran.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2910-2024 tillsynsbegäran mail.docx", "S 2910-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/S 2910-2024 prioriterade fågelarter.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2731-2022 tillsynsbegäran mail.docx", "S 2731-2022")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S 4056-2023</t>
+          <t>S 2910-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3749,14 +3750,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45243</v>
+        <v>45503</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3769,7 +3770,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.1</v>
+        <v>0.4</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3809,42 +3810,46 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 4056-2023 artfynd.xlsx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2910-2024 artfynd.xlsx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 4056-2023 karta.png", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2910-2024 karta.png", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 4056-2023 georefererad karta.tif", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2910-2024 georefererad karta.tif", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 4056-2023 FSC-klagomål.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2910-2024 FSC-klagomål.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 4056-2023 FSC-klagomål mail.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2910-2024 FSC-klagomål mail.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 4056-2023 tillsynsbegäran.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2910-2024 tillsynsbegäran.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 4056-2023 tillsynsbegäran mail.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2910-2024 tillsynsbegäran mail.docx", "S 2910-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/S 2910-2024 prioriterade fågelarter.docx", "S 2910-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S 2731-2022</t>
+          <t>S 4056-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3858,10 +3863,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44704</v>
+        <v>45243</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3873,13 +3878,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>24.7</v>
+        <v>7.1</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3915,39 +3915,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2731-2022 artfynd.xlsx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 4056-2023 artfynd.xlsx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2731-2022 karta.png", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 4056-2023 karta.png", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2731-2022 georefererad karta.tif", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 4056-2023 georefererad karta.tif", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2731-2022 FSC-klagomål.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 4056-2023 FSC-klagomål.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2731-2022 FSC-klagomål mail.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 4056-2023 FSC-klagomål mail.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2731-2022 tillsynsbegäran.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 4056-2023 tillsynsbegäran.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2731-2022 tillsynsbegäran mail.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 4056-2023 tillsynsbegäran mail.docx", "S 4056-2023")</f>
         <v/>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 29333-2022</t>
+          <t>A 56006-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44752</v>
+        <v>44477</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56006-2021</t>
+          <t>A 29333-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44477</v>
+        <v>44752</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38556-2022</t>
+          <t>A 9773-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44813</v>
+        <v>45362</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5213,7 +5213,7 @@
         <v>44543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12139-2022</t>
+          <t>A 62180-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44636</v>
+        <v>44915</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5298,8 +5298,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.3</v>
+        <v>7.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5342,7 +5347,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45063-2022</t>
+          <t>A 26837-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5356,10 +5361,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44841</v>
+        <v>44740</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5372,7 +5377,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5415,7 +5420,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6020-2022</t>
+          <t>A 9748-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5429,10 +5434,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44599</v>
+        <v>45362</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5445,7 +5450,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5488,7 +5493,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 73830-2021</t>
+          <t>A 12139-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5502,10 +5507,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44552</v>
+        <v>44636</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5518,7 +5523,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5561,7 +5566,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19390-2023</t>
+          <t>A 38556-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5575,10 +5580,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45048</v>
+        <v>44813</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5591,7 +5596,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5634,7 +5639,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 44814-2022</t>
+          <t>A 29334-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5648,10 +5653,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44841</v>
+        <v>44752</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5663,8 +5668,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5707,7 +5717,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9748-2024</t>
+          <t>A 27497-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5721,10 +5731,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45362</v>
+        <v>45474</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5780,7 +5790,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52876-2024</t>
+          <t>A 24154-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5794,10 +5804,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45610</v>
+        <v>45079</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5810,7 +5820,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5853,7 +5863,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10379-2024</t>
+          <t>A 45063-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5867,10 +5877,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45365</v>
+        <v>44841</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5883,7 +5893,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5926,7 +5936,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23740-2023</t>
+          <t>A 21023-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5940,10 +5950,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45077</v>
+        <v>45439</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5956,7 +5966,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5999,7 +6009,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 72261-2021</t>
+          <t>A 26178-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6013,10 +6023,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44545</v>
+        <v>45091</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6072,7 +6082,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17737-2023</t>
+          <t>A 26179-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6086,10 +6096,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45037</v>
+        <v>45091</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6102,7 +6112,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6145,7 +6155,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 54669-2023</t>
+          <t>A 54646-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6162,7 +6172,7 @@
         <v>45235</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6175,7 +6185,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6218,7 +6228,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9359-2025</t>
+          <t>A 21910-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6232,10 +6242,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45715</v>
+        <v>45443</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6248,7 +6258,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6291,7 +6301,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 23469-2025</t>
+          <t>A 21152-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6305,10 +6315,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45792</v>
+        <v>44704</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6321,7 +6331,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6364,7 +6374,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25589-2025</t>
+          <t>A 58130-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6378,10 +6388,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45803</v>
+        <v>44900</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6394,7 +6404,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>23.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6437,7 +6447,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 47890-2022</t>
+          <t>A 11121-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6451,10 +6461,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44855</v>
+        <v>45723</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6467,7 +6477,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6510,7 +6520,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 26032-2025</t>
+          <t>A 1492-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6524,10 +6534,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45804</v>
+        <v>45305</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6540,7 +6550,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6583,7 +6593,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26020-2025</t>
+          <t>A 1493-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6597,10 +6607,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45804</v>
+        <v>45305</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6613,7 +6623,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6656,7 +6666,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23898-2023</t>
+          <t>A 9573-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6670,10 +6680,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45078</v>
+        <v>45715</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6686,7 +6696,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6729,7 +6739,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52243-2025</t>
+          <t>A 19643-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6743,10 +6753,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45953</v>
+        <v>45432</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6758,8 +6768,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6802,7 +6817,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 53163-2025</t>
+          <t>A 22406-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6816,10 +6831,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45958</v>
+        <v>45446</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6832,7 +6847,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6875,7 +6890,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31399-2025</t>
+          <t>A 55049-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6889,10 +6904,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45833</v>
+        <v>45237</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6905,7 +6920,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6948,7 +6963,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52246-2025</t>
+          <t>A 10379-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6962,10 +6977,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45953</v>
+        <v>45365</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6978,7 +6993,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7021,7 +7036,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7915-2025</t>
+          <t>A 54661-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7035,10 +7050,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45707</v>
+        <v>45235</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7051,7 +7066,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7094,7 +7109,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31704-2023</t>
+          <t>A 11605-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7108,10 +7123,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45117</v>
+        <v>44994</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7124,7 +7139,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.7</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7167,7 +7182,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 27523-2025</t>
+          <t>A 26058-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7181,10 +7196,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45813</v>
+        <v>45468</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7197,7 +7212,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7240,7 +7255,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14912-2024</t>
+          <t>A 47871-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7250,14 +7265,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45398</v>
+        <v>44855</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7270,7 +7285,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7313,7 +7328,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1225-2026</t>
+          <t>A 44880-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7327,10 +7342,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46031</v>
+        <v>44841</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7343,7 +7358,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.6</v>
+        <v>0.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7386,7 +7401,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 15478-2025</t>
+          <t>A 57208-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7400,10 +7415,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45747</v>
+        <v>44895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7416,7 +7431,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7459,7 +7474,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21146-2022</t>
+          <t>A 31399-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7473,10 +7488,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44704</v>
+        <v>45833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7489,7 +7504,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.4</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7532,7 +7547,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2537-2026</t>
+          <t>A 64091-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7546,10 +7561,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46037</v>
+        <v>45279</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7562,7 +7577,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7605,7 +7620,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28693-2025</t>
+          <t>A 38897-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7619,10 +7634,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45819</v>
+        <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7635,7 +7650,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7678,7 +7693,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2474-2026</t>
+          <t>A 7915-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7692,10 +7707,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46037</v>
+        <v>45707</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7708,7 +7723,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>8.6</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7751,7 +7766,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 41912-2025</t>
+          <t>A 40814-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7765,10 +7780,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45903</v>
+        <v>45171</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7781,7 +7796,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7824,7 +7839,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 29642-2025</t>
+          <t>A 40017-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7838,10 +7853,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45825</v>
+        <v>45168</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7854,7 +7869,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7897,7 +7912,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41926-2025</t>
+          <t>A 37501-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7911,10 +7926,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45903</v>
+        <v>45541</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7970,7 +7985,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 54667-2023</t>
+          <t>A 33796-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7984,10 +7999,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45235</v>
+        <v>45133</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8000,7 +8015,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8043,7 +8058,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3934-2026</t>
+          <t>A 2088-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8057,10 +8072,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46043</v>
+        <v>44939</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8073,7 +8088,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8116,7 +8131,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 42708-2025</t>
+          <t>A 2092-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8130,10 +8145,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45908</v>
+        <v>44939</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8146,7 +8161,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8189,7 +8204,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 42728-2025</t>
+          <t>A 52528-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8203,10 +8218,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45908</v>
+        <v>44466</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8219,7 +8234,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8262,7 +8277,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 4989-2026</t>
+          <t>A 15987-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8276,10 +8291,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46049</v>
+        <v>45749</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8292,7 +8307,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8335,7 +8350,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 5002-2026</t>
+          <t>A 13283-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8349,10 +8364,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46049</v>
+        <v>46093</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8365,7 +8380,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>8.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8408,7 +8423,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13797-2025</t>
+          <t>A 41912-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8422,10 +8437,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45737</v>
+        <v>45903</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8438,7 +8453,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8481,7 +8496,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 12038-2025</t>
+          <t>A 41926-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8495,10 +8510,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45728</v>
+        <v>45903</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8511,7 +8526,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8554,7 +8569,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 43990-2025</t>
+          <t>A 42728-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8568,10 +8583,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45915</v>
+        <v>45908</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8584,7 +8599,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8627,7 +8642,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 25963-2023</t>
+          <t>A 14734-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8641,10 +8656,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45090</v>
+        <v>46101</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8657,7 +8672,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8700,7 +8715,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 40814-2023</t>
+          <t>A 42708-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8714,10 +8729,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45171</v>
+        <v>45908</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8730,7 +8745,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8773,7 +8788,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32855-2023</t>
+          <t>A 36838-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8787,10 +8802,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45124</v>
+        <v>45538</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8803,7 +8818,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8846,7 +8861,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17270-2025</t>
+          <t>A 34279-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8860,10 +8875,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45756</v>
+        <v>45138</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8876,7 +8891,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8919,7 +8934,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 1492-2024</t>
+          <t>A 15236-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8933,10 +8948,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45305</v>
+        <v>46105</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8949,7 +8964,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8992,7 +9007,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 1493-2024</t>
+          <t>A 15240-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9006,10 +9021,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45305</v>
+        <v>46105</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9022,7 +9037,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9065,7 +9080,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 21910-2024</t>
+          <t>A 15108-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9079,10 +9094,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45443</v>
+        <v>46105</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9095,7 +9110,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9138,7 +9153,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32704-2025</t>
+          <t>A 13797-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9152,10 +9167,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45839</v>
+        <v>45737</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9168,7 +9183,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9211,7 +9226,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 44897-2025</t>
+          <t>A 43990-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9225,10 +9240,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45918</v>
+        <v>45915</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9241,7 +9256,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9301,7 +9316,7 @@
         <v>45918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9357,7 +9372,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 57703-2022</t>
+          <t>A 57795-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9374,7 +9389,7 @@
         <v>44897</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9387,7 +9402,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9430,7 +9445,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 26058-2024</t>
+          <t>A 1783-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9444,10 +9459,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45468</v>
+        <v>45671</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9460,7 +9475,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9503,7 +9518,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 63783-2023</t>
+          <t>A 50279-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9517,10 +9532,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45278</v>
+        <v>45216</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9533,7 +9548,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9576,7 +9591,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7242-2026</t>
+          <t>A 16363-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9590,10 +9605,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46058</v>
+        <v>46111</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9606,7 +9621,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9649,7 +9664,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 1397-2023</t>
+          <t>A 16283-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9663,10 +9678,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44936</v>
+        <v>46111</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9679,7 +9694,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9722,7 +9737,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 8024-2026</t>
+          <t>A 73830-2021</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9736,10 +9751,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46063</v>
+        <v>44552</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9751,13 +9766,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9800,7 +9810,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 9105-2026</t>
+          <t>A 6020-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9814,10 +9824,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46069</v>
+        <v>44599</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9830,7 +9840,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9873,7 +9883,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 18285-2025</t>
+          <t>A 44897-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9887,10 +9897,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45762</v>
+        <v>45918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9903,7 +9913,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9946,7 +9956,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 9127-2026</t>
+          <t>A 17608-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9960,10 +9970,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46069</v>
+        <v>46121</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9976,7 +9986,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10019,7 +10029,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 36543-2022</t>
+          <t>A 13068-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10033,10 +10043,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44804</v>
+        <v>45002</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10049,7 +10059,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10092,7 +10102,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61602-2024</t>
+          <t>A 48672-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10106,10 +10116,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45646</v>
+        <v>45936</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10122,7 +10132,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10165,7 +10175,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 13068-2023</t>
+          <t>A 17737-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10179,10 +10189,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45002</v>
+        <v>45037</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10195,7 +10205,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10238,7 +10248,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 9125-2026</t>
+          <t>A 981-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10252,10 +10262,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46069</v>
+        <v>44935</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10268,7 +10278,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10311,7 +10321,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 9292-2026</t>
+          <t>A 44925-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10325,10 +10335,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46070</v>
+        <v>45918</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10341,7 +10351,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10384,7 +10394,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 5954-2025</t>
+          <t>A 36280-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10394,14 +10404,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45695</v>
+        <v>45867</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10414,7 +10424,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10457,7 +10467,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 48672-2025</t>
+          <t>A 30136-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10471,10 +10481,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45936</v>
+        <v>44757</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10486,8 +10496,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10530,7 +10545,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19643-2024</t>
+          <t>A 20492-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10544,10 +10559,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45432</v>
+        <v>45435</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10559,13 +10574,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10608,7 +10618,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 10473-2026</t>
+          <t>A 22975-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10622,10 +10632,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46077</v>
+        <v>45072</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10638,7 +10648,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10681,7 +10691,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 10466-2026</t>
+          <t>A 35490-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10695,10 +10705,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46077</v>
+        <v>45855</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10711,7 +10721,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10754,7 +10764,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 10480-2026</t>
+          <t>A 53142-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10768,10 +10778,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46077</v>
+        <v>45958</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10784,7 +10794,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10827,7 +10837,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 23692-2023</t>
+          <t>A 44864-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10841,10 +10851,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45077</v>
+        <v>45918</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10857,7 +10867,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10900,7 +10910,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 44925-2025</t>
+          <t>A 43992-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10914,10 +10924,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45918</v>
+        <v>45915</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10930,7 +10940,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10973,7 +10983,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 37501-2024</t>
+          <t>A 13611-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10987,10 +10997,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45541</v>
+        <v>45736</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11003,7 +11013,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11046,7 +11056,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 44880-2022</t>
+          <t>A 38928-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11060,10 +11070,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44841</v>
+        <v>45548</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11076,7 +11086,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11119,7 +11129,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 171-2025</t>
+          <t>A 63783-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11133,10 +11143,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45659</v>
+        <v>45278</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11149,7 +11159,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11192,7 +11202,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 36280-2025</t>
+          <t>A 9359-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11202,14 +11212,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45867</v>
+        <v>45715</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11222,7 +11232,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11265,7 +11275,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 38897-2025</t>
+          <t>A 3205-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11279,10 +11289,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45887</v>
+        <v>45679</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11294,8 +11304,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.5</v>
+        <v>6.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11338,7 +11353,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 9691-2023</t>
+          <t>A 52876-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11352,10 +11367,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44984</v>
+        <v>45610</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11368,7 +11383,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11411,7 +11426,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 17641-2023</t>
+          <t>A 32855-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11425,10 +11440,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45035</v>
+        <v>45124</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11441,7 +11456,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11484,7 +11499,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 39650-2023</t>
+          <t>A 3864-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11498,10 +11513,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45167</v>
+        <v>44951</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11514,7 +11529,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11557,7 +11572,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 13283-2026</t>
+          <t>A 56455-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11571,10 +11586,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46093</v>
+        <v>45975</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11587,7 +11602,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>8.1</v>
+        <v>0.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11630,7 +11645,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 24154-2023</t>
+          <t>A 42177-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11644,10 +11659,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45079</v>
+        <v>45178</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11660,7 +11675,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11703,7 +11718,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 65211-2021</t>
+          <t>A 57343-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11717,10 +11732,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44515</v>
+        <v>45980</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11733,7 +11748,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11776,7 +11791,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 14734-2026</t>
+          <t>A 30638-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11790,10 +11805,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46101</v>
+        <v>45112</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11806,7 +11821,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11849,7 +11864,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 53142-2025</t>
+          <t>A 57790-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11863,10 +11878,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45958</v>
+        <v>45981</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11879,7 +11894,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11922,7 +11937,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 24765-2023</t>
+          <t>A 58284-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11936,10 +11951,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45084</v>
+        <v>45250</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11952,7 +11967,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11995,7 +12010,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 15240-2026</t>
+          <t>A 2086-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12009,10 +12024,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46105</v>
+        <v>44939</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12025,7 +12040,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12068,7 +12083,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 15236-2026</t>
+          <t>A 58347-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12082,10 +12097,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46105</v>
+        <v>45985</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12098,7 +12113,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12141,7 +12156,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 15108-2026</t>
+          <t>A 2359-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12155,10 +12170,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46105</v>
+        <v>44942</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12171,7 +12186,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12214,7 +12229,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 16363-2026</t>
+          <t>A 35168-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12228,10 +12243,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46111</v>
+        <v>45852</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12244,7 +12259,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12287,7 +12302,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 16283-2026</t>
+          <t>A 28221-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12301,10 +12316,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46111</v>
+        <v>45099</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12317,7 +12332,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.9</v>
+        <v>6.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12360,7 +12375,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 17608-2026</t>
+          <t>A 171-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12374,10 +12389,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46121</v>
+        <v>45659</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12390,7 +12405,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12433,7 +12448,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 56455-2025</t>
+          <t>A 20671-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12447,10 +12462,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45975</v>
+        <v>46141</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12463,7 +12478,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12506,7 +12521,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 35490-2025</t>
+          <t>A 60789-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12520,10 +12535,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45855</v>
+        <v>45999</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12536,7 +12551,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12579,7 +12594,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 13611-2025</t>
+          <t>A 57161-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12593,10 +12608,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45736</v>
+        <v>44895</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12609,7 +12624,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12652,7 +12667,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 57343-2025</t>
+          <t>A 45192-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12666,10 +12681,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45980</v>
+        <v>44844</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12682,7 +12697,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12725,7 +12740,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 57790-2025</t>
+          <t>A 27967-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12739,10 +12754,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45981</v>
+        <v>45476</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12755,7 +12770,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12798,7 +12813,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 981-2023</t>
+          <t>A 36543-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12812,10 +12827,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44935</v>
+        <v>44804</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12828,7 +12843,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12871,7 +12886,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 58347-2025</t>
+          <t>A 5941-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12885,10 +12900,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45985</v>
+        <v>45695</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12901,7 +12916,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12944,7 +12959,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 44864-2025</t>
+          <t>A 40190-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12958,10 +12973,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45918</v>
+        <v>44820</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12974,7 +12989,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13017,7 +13032,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 42177-2023</t>
+          <t>A 44814-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13031,10 +13046,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45178</v>
+        <v>44841</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13047,7 +13062,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13090,7 +13105,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 28221-2023</t>
+          <t>A 47890-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13104,10 +13119,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45099</v>
+        <v>44855</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13120,7 +13135,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>6.7</v>
+        <v>1.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13163,7 +13178,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 11605-2023</t>
+          <t>A 22550-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13177,10 +13192,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44994</v>
+        <v>46155</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13236,7 +13251,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 23693-2023</t>
+          <t>A 22552-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13250,10 +13265,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45077</v>
+        <v>46155</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13266,7 +13281,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13309,7 +13324,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 43992-2025</t>
+          <t>A 1397-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13323,10 +13338,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45915</v>
+        <v>44936</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13339,7 +13354,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13382,7 +13397,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 45192-2022</t>
+          <t>A 34631-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13396,10 +13411,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44844</v>
+        <v>45848</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13412,7 +13427,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13455,7 +13470,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 60789-2025</t>
+          <t>A 52243-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13469,10 +13484,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45999</v>
+        <v>45953</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13485,7 +13500,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13528,7 +13543,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 3205-2025</t>
+          <t>A 53163-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13542,10 +13557,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45679</v>
+        <v>45958</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13557,13 +13572,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>6.7</v>
+        <v>3.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13606,7 +13616,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 9573-2025</t>
+          <t>A 52246-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13620,10 +13630,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45715</v>
+        <v>45953</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13636,7 +13646,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13679,7 +13689,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 20671-2026</t>
+          <t>A 23693-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13693,10 +13703,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46141</v>
+        <v>45077</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13709,7 +13719,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13752,7 +13762,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 35168-2025</t>
+          <t>A 23990-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13766,10 +13776,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45852</v>
+        <v>45078</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13782,7 +13792,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13825,7 +13835,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 22975-2023</t>
+          <t>A 34591-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13839,10 +13849,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45072</v>
+        <v>45140</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13855,7 +13865,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13898,7 +13908,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 14430-2023</t>
+          <t>A 52372-2021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13912,10 +13922,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45012</v>
+        <v>44465</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13928,7 +13938,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13971,7 +13981,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 64091-2023</t>
+          <t>A 11126-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13985,10 +13995,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45279</v>
+        <v>45723</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14001,7 +14011,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14044,7 +14054,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 25962-2023</t>
+          <t>A 1225-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14058,10 +14068,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45090</v>
+        <v>46031</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14074,7 +14084,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>7.3</v>
+        <v>5.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14117,7 +14127,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 30136-2022</t>
+          <t>A 2474-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14131,10 +14141,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44757</v>
+        <v>46037</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14146,13 +14156,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14195,7 +14200,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 38214-2023</t>
+          <t>A 54667-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14209,10 +14214,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45161</v>
+        <v>45235</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14225,7 +14230,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14268,7 +14273,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 22550-2026</t>
+          <t>A 2537-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14282,10 +14287,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46155</v>
+        <v>46037</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14298,7 +14303,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14341,7 +14346,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 23739-2023</t>
+          <t>A 3934-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14355,10 +14360,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45077</v>
+        <v>46043</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14371,7 +14376,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14414,7 +14419,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 22552-2026</t>
+          <t>A 31925-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14428,10 +14433,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46155</v>
+        <v>45510</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14444,7 +14449,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14487,7 +14492,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 34631-2025</t>
+          <t>A 53676-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14501,10 +14506,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45848</v>
+        <v>45960</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14517,7 +14522,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14560,7 +14565,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 34591-2023</t>
+          <t>A 44846-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14574,10 +14579,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45140</v>
+        <v>45918</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14590,7 +14595,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14633,7 +14638,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 53676-2025</t>
+          <t>A 57703-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14647,10 +14652,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45960</v>
+        <v>44897</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14663,7 +14668,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14706,7 +14711,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 44846-2025</t>
+          <t>A 5002-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14720,10 +14725,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45918</v>
+        <v>46049</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14736,7 +14741,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14779,7 +14784,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 25674-2026</t>
+          <t>A 2399-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14789,14 +14794,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46178</v>
+        <v>45672</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14809,7 +14814,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14852,7 +14857,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 25699-2026</t>
+          <t>A 29335-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14866,10 +14871,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46178</v>
+        <v>44752</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14881,8 +14886,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14925,7 +14935,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 25772-2026</t>
+          <t>A 22699-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14939,10 +14949,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46178</v>
+        <v>45448</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14955,7 +14965,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14998,7 +15008,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 25778-2026</t>
+          <t>A 4989-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15012,10 +15022,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46178</v>
+        <v>46049</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15028,7 +15038,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15071,7 +15081,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 25789-2026</t>
+          <t>A 2090-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15085,10 +15095,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46178</v>
+        <v>44939</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15101,7 +15111,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15144,7 +15154,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 25912-2026</t>
+          <t>A 25965-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15158,10 +15168,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46178</v>
+        <v>45090</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15174,7 +15184,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15217,7 +15227,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 25794-2026</t>
+          <t>A 25501-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15231,10 +15241,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15247,7 +15257,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15290,7 +15300,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 25780-2026</t>
+          <t>A 25778-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15307,7 +15317,7 @@
         <v>46178</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15320,7 +15330,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15363,7 +15373,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 25501-2026</t>
+          <t>A 25789-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15377,10 +15387,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15393,7 +15403,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15436,7 +15446,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 25765-2026</t>
+          <t>A 25674-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15453,7 +15463,7 @@
         <v>46178</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15466,7 +15476,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15509,7 +15519,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 26578-2026</t>
+          <t>A 25699-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15523,10 +15533,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15539,7 +15549,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15582,7 +15592,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 26580-2026</t>
+          <t>A 25963-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15596,10 +15606,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46183</v>
+        <v>45090</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15612,7 +15622,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15655,7 +15665,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 26597-2026</t>
+          <t>A 25765-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15669,10 +15679,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15685,7 +15695,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15728,7 +15738,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 26564-2026</t>
+          <t>A 7242-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15742,10 +15752,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46183</v>
+        <v>46058</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15758,7 +15768,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15801,7 +15811,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 26593-2026</t>
+          <t>A 19390-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15815,10 +15825,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46183</v>
+        <v>45048</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15831,7 +15841,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15874,7 +15884,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 26583-2026</t>
+          <t>A 25772-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15888,10 +15898,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15904,7 +15914,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>8.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15947,7 +15957,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 26594-2026</t>
+          <t>A 25912-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15961,10 +15971,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15977,7 +15987,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16020,7 +16030,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 26596-2026</t>
+          <t>A 25780-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16034,10 +16044,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16050,7 +16060,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16093,7 +16103,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 27146-2026</t>
+          <t>A 25794-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16107,10 +16117,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46188</v>
+        <v>46178</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16123,7 +16133,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16166,7 +16176,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 9559-2022</t>
+          <t>A 8204-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16180,10 +16190,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44617</v>
+        <v>44971</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16196,7 +16206,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16239,7 +16249,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 31925-2024</t>
+          <t>A 26580-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16253,10 +16263,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45510</v>
+        <v>46183</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16269,7 +16279,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16312,7 +16322,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 29401-2026</t>
+          <t>A 26597-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16326,10 +16336,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46203</v>
+        <v>46183</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16342,7 +16352,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16385,7 +16395,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 29530-2026</t>
+          <t>A 26564-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16399,10 +16409,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46203</v>
+        <v>46183</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16415,7 +16425,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16458,7 +16468,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 29528-2026</t>
+          <t>A 26596-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16472,10 +16482,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46203</v>
+        <v>46183</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16488,7 +16498,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16531,7 +16541,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 29529-2026</t>
+          <t>A 24765-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16545,10 +16555,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46203</v>
+        <v>45084</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16561,7 +16571,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16604,7 +16614,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 30638-2023</t>
+          <t>A 8024-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16618,10 +16628,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45112</v>
+        <v>46063</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16633,8 +16643,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16677,7 +16692,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 2088-2023</t>
+          <t>A 26583-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16691,10 +16706,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44939</v>
+        <v>46183</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16707,7 +16722,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16750,7 +16765,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 34919-2026</t>
+          <t>A 26594-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16764,10 +16779,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46259</v>
+        <v>46183</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16780,7 +16795,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16823,7 +16838,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 34770-2026</t>
+          <t>A 26578-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16837,10 +16852,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46258</v>
+        <v>46183</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16853,7 +16868,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16896,7 +16911,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 33183-2026</t>
+          <t>A 26593-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16910,10 +16925,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46245</v>
+        <v>46183</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16926,7 +16941,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16969,7 +16984,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 33180-2026</t>
+          <t>A 9292-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16983,10 +16998,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46245</v>
+        <v>46070</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16999,7 +17014,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17042,7 +17057,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 28980-2026</t>
+          <t>A 9125-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17056,10 +17071,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46199</v>
+        <v>46069</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17072,7 +17087,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17115,7 +17130,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 33182-2026</t>
+          <t>A 9105-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17129,10 +17144,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46245</v>
+        <v>46069</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17145,7 +17160,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17188,7 +17203,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 52528-2021</t>
+          <t>A 9127-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17202,10 +17217,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44466</v>
+        <v>46069</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17218,7 +17233,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17261,7 +17276,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 35988-2026</t>
+          <t>A 10466-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17275,10 +17290,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46266</v>
+        <v>46077</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17291,7 +17306,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17334,7 +17349,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 36838-2024</t>
+          <t>A 10473-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17348,10 +17363,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45538</v>
+        <v>46077</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17364,7 +17379,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17407,7 +17422,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 1904-2023</t>
+          <t>A 10480-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17421,10 +17436,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44939</v>
+        <v>46077</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17437,7 +17452,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17480,7 +17495,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 8204-2023</t>
+          <t>A 27146-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17494,10 +17509,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44971</v>
+        <v>46188</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17510,7 +17525,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17553,7 +17568,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 11121-2025</t>
+          <t>A 65211-2021</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17567,10 +17582,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45723</v>
+        <v>44515</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17583,7 +17598,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.2</v>
+        <v>4.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17626,7 +17641,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 3830-2022</t>
+          <t>A 9691-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17640,10 +17655,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44587</v>
+        <v>44984</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17656,7 +17671,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17699,7 +17714,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 37517-2026</t>
+          <t>A 39650-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17713,10 +17728,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46276</v>
+        <v>45167</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17729,7 +17744,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17772,7 +17787,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 21152-2022</t>
+          <t>A 63029-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17786,10 +17801,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44704</v>
+        <v>45272</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17802,7 +17817,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17845,7 +17860,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 58130-2022</t>
+          <t>A 14430-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17859,10 +17874,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44900</v>
+        <v>45012</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17875,7 +17890,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>23.2</v>
+        <v>0.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17918,7 +17933,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 2359-2023</t>
+          <t>A 23692-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17932,10 +17947,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44942</v>
+        <v>45077</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17948,7 +17963,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17991,7 +18006,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 55049-2023</t>
+          <t>A 23739-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18005,10 +18020,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45237</v>
+        <v>45077</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18021,7 +18036,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18064,7 +18079,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 15987-2025</t>
+          <t>A 23740-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18078,10 +18093,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45749</v>
+        <v>45077</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18094,7 +18109,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18137,7 +18152,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 57208-2022</t>
+          <t>A 14912-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18147,14 +18162,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44895</v>
+        <v>45398</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18167,7 +18182,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18210,7 +18225,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 3864-2023</t>
+          <t>A 1935-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18224,10 +18239,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44951</v>
+        <v>45308</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18240,7 +18255,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18283,7 +18298,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 25965-2023</t>
+          <t>A 72261-2021</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18297,10 +18312,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45090</v>
+        <v>44545</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18313,7 +18328,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18356,7 +18371,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 38928-2024</t>
+          <t>A 23898-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18370,10 +18385,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45548</v>
+        <v>45078</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18386,7 +18401,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18429,7 +18444,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 7707-2024</t>
+          <t>A 29401-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18443,10 +18458,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45349</v>
+        <v>46203</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18459,7 +18474,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18519,7 +18534,7 @@
         <v>45009</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18575,7 +18590,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 47871-2022</t>
+          <t>A 37620-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18589,10 +18604,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44855</v>
+        <v>45159</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18605,7 +18620,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18648,7 +18663,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 40190-2022</t>
+          <t>A 29528-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18662,10 +18677,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44820</v>
+        <v>46203</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18678,7 +18693,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18721,7 +18736,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 40017-2023</t>
+          <t>A 29530-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18735,10 +18750,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45168</v>
+        <v>46203</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18751,7 +18766,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18794,7 +18809,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 34279-2023</t>
+          <t>A 29529-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18808,10 +18823,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45138</v>
+        <v>46203</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18824,7 +18839,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18867,7 +18882,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 54661-2023</t>
+          <t>A 31704-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18881,10 +18896,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45235</v>
+        <v>45117</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18897,7 +18912,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18940,7 +18955,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 54646-2023</t>
+          <t>A 7707-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18954,10 +18969,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45235</v>
+        <v>45349</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18970,7 +18985,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19013,7 +19028,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 2092-2023</t>
+          <t>A 56460-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19027,10 +19042,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44939</v>
+        <v>45243</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19043,7 +19058,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19086,7 +19101,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 21023-2024</t>
+          <t>A 5954-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19100,10 +19115,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45439</v>
+        <v>45695</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19116,7 +19131,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19159,7 +19174,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 62180-2022</t>
+          <t>A 2405-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19173,10 +19188,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44915</v>
+        <v>45674</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19188,13 +19203,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19237,7 +19247,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 23990-2023</t>
+          <t>A 25967-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19251,10 +19261,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45078</v>
+        <v>45090</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19267,7 +19277,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19310,7 +19320,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 1935-2024</t>
+          <t>A 9559-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19324,10 +19334,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45308</v>
+        <v>44617</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19340,7 +19350,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19383,7 +19393,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 52372-2021</t>
+          <t>A 34770-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19397,10 +19407,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44465</v>
+        <v>46258</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19413,7 +19423,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19456,7 +19466,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 22406-2024</t>
+          <t>A 33183-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19470,10 +19480,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45446</v>
+        <v>46245</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19486,7 +19496,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19529,7 +19539,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 26179-2023</t>
+          <t>A 34919-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19543,10 +19553,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45091</v>
+        <v>46259</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19559,7 +19569,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19602,7 +19612,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 27967-2024</t>
+          <t>A 33182-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19616,10 +19626,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45476</v>
+        <v>46245</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19632,7 +19642,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19675,7 +19685,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 26837-2022</t>
+          <t>A 33180-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19689,10 +19699,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44740</v>
+        <v>46245</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19705,7 +19715,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19748,7 +19758,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 25967-2023</t>
+          <t>A 28980-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19762,10 +19772,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45090</v>
+        <v>46199</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19778,7 +19788,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19821,7 +19831,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 29334-2022</t>
+          <t>A 48966-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19835,10 +19845,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44752</v>
+        <v>45209</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19850,13 +19860,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I249" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19899,7 +19904,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 5941-2025</t>
+          <t>A 50304-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19909,14 +19914,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45695</v>
+        <v>45209</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19929,7 +19934,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0.6</v>
+        <v>17.9</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19972,7 +19977,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 29335-2022</t>
+          <t>A 35988-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19986,10 +19991,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44752</v>
+        <v>46266</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20001,13 +20006,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I251" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20050,7 +20050,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 44882-2022</t>
+          <t>A 38214-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20064,10 +20064,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>44841</v>
+        <v>45161</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20123,7 +20123,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 56460-2023</t>
+          <t>A 27540-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20137,10 +20137,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45243</v>
+        <v>45474</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20196,7 +20196,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 1783-2025</t>
+          <t>A 9695-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20210,10 +20210,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45671</v>
+        <v>44984</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20269,7 +20269,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 26178-2023</t>
+          <t>A 25962-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20283,10 +20283,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45091</v>
+        <v>45090</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.7</v>
+        <v>7.3</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20342,7 +20342,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 51577-2023</t>
+          <t>A 1904-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20356,10 +20356,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45222</v>
+        <v>44939</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20415,7 +20415,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 63029-2023</t>
+          <t>A 51577-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20429,10 +20429,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45272</v>
+        <v>45222</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20488,7 +20488,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 58284-2023</t>
+          <t>A 3830-2022</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45250</v>
+        <v>44587</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20561,7 +20561,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 27497-2024</t>
+          <t>A 17641-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20575,10 +20575,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45474</v>
+        <v>45035</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>2.2</v>
+        <v>7.3</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20634,7 +20634,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 48966-2023</t>
+          <t>A 37517-2026</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20648,10 +20648,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45209</v>
+        <v>46276</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20707,7 +20707,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 2405-2025</t>
+          <t>A 44882-2022</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20721,10 +20721,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45674</v>
+        <v>44841</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20780,7 +20780,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 27540-2024</t>
+          <t>A 37912-2026</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20794,10 +20794,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45474</v>
+        <v>46280</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 9773-2024</t>
+          <t>A 168-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20867,10 +20867,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45362</v>
+        <v>45659</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20926,7 +20926,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 57795-2022</t>
+          <t>A 49362-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20940,10 +20940,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44897</v>
+        <v>45595</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20999,7 +20999,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 50279-2023</t>
+          <t>A 22391-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21013,10 +21013,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45216</v>
+        <v>45446</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21072,7 +21072,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 33796-2023</t>
+          <t>A 27486-2024</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45133</v>
+        <v>45474</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21145,7 +21145,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 2090-2023</t>
+          <t>A 25958-2023</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21159,10 +21159,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>44939</v>
+        <v>45090</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21218,7 +21218,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 57161-2022</t>
+          <t>A 17458-2023</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21232,10 +21232,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>44895</v>
+        <v>45034</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21291,7 +21291,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 2086-2023</t>
+          <t>A 23469-2025</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21305,10 +21305,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>44939</v>
+        <v>45792</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21364,7 +21364,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 50304-2023</t>
+          <t>A 54669-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21374,14 +21374,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45209</v>
+        <v>45235</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>17.9</v>
+        <v>1</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21437,7 +21437,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 11126-2025</t>
+          <t>A 11460-2025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21451,10 +21451,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21510,7 +21510,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 37620-2023</t>
+          <t>A 26032-2025</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21524,10 +21524,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45159</v>
+        <v>45804</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 9695-2023</t>
+          <t>A 25589-2025</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21597,10 +21597,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>44984</v>
+        <v>45803</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21656,7 +21656,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 2399-2025</t>
+          <t>A 26020-2025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21666,14 +21666,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45672</v>
+        <v>45804</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21729,7 +21729,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 22699-2024</t>
+          <t>A 27523-2025</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21743,10 +21743,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45448</v>
+        <v>45813</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21802,7 +21802,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 20492-2024</t>
+          <t>A 15478-2025</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21816,10 +21816,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45435</v>
+        <v>45747</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21875,7 +21875,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 49362-2024</t>
+          <t>A 21146-2022</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21889,10 +21889,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>45595</v>
+        <v>44704</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21948,7 +21948,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 168-2025</t>
+          <t>A 28693-2025</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21962,10 +21962,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45659</v>
+        <v>45819</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>6.9</v>
+        <v>1.6</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -22021,7 +22021,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 25958-2023</t>
+          <t>A 29642-2025</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -22035,10 +22035,10 @@
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>45090</v>
+        <v>45825</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -22094,7 +22094,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 27486-2024</t>
+          <t>A 17270-2025</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -22108,10 +22108,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>45474</v>
+        <v>45756</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 22391-2024</t>
+          <t>A 12038-2025</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -22181,10 +22181,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>45446</v>
+        <v>45728</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -22240,7 +22240,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 11460-2025</t>
+          <t>A 32704-2025</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22254,10 +22254,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>45726</v>
+        <v>45839</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -22313,7 +22313,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 17458-2023</t>
+          <t>A 18285-2025</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22327,10 +22327,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45034</v>
+        <v>45762</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -22386,24 +22386,24 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>S 1016-2020</t>
+          <t>A 61602-2024</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>43957</v>
+        <v>45646</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -22459,7 +22459,7 @@
     <row r="285" ht="15" customHeight="1">
       <c r="A285" t="inlineStr">
         <is>
-          <t>S 2857-2024</t>
+          <t>S 1016-2020</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -22469,14 +22469,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D285" s="1" t="n">
-        <v>45496</v>
+        <v>43957</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         </is>
       </c>
       <c r="I285" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -22532,7 +22532,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>S 9957-2021</t>
+          <t>S 1259-2022</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -22542,14 +22542,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>44536</v>
+        <v>44627</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>26.1</v>
+        <v>0.7</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -22605,7 +22605,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>S 455-2023</t>
+          <t>S 1070-2022</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -22619,10 +22619,10 @@
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>44959</v>
+        <v>44613</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>14.9</v>
+        <v>46</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -22678,7 +22678,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>S 5219-2022</t>
+          <t>S 2857-2024</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -22688,14 +22688,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>44820</v>
+        <v>45496</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>22.7</v>
+        <v>2.5</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -22751,7 +22751,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>S 2907-2024</t>
+          <t>S 9957-2021</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -22765,10 +22765,10 @@
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>45503</v>
+        <v>44536</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>72.5</v>
+        <v>26.1</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -22824,7 +22824,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>S 1259-2022</t>
+          <t>S 455-2023</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -22834,14 +22834,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>44627</v>
+        <v>44959</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>0.7</v>
+        <v>14.9</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -22897,7 +22897,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>S 4069-2022</t>
+          <t>S 5219-2022</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -22911,10 +22911,10 @@
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>44757</v>
+        <v>44820</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>24.7</v>
+        <v>22.7</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -22970,7 +22970,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>S 1070-2022</t>
+          <t>S 2907-2024</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -22984,10 +22984,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>44613</v>
+        <v>45503</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>46</v>
+        <v>72.5</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -23043,7 +23043,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>S 2756-2024</t>
+          <t>S 4069-2022</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -23053,14 +23053,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Dikesrensning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>45484</v>
+        <v>44757</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>2.9</v>
+        <v>24.7</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -23116,7 +23116,7 @@
     <row r="294" ht="15" customHeight="1">
       <c r="A294" t="inlineStr">
         <is>
-          <t>S 856-2023</t>
+          <t>S 2756-2024</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -23126,14 +23126,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Dikesrensning</t>
         </is>
       </c>
       <c r="D294" s="1" t="n">
-        <v>44993</v>
+        <v>45484</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>20.8</v>
+        <v>2.9</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -23189,7 +23189,7 @@
     <row r="295" ht="15" customHeight="1">
       <c r="A295" t="inlineStr">
         <is>
-          <t>S 2633-2023</t>
+          <t>S 856-2023</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -23203,10 +23203,10 @@
         </is>
       </c>
       <c r="D295" s="1" t="n">
-        <v>45148</v>
+        <v>44993</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         </is>
       </c>
       <c r="I295" t="n">
-        <v>9</v>
+        <v>20.8</v>
       </c>
       <c r="J295" t="n">
         <v>0</v>
@@ -23262,7 +23262,7 @@
     <row r="296" ht="15" customHeight="1">
       <c r="A296" t="inlineStr">
         <is>
-          <t>S 293-2026</t>
+          <t>S 2633-2023</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -23276,10 +23276,10 @@
         </is>
       </c>
       <c r="D296" s="1" t="n">
-        <v>46057</v>
+        <v>45148</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="I296" t="n">
-        <v>40.7</v>
+        <v>9</v>
       </c>
       <c r="J296" t="n">
         <v>0</v>
@@ -23335,7 +23335,7 @@
     <row r="297" ht="15" customHeight="1">
       <c r="A297" t="inlineStr">
         <is>
-          <t>S 718-2026</t>
+          <t>S 293-2026</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -23349,10 +23349,10 @@
         </is>
       </c>
       <c r="D297" s="1" t="n">
-        <v>46093</v>
+        <v>46057</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>8.699999999999999</v>
+        <v>40.7</v>
       </c>
       <c r="J297" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
     <row r="298" ht="15" customHeight="1">
       <c r="A298" t="inlineStr">
         <is>
-          <t>S 755-2026</t>
+          <t>S 718-2026</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -23422,10 +23422,10 @@
         </is>
       </c>
       <c r="D298" s="1" t="n">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         </is>
       </c>
       <c r="I298" t="n">
-        <v>14.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J298" t="n">
         <v>0</v>
@@ -23481,7 +23481,7 @@
     <row r="299" ht="15" customHeight="1">
       <c r="A299" t="inlineStr">
         <is>
-          <t>S 1079-2026</t>
+          <t>S 755-2026</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -23495,10 +23495,10 @@
         </is>
       </c>
       <c r="D299" s="1" t="n">
-        <v>46129</v>
+        <v>46097</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         </is>
       </c>
       <c r="I299" t="n">
-        <v>11</v>
+        <v>14.3</v>
       </c>
       <c r="J299" t="n">
         <v>0</v>
@@ -23554,148 +23554,221 @@
     <row r="300" ht="15" customHeight="1">
       <c r="A300" t="inlineStr">
         <is>
+          <t>S 1079-2026</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D300" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="E300" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I300" t="n">
+        <v>11</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" t="n">
+        <v>0</v>
+      </c>
+      <c r="L300" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" t="n">
+        <v>0</v>
+      </c>
+      <c r="N300" t="n">
+        <v>0</v>
+      </c>
+      <c r="O300" t="n">
+        <v>0</v>
+      </c>
+      <c r="P300" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>0</v>
+      </c>
+      <c r="R300" t="n">
+        <v>0</v>
+      </c>
+      <c r="S300" t="n">
+        <v>0</v>
+      </c>
+      <c r="T300" t="n">
+        <v>0</v>
+      </c>
+      <c r="U300" t="n">
+        <v>0</v>
+      </c>
+      <c r="V300" s="2" t="inlineStr"/>
+    </row>
+    <row r="301" ht="15" customHeight="1">
+      <c r="A301" t="inlineStr">
+        <is>
           <t>S 1124-2026</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B301" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
+      <c r="C301" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D300" s="1" t="n">
+      <c r="D301" s="1" t="n">
         <v>46134</v>
       </c>
-      <c r="E300" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I300" t="n">
+      <c r="E301" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I301" t="n">
         <v>30</v>
       </c>
-      <c r="J300" t="n">
-        <v>0</v>
-      </c>
-      <c r="K300" t="n">
-        <v>0</v>
-      </c>
-      <c r="L300" t="n">
-        <v>0</v>
-      </c>
-      <c r="M300" t="n">
-        <v>0</v>
-      </c>
-      <c r="N300" t="n">
-        <v>0</v>
-      </c>
-      <c r="O300" t="n">
-        <v>0</v>
-      </c>
-      <c r="P300" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
-      <c r="R300" t="n">
-        <v>0</v>
-      </c>
-      <c r="S300" t="n">
-        <v>0</v>
-      </c>
-      <c r="T300" t="n">
-        <v>0</v>
-      </c>
-      <c r="U300" t="n">
-        <v>0</v>
-      </c>
-      <c r="V300" s="2" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" t="n">
+        <v>0</v>
+      </c>
+      <c r="M301" t="n">
+        <v>0</v>
+      </c>
+      <c r="N301" t="n">
+        <v>0</v>
+      </c>
+      <c r="O301" t="n">
+        <v>0</v>
+      </c>
+      <c r="P301" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>0</v>
+      </c>
+      <c r="R301" t="n">
+        <v>0</v>
+      </c>
+      <c r="S301" t="n">
+        <v>0</v>
+      </c>
+      <c r="T301" t="n">
+        <v>0</v>
+      </c>
+      <c r="U301" t="n">
+        <v>0</v>
+      </c>
+      <c r="V301" s="2" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
         <is>
           <t>S 1336-2026</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B302" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
+      <c r="C302" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D301" s="1" t="n">
+      <c r="D302" s="1" t="n">
         <v>46150</v>
       </c>
-      <c r="E301" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I301" t="n">
+      <c r="E302" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I302" t="n">
         <v>35.2</v>
       </c>
-      <c r="J301" t="n">
-        <v>0</v>
-      </c>
-      <c r="K301" t="n">
-        <v>0</v>
-      </c>
-      <c r="L301" t="n">
-        <v>0</v>
-      </c>
-      <c r="M301" t="n">
-        <v>0</v>
-      </c>
-      <c r="N301" t="n">
-        <v>0</v>
-      </c>
-      <c r="O301" t="n">
-        <v>0</v>
-      </c>
-      <c r="P301" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
-      <c r="R301" t="n">
-        <v>0</v>
-      </c>
-      <c r="S301" t="n">
-        <v>0</v>
-      </c>
-      <c r="T301" t="n">
-        <v>0</v>
-      </c>
-      <c r="U301" t="n">
-        <v>0</v>
-      </c>
-      <c r="V301" s="2" t="inlineStr"/>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0</v>
+      </c>
+      <c r="L302" t="n">
+        <v>0</v>
+      </c>
+      <c r="M302" t="n">
+        <v>0</v>
+      </c>
+      <c r="N302" t="n">
+        <v>0</v>
+      </c>
+      <c r="O302" t="n">
+        <v>0</v>
+      </c>
+      <c r="P302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>0</v>
+      </c>
+      <c r="R302" t="n">
+        <v>0</v>
+      </c>
+      <c r="S302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U302" t="n">
+        <v>0</v>
+      </c>
+      <c r="V302" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 39622-2023</t>
+          <t>A 5927-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45163</v>
+        <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1300,22 +1300,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>10.7</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1324,21 +1324,129 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Hussvala
+Ladusvala
+Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 5927-2023 artfynd.xlsx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 5927-2023 karta.png", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 5927-2023 georefererad karta.tif", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 5927-2023 FSC-klagomål.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 5927-2023 FSC-klagomål mail.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 5927-2023 tillsynsbegäran.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 5927-2023 tillsynsbegäran mail.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 39622-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Dvärghäxört
 Skogsödla
@@ -1346,107 +1454,107 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 39622-2023 artfynd.xlsx", "A 39622-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 39622-2023 karta.png", "A 39622-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 39622-2023 georefererad karta.tif", "A 39622-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 39622-2023 FSC-klagomål.docx", "A 39622-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 39622-2023 FSC-klagomål mail.docx", "A 39622-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 39622-2023 tillsynsbegäran.docx", "A 39622-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 39622-2023 tillsynsbegäran mail.docx", "A 39622-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 4112-2025</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45684</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>11.4</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>6</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>4</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Gröngöling
@@ -1454,140 +1562,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 4112-2025 artfynd.xlsx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 4112-2025 karta.png", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 4112-2025 georefererad karta.tif", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 4112-2025 FSC-klagomål.docx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 4112-2025 FSC-klagomål mail.docx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 4112-2025 tillsynsbegäran.docx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 4112-2025 tillsynsbegäran mail.docx", "A 4112-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 5927-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44963</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Hussvala
-Ladusvala
-Svart skogssnigel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 5927-2023 artfynd.xlsx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 5927-2023 karta.png", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 5927-2023 georefererad karta.tif", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 5927-2023 FSC-klagomål.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 5927-2023 FSC-klagomål mail.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 5927-2023 tillsynsbegäran.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 5927-2023 tillsynsbegäran mail.docx", "A 5927-2023")</f>
         <v/>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45945</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>46183</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45642</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22410-2024</t>
+          <t>A 1604-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45446</v>
+        <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2919,21 +2919,26 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -2944,10 +2949,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2956,39 +2961,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 22410-2024 artfynd.xlsx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 1604-2025 artfynd.xlsx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 22410-2024 karta.png", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 1604-2025 karta.png", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 22410-2024 georefererad karta.tif", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 1604-2025 georefererad karta.tif", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 22410-2024 FSC-klagomål.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 1604-2025 FSC-klagomål.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 22410-2024 FSC-klagomål mail.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 1604-2025 FSC-klagomål mail.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 22410-2024 tillsynsbegäran.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 1604-2025 tillsynsbegäran.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 22410-2024 tillsynsbegäran mail.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 1604-2025 tillsynsbegäran mail.docx", "A 1604-2025")</f>
         <v/>
       </c>
     </row>
@@ -3012,7 +3017,7 @@
         <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3117,7 +3122,7 @@
         <v>45980</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3222,7 +3227,7 @@
         <v>46076</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3310,7 +3315,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1604-2025</t>
+          <t>A 15068-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3324,10 +3329,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45670</v>
+        <v>45015</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3339,25 +3344,20 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>9.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3385,42 +3385,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 1604-2025 artfynd.xlsx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 15068-2023 artfynd.xlsx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 1604-2025 karta.png", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 15068-2023 karta.png", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 1604-2025 georefererad karta.tif", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 15068-2023 georefererad karta.tif", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 1604-2025 FSC-klagomål.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 15068-2023 FSC-klagomål.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 1604-2025 FSC-klagomål mail.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 15068-2023 FSC-klagomål mail.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 1604-2025 tillsynsbegäran.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 15068-2023 tillsynsbegäran.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 1604-2025 tillsynsbegäran mail.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 15068-2023 tillsynsbegäran mail.docx", "A 15068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15068-2023</t>
+          <t>A 22410-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45015</v>
+        <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3450,13 +3450,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>9.9</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3486,39 +3486,39 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 15068-2023 artfynd.xlsx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 22410-2024 artfynd.xlsx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 15068-2023 karta.png", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 22410-2024 karta.png", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 15068-2023 georefererad karta.tif", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 22410-2024 georefererad karta.tif", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 15068-2023 FSC-klagomål.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 22410-2024 FSC-klagomål.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 15068-2023 FSC-klagomål mail.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 22410-2024 FSC-klagomål mail.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 15068-2023 tillsynsbegäran.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 22410-2024 tillsynsbegäran.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 15068-2023 tillsynsbegäran mail.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 22410-2024 tillsynsbegäran mail.docx", "A 22410-2024")</f>
         <v/>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
         <v>45784</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S 2731-2022</t>
+          <t>S 2910-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3640,14 +3640,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44704</v>
+        <v>45503</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3659,13 +3659,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>24.7</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3701,46 +3696,50 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2731-2022 artfynd.xlsx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2910-2024 artfynd.xlsx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2731-2022 karta.png", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2910-2024 karta.png", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2731-2022 georefererad karta.tif", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2910-2024 georefererad karta.tif", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2731-2022 FSC-klagomål.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2910-2024 FSC-klagomål.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2731-2022 FSC-klagomål mail.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2910-2024 FSC-klagomål mail.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2731-2022 tillsynsbegäran.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2910-2024 tillsynsbegäran.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2731-2022 tillsynsbegäran mail.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2910-2024 tillsynsbegäran mail.docx", "S 2910-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/S 2910-2024 prioriterade fågelarter.docx", "S 2910-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S 2910-2024</t>
+          <t>S 4056-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3750,14 +3749,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45503</v>
+        <v>45243</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3770,7 +3769,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.4</v>
+        <v>7.1</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3810,46 +3809,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2910-2024 artfynd.xlsx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 4056-2023 artfynd.xlsx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2910-2024 karta.png", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 4056-2023 karta.png", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2910-2024 georefererad karta.tif", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 4056-2023 georefererad karta.tif", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2910-2024 FSC-klagomål.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 4056-2023 FSC-klagomål.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2910-2024 FSC-klagomål mail.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 4056-2023 FSC-klagomål mail.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2910-2024 tillsynsbegäran.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 4056-2023 tillsynsbegäran.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2910-2024 tillsynsbegäran mail.docx", "S 2910-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/S 2910-2024 prioriterade fågelarter.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 4056-2023 tillsynsbegäran mail.docx", "S 4056-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S 4056-2023</t>
+          <t>S 2731-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3863,10 +3858,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45243</v>
+        <v>44704</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3878,8 +3873,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>7.1</v>
+        <v>24.7</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3915,39 +3915,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 4056-2023 artfynd.xlsx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2731-2022 artfynd.xlsx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 4056-2023 karta.png", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2731-2022 karta.png", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 4056-2023 georefererad karta.tif", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2731-2022 georefererad karta.tif", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 4056-2023 FSC-klagomål.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2731-2022 FSC-klagomål.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 4056-2023 FSC-klagomål mail.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2731-2022 FSC-klagomål mail.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 4056-2023 tillsynsbegäran.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2731-2022 tillsynsbegäran.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 4056-2023 tillsynsbegäran mail.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2731-2022 tillsynsbegäran mail.docx", "S 2731-2022")</f>
         <v/>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44477</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44752</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9773-2024</t>
+          <t>A 38556-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45362</v>
+        <v>44813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5213,7 +5213,7 @@
         <v>44543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62180-2022</t>
+          <t>A 12139-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44915</v>
+        <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5298,13 +5298,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>7.5</v>
+        <v>0.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5347,7 +5342,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26837-2022</t>
+          <t>A 45063-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5361,10 +5356,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44740</v>
+        <v>44841</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5377,7 +5372,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5420,7 +5415,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9748-2024</t>
+          <t>A 6020-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5434,10 +5429,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45362</v>
+        <v>44599</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5450,7 +5445,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5493,7 +5488,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12139-2022</t>
+          <t>A 19390-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5507,10 +5502,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44636</v>
+        <v>45048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5523,7 +5518,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5566,7 +5561,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38556-2022</t>
+          <t>A 73830-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5580,10 +5575,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44813</v>
+        <v>44552</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5596,7 +5591,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5639,7 +5634,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 29334-2022</t>
+          <t>A 44814-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5653,10 +5648,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44752</v>
+        <v>44841</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5668,13 +5663,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5717,7 +5707,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 27497-2024</t>
+          <t>A 9748-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5731,10 +5721,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45474</v>
+        <v>45362</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5790,7 +5780,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 24154-2023</t>
+          <t>A 52876-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5804,10 +5794,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45079</v>
+        <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5820,7 +5810,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5863,7 +5853,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45063-2022</t>
+          <t>A 10379-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5877,10 +5867,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44841</v>
+        <v>45365</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5893,7 +5883,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5936,7 +5926,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 21023-2024</t>
+          <t>A 23740-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5950,10 +5940,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45439</v>
+        <v>45077</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5966,7 +5956,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6009,7 +5999,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26178-2023</t>
+          <t>A 72261-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6023,10 +6013,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45091</v>
+        <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6082,7 +6072,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26179-2023</t>
+          <t>A 17737-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6096,10 +6086,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45091</v>
+        <v>45037</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6112,7 +6102,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6155,7 +6145,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 54646-2023</t>
+          <t>A 9359-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6169,10 +6159,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45235</v>
+        <v>45715</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6185,7 +6175,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6228,7 +6218,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 21910-2024</t>
+          <t>A 47890-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6242,10 +6232,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45443</v>
+        <v>44855</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6258,7 +6248,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6301,7 +6291,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 21152-2022</t>
+          <t>A 23898-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6315,10 +6305,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44704</v>
+        <v>45078</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6331,7 +6321,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6374,7 +6364,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58130-2022</t>
+          <t>A 31704-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6388,10 +6378,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44900</v>
+        <v>45117</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6404,7 +6394,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>23.2</v>
+        <v>6.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6447,7 +6437,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11121-2025</t>
+          <t>A 14912-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6457,14 +6447,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45723</v>
+        <v>45398</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6477,7 +6467,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6520,7 +6510,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1492-2024</t>
+          <t>A 25589-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6534,10 +6524,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45305</v>
+        <v>45803</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6550,7 +6540,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6593,7 +6583,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1493-2024</t>
+          <t>A 26032-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6607,10 +6597,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45305</v>
+        <v>45804</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6623,7 +6613,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6666,7 +6656,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 9573-2025</t>
+          <t>A 26020-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6680,10 +6670,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45715</v>
+        <v>45804</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6696,7 +6686,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6739,7 +6729,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19643-2024</t>
+          <t>A 54667-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6753,10 +6743,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45432</v>
+        <v>45235</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6768,13 +6758,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6817,7 +6802,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22406-2024</t>
+          <t>A 1225-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6831,10 +6816,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45446</v>
+        <v>46031</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6847,7 +6832,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6890,7 +6875,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 55049-2023</t>
+          <t>A 31399-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6904,10 +6889,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45237</v>
+        <v>45833</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6920,7 +6905,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6963,7 +6948,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10379-2024</t>
+          <t>A 27523-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6977,10 +6962,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45365</v>
+        <v>45813</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6993,7 +6978,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7036,7 +7021,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54661-2023</t>
+          <t>A 7915-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7050,10 +7035,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45235</v>
+        <v>45707</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7066,7 +7051,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7109,7 +7094,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11605-2023</t>
+          <t>A 15478-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7123,10 +7108,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44994</v>
+        <v>45747</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7139,7 +7124,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7182,7 +7167,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26058-2024</t>
+          <t>A 21146-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7196,10 +7181,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45468</v>
+        <v>44704</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7212,7 +7197,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>7.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7255,7 +7240,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 47871-2022</t>
+          <t>A 25963-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7269,10 +7254,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44855</v>
+        <v>45090</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7285,7 +7270,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7328,7 +7313,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 44880-2022</t>
+          <t>A 40814-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7342,10 +7327,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44841</v>
+        <v>45171</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7358,7 +7343,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7401,7 +7386,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 57208-2022</t>
+          <t>A 32855-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7415,10 +7400,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44895</v>
+        <v>45124</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7431,7 +7416,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7474,7 +7459,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 31399-2025</t>
+          <t>A 1492-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7488,10 +7473,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45833</v>
+        <v>45305</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7504,7 +7489,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7547,7 +7532,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 64091-2023</t>
+          <t>A 1493-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7561,10 +7546,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45279</v>
+        <v>45305</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7577,7 +7562,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7620,7 +7605,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 38897-2025</t>
+          <t>A 21910-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7634,10 +7619,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45887</v>
+        <v>45443</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7650,7 +7635,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7693,7 +7678,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7915-2025</t>
+          <t>A 28693-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7707,10 +7692,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45707</v>
+        <v>45819</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7723,7 +7708,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7766,7 +7751,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 40814-2023</t>
+          <t>A 29642-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7780,10 +7765,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45171</v>
+        <v>45825</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7796,7 +7781,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7839,7 +7824,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40017-2023</t>
+          <t>A 57703-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7853,10 +7838,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45168</v>
+        <v>44897</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7869,7 +7854,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7912,7 +7897,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37501-2024</t>
+          <t>A 26058-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7926,10 +7911,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45541</v>
+        <v>45468</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7985,7 +7970,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33796-2023</t>
+          <t>A 41912-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7999,10 +7984,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45133</v>
+        <v>45903</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8058,7 +8043,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2088-2023</t>
+          <t>A 41926-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8072,10 +8057,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44939</v>
+        <v>45903</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8088,7 +8073,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8131,7 +8116,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2092-2023</t>
+          <t>A 63783-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8145,10 +8130,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44939</v>
+        <v>45278</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8161,7 +8146,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8204,7 +8189,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 52528-2021</t>
+          <t>A 1397-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8218,10 +8203,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44466</v>
+        <v>44936</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8234,7 +8219,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8277,7 +8262,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 15987-2025</t>
+          <t>A 42708-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8291,10 +8276,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45749</v>
+        <v>45908</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8307,7 +8292,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6</v>
+        <v>0.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8350,7 +8335,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13283-2026</t>
+          <t>A 42728-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8364,10 +8349,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46093</v>
+        <v>45908</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8380,7 +8365,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8423,7 +8408,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 41912-2025</t>
+          <t>A 12038-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8437,10 +8422,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45903</v>
+        <v>45728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8453,7 +8438,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8496,7 +8481,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 41926-2025</t>
+          <t>A 36543-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8510,10 +8495,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45903</v>
+        <v>44804</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8526,7 +8511,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8569,7 +8554,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 42728-2025</t>
+          <t>A 13068-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8583,10 +8568,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45908</v>
+        <v>45002</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8599,7 +8584,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8642,7 +8627,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14734-2026</t>
+          <t>A 13797-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8656,10 +8641,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46101</v>
+        <v>45737</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8672,7 +8657,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8715,7 +8700,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42708-2025</t>
+          <t>A 17270-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8729,10 +8714,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45908</v>
+        <v>45756</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8745,7 +8730,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8788,7 +8773,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 36838-2024</t>
+          <t>A 43990-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8802,10 +8787,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45538</v>
+        <v>45915</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8818,7 +8803,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8861,7 +8846,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34279-2023</t>
+          <t>A 5954-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8875,10 +8860,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45138</v>
+        <v>45695</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8891,7 +8876,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8934,7 +8919,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 15236-2026</t>
+          <t>A 2537-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8948,10 +8933,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46105</v>
+        <v>46037</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8964,7 +8949,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9007,7 +8992,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 15240-2026</t>
+          <t>A 32704-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9021,10 +9006,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46105</v>
+        <v>45839</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9037,7 +9022,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9080,7 +9065,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 15108-2026</t>
+          <t>A 19643-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9094,10 +9079,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46105</v>
+        <v>45432</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9109,8 +9094,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9153,7 +9143,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 13797-2025</t>
+          <t>A 44897-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9167,10 +9157,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45737</v>
+        <v>45918</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9183,7 +9173,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9226,7 +9216,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 43990-2025</t>
+          <t>A 44890-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9240,10 +9230,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45915</v>
+        <v>45918</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9256,7 +9246,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9299,7 +9289,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 44890-2025</t>
+          <t>A 23692-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9313,10 +9303,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45918</v>
+        <v>45077</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9329,7 +9319,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9372,7 +9362,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 57795-2022</t>
+          <t>A 2474-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9386,10 +9376,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44897</v>
+        <v>46037</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9402,7 +9392,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>8.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9445,7 +9435,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 1783-2025</t>
+          <t>A 37501-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9459,10 +9449,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45671</v>
+        <v>45541</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9475,7 +9465,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9518,7 +9508,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 50279-2023</t>
+          <t>A 44880-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9532,10 +9522,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45216</v>
+        <v>44841</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9548,7 +9538,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9591,7 +9581,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 16363-2026</t>
+          <t>A 171-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9605,10 +9595,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46111</v>
+        <v>45659</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9621,7 +9611,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9664,7 +9654,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 16283-2026</t>
+          <t>A 18285-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9678,10 +9668,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46111</v>
+        <v>45762</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9694,7 +9684,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9737,7 +9727,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 73830-2021</t>
+          <t>A 61602-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9751,10 +9741,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44552</v>
+        <v>45646</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9767,7 +9757,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9810,7 +9800,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 6020-2022</t>
+          <t>A 9691-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9824,10 +9814,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44599</v>
+        <v>44984</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9840,7 +9830,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9883,7 +9873,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 44897-2025</t>
+          <t>A 48672-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9897,10 +9887,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45918</v>
+        <v>45936</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9913,7 +9903,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9956,7 +9946,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 17608-2026</t>
+          <t>A 17641-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9970,10 +9960,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46121</v>
+        <v>45035</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9986,7 +9976,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>7.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10029,7 +10019,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 13068-2023</t>
+          <t>A 3934-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10043,10 +10033,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45002</v>
+        <v>46043</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10059,7 +10049,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10102,7 +10092,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 48672-2025</t>
+          <t>A 4989-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10116,10 +10106,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45936</v>
+        <v>46049</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10132,7 +10122,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10175,7 +10165,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 17737-2023</t>
+          <t>A 44925-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10189,10 +10179,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45037</v>
+        <v>45918</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10205,7 +10195,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10248,7 +10238,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 981-2023</t>
+          <t>A 5002-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10262,10 +10252,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44935</v>
+        <v>46049</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10278,7 +10268,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10321,7 +10311,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 44925-2025</t>
+          <t>A 39650-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10335,10 +10325,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45918</v>
+        <v>45167</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10351,7 +10341,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10411,7 +10401,7 @@
         <v>45867</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10467,7 +10457,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 30136-2022</t>
+          <t>A 24154-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10481,10 +10471,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44757</v>
+        <v>45079</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10496,13 +10486,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10545,7 +10530,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 20492-2024</t>
+          <t>A 65211-2021</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10559,10 +10544,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45435</v>
+        <v>44515</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10575,7 +10560,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10618,7 +10603,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 22975-2023</t>
+          <t>A 38897-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10632,10 +10617,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45072</v>
+        <v>45887</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10648,7 +10633,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10691,7 +10676,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 35490-2025</t>
+          <t>A 24765-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10705,10 +10690,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45855</v>
+        <v>45084</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10721,7 +10706,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10781,7 +10766,7 @@
         <v>45958</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10837,7 +10822,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 44864-2025</t>
+          <t>A 7242-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10851,10 +10836,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45918</v>
+        <v>46058</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10867,7 +10852,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10910,7 +10895,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 43992-2025</t>
+          <t>A 8024-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10924,10 +10909,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45915</v>
+        <v>46063</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10939,8 +10924,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10983,7 +10973,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 13611-2025</t>
+          <t>A 9105-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10997,10 +10987,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45736</v>
+        <v>46069</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11013,7 +11003,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11056,7 +11046,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 38928-2024</t>
+          <t>A 9127-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11070,10 +11060,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45548</v>
+        <v>46069</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11086,7 +11076,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11129,7 +11119,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 63783-2023</t>
+          <t>A 9125-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11143,10 +11133,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45278</v>
+        <v>46069</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11159,7 +11149,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11202,7 +11192,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 9359-2025</t>
+          <t>A 56455-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11216,10 +11206,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45715</v>
+        <v>45975</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11275,7 +11265,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 3205-2025</t>
+          <t>A 9292-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11289,10 +11279,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45679</v>
+        <v>46070</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11304,13 +11294,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>6.7</v>
+        <v>1.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11353,7 +11338,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 52876-2024</t>
+          <t>A 57343-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11367,10 +11352,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45610</v>
+        <v>45980</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11383,7 +11368,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11426,7 +11411,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 32855-2023</t>
+          <t>A 57790-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11440,10 +11425,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45124</v>
+        <v>45981</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11456,7 +11441,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11499,7 +11484,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3864-2023</t>
+          <t>A 42177-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11513,10 +11498,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44951</v>
+        <v>45178</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11529,7 +11514,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.2</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11572,7 +11557,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 56455-2025</t>
+          <t>A 58347-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11586,10 +11571,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45975</v>
+        <v>45985</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11602,7 +11587,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11645,7 +11630,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 42177-2023</t>
+          <t>A 28221-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11659,10 +11644,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45178</v>
+        <v>45099</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11675,7 +11660,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.5</v>
+        <v>6.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11718,7 +11703,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 57343-2025</t>
+          <t>A 10473-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11732,10 +11717,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45980</v>
+        <v>46077</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11748,7 +11733,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11791,7 +11776,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 30638-2023</t>
+          <t>A 11605-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11805,10 +11790,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45112</v>
+        <v>44994</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11821,7 +11806,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11864,7 +11849,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 57790-2025</t>
+          <t>A 23693-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11878,10 +11863,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45981</v>
+        <v>45077</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11894,7 +11879,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11937,7 +11922,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 58284-2023</t>
+          <t>A 10466-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11951,10 +11936,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45250</v>
+        <v>46077</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11967,7 +11952,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12010,7 +11995,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 2086-2023</t>
+          <t>A 10480-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12024,10 +12009,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44939</v>
+        <v>46077</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12040,7 +12025,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12083,7 +12068,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 58347-2025</t>
+          <t>A 45192-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12097,10 +12082,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45985</v>
+        <v>44844</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12113,7 +12098,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12156,7 +12141,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 2359-2023</t>
+          <t>A 60789-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12170,10 +12155,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44942</v>
+        <v>45999</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12186,7 +12171,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12229,7 +12214,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 35168-2025</t>
+          <t>A 9573-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12243,10 +12228,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45852</v>
+        <v>45715</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12259,7 +12244,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12302,7 +12287,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 28221-2023</t>
+          <t>A 13283-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12316,10 +12301,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45099</v>
+        <v>46093</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12332,7 +12317,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12375,7 +12360,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 171-2025</t>
+          <t>A 22975-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12389,10 +12374,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45659</v>
+        <v>45072</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12405,7 +12390,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12448,7 +12433,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 20671-2026</t>
+          <t>A 52243-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12462,10 +12447,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46141</v>
+        <v>45953</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12478,7 +12463,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12521,7 +12506,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 60789-2025</t>
+          <t>A 53163-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12535,10 +12520,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45999</v>
+        <v>45958</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12551,7 +12536,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12594,7 +12579,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 57161-2022</t>
+          <t>A 52246-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12608,10 +12593,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44895</v>
+        <v>45953</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12624,7 +12609,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12667,7 +12652,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 45192-2022</t>
+          <t>A 14430-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12681,10 +12666,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44844</v>
+        <v>45012</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12697,7 +12682,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12740,7 +12725,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 27967-2024</t>
+          <t>A 64091-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12754,10 +12739,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45476</v>
+        <v>45279</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12770,7 +12755,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12813,7 +12798,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 36543-2022</t>
+          <t>A 14734-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12827,10 +12812,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44804</v>
+        <v>46101</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12843,7 +12828,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12886,7 +12871,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 5941-2025</t>
+          <t>A 25962-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12900,10 +12885,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45695</v>
+        <v>45090</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12916,7 +12901,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12959,7 +12944,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 40190-2022</t>
+          <t>A 15240-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12973,10 +12958,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44820</v>
+        <v>46105</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12989,7 +12974,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13032,7 +13017,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 44814-2022</t>
+          <t>A 30136-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13046,10 +13031,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44841</v>
+        <v>44757</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13061,8 +13046,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13105,7 +13095,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 47890-2022</t>
+          <t>A 38214-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13119,10 +13109,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44855</v>
+        <v>45161</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13135,7 +13125,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13178,7 +13168,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 22550-2026</t>
+          <t>A 15236-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13192,10 +13182,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46155</v>
+        <v>46105</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13208,7 +13198,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13251,7 +13241,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 22552-2026</t>
+          <t>A 15108-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13265,10 +13255,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46155</v>
+        <v>46105</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13281,7 +13271,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13324,7 +13314,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 1397-2023</t>
+          <t>A 23739-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13338,10 +13328,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44936</v>
+        <v>45077</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13354,7 +13344,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13397,7 +13387,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 34631-2025</t>
+          <t>A 16363-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13411,10 +13401,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45848</v>
+        <v>46111</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13427,7 +13417,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13470,7 +13460,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 52243-2025</t>
+          <t>A 16283-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13484,10 +13474,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45953</v>
+        <v>46111</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13500,7 +13490,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13543,7 +13533,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 53163-2025</t>
+          <t>A 34591-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13557,10 +13547,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45958</v>
+        <v>45140</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13573,7 +13563,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13616,7 +13606,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 52246-2025</t>
+          <t>A 17608-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13630,10 +13620,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45953</v>
+        <v>46121</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13646,7 +13636,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13689,7 +13679,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 23693-2023</t>
+          <t>A 9559-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13703,10 +13693,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45077</v>
+        <v>44617</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13719,7 +13709,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13762,7 +13752,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 23990-2023</t>
+          <t>A 31925-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13776,10 +13766,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45078</v>
+        <v>45510</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13792,7 +13782,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13835,7 +13825,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 34591-2023</t>
+          <t>A 30638-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13849,10 +13839,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45140</v>
+        <v>45112</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13865,7 +13855,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13908,7 +13898,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 52372-2021</t>
+          <t>A 2088-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13922,10 +13912,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44465</v>
+        <v>44939</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13938,7 +13928,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13981,7 +13971,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 11126-2025</t>
+          <t>A 35490-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13995,10 +13985,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45723</v>
+        <v>45855</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14011,7 +14001,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14054,7 +14044,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 1225-2026</t>
+          <t>A 13611-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14068,10 +14058,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46031</v>
+        <v>45736</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14084,7 +14074,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.6</v>
+        <v>2.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14127,7 +14117,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 2474-2026</t>
+          <t>A 981-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14141,10 +14131,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46037</v>
+        <v>44935</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14157,7 +14147,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>8.6</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14200,7 +14190,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 54667-2023</t>
+          <t>A 44864-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14214,10 +14204,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45235</v>
+        <v>45918</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14230,7 +14220,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14273,7 +14263,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 2537-2026</t>
+          <t>A 43992-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14287,10 +14277,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46037</v>
+        <v>45915</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14303,7 +14293,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14346,7 +14336,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 3934-2026</t>
+          <t>A 52528-2021</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14360,10 +14350,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46043</v>
+        <v>44466</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14376,7 +14366,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14419,7 +14409,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 31925-2024</t>
+          <t>A 3205-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14433,10 +14423,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45510</v>
+        <v>45679</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14448,8 +14438,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>2.9</v>
+        <v>6.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14492,7 +14487,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 53676-2025</t>
+          <t>A 36838-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14506,10 +14501,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45960</v>
+        <v>45538</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14522,7 +14517,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14565,7 +14560,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 44846-2025</t>
+          <t>A 20671-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14579,10 +14574,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45918</v>
+        <v>46141</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14595,7 +14590,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14638,7 +14633,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 57703-2022</t>
+          <t>A 1904-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14652,10 +14647,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44897</v>
+        <v>44939</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14668,7 +14663,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14711,7 +14706,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 5002-2026</t>
+          <t>A 35168-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14725,10 +14720,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46049</v>
+        <v>45852</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14741,7 +14736,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14784,7 +14779,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 2399-2025</t>
+          <t>A 8204-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14794,14 +14789,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45672</v>
+        <v>44971</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14814,7 +14809,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14857,7 +14852,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 29335-2022</t>
+          <t>A 11121-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14871,10 +14866,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44752</v>
+        <v>45723</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14886,13 +14881,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14935,7 +14925,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 22699-2024</t>
+          <t>A 3830-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14949,10 +14939,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45448</v>
+        <v>44587</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14965,7 +14955,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15008,7 +14998,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 4989-2026</t>
+          <t>A 21152-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15022,10 +15012,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46049</v>
+        <v>44704</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15038,7 +15028,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15081,7 +15071,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 2090-2023</t>
+          <t>A 58130-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15095,10 +15085,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44939</v>
+        <v>44900</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15111,7 +15101,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>23.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15154,7 +15144,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 25965-2023</t>
+          <t>A 2359-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15168,10 +15158,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45090</v>
+        <v>44942</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15184,7 +15174,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15227,7 +15217,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 25501-2026</t>
+          <t>A 22550-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15241,10 +15231,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46177</v>
+        <v>46155</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15257,7 +15247,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15300,7 +15290,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 25778-2026</t>
+          <t>A 22552-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15314,10 +15304,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46178</v>
+        <v>46155</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15330,7 +15320,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15373,7 +15363,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 25789-2026</t>
+          <t>A 55049-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15387,10 +15377,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46178</v>
+        <v>45237</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15403,7 +15393,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15446,7 +15436,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 25674-2026</t>
+          <t>A 15987-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15460,10 +15450,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46178</v>
+        <v>45749</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15476,7 +15466,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15519,7 +15509,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 25699-2026</t>
+          <t>A 57208-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15533,10 +15523,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46178</v>
+        <v>44895</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15549,7 +15539,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15592,7 +15582,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 25963-2023</t>
+          <t>A 34631-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15606,10 +15596,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45090</v>
+        <v>45848</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15622,7 +15612,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15665,7 +15655,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 25765-2026</t>
+          <t>A 3864-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15679,10 +15669,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46178</v>
+        <v>44951</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15695,7 +15685,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15738,7 +15728,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 7242-2026</t>
+          <t>A 25965-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15752,10 +15742,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46058</v>
+        <v>45090</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15768,7 +15758,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15811,7 +15801,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 19390-2023</t>
+          <t>A 38928-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15825,10 +15815,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45048</v>
+        <v>45548</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15841,7 +15831,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15884,7 +15874,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 25772-2026</t>
+          <t>A 7707-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15898,10 +15888,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46178</v>
+        <v>45349</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15914,7 +15904,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15957,7 +15947,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 25912-2026</t>
+          <t>A 14254-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15971,10 +15961,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46178</v>
+        <v>45009</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16030,7 +16020,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 25780-2026</t>
+          <t>A 53676-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16044,10 +16034,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46178</v>
+        <v>45960</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16060,7 +16050,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16103,7 +16093,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 25794-2026</t>
+          <t>A 44846-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16117,10 +16107,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46178</v>
+        <v>45918</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16133,7 +16123,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16176,7 +16166,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 8204-2023</t>
+          <t>A 25674-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16190,10 +16180,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44971</v>
+        <v>46178</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16206,7 +16196,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16249,7 +16239,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 26580-2026</t>
+          <t>A 25699-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16263,10 +16253,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16279,7 +16269,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16322,7 +16312,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 26597-2026</t>
+          <t>A 25772-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16336,10 +16326,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16352,7 +16342,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16395,7 +16385,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 26564-2026</t>
+          <t>A 25778-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16409,10 +16399,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16425,7 +16415,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16468,7 +16458,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 26596-2026</t>
+          <t>A 25789-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16482,10 +16472,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16498,7 +16488,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16541,7 +16531,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 24765-2023</t>
+          <t>A 25912-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16555,10 +16545,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45084</v>
+        <v>46178</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16571,7 +16561,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16614,7 +16604,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 8024-2026</t>
+          <t>A 25794-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16628,10 +16618,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46063</v>
+        <v>46178</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16643,13 +16633,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16692,7 +16677,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 26583-2026</t>
+          <t>A 25780-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16706,10 +16691,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16722,7 +16707,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>8.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16765,7 +16750,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 26594-2026</t>
+          <t>A 25501-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16779,10 +16764,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46183</v>
+        <v>46177</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16795,7 +16780,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16838,7 +16823,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 26578-2026</t>
+          <t>A 25765-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16852,10 +16837,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16911,7 +16896,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 26593-2026</t>
+          <t>A 47871-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16925,10 +16910,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46183</v>
+        <v>44855</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16941,7 +16926,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16984,7 +16969,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 9292-2026</t>
+          <t>A 40190-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16998,10 +16983,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46070</v>
+        <v>44820</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17014,7 +16999,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17057,7 +17042,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 9125-2026</t>
+          <t>A 26578-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17071,10 +17056,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46069</v>
+        <v>46183</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17087,7 +17072,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17130,7 +17115,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 9105-2026</t>
+          <t>A 26580-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17144,10 +17129,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46069</v>
+        <v>46183</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17160,7 +17145,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17203,7 +17188,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 9127-2026</t>
+          <t>A 26597-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17217,10 +17202,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46069</v>
+        <v>46183</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17233,7 +17218,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17276,7 +17261,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 10466-2026</t>
+          <t>A 26564-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17290,10 +17275,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46077</v>
+        <v>46183</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17306,7 +17291,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17349,7 +17334,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 10473-2026</t>
+          <t>A 26593-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17363,10 +17348,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46077</v>
+        <v>46183</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17379,7 +17364,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17422,7 +17407,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 10480-2026</t>
+          <t>A 26583-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17436,10 +17421,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46077</v>
+        <v>46183</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17452,7 +17437,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17495,7 +17480,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 27146-2026</t>
+          <t>A 26594-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17509,10 +17494,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46188</v>
+        <v>46183</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17525,7 +17510,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17568,7 +17553,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 65211-2021</t>
+          <t>A 26596-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17582,10 +17567,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44515</v>
+        <v>46183</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17598,7 +17583,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17641,7 +17626,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 9691-2023</t>
+          <t>A 27146-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17655,10 +17640,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44984</v>
+        <v>46188</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17671,7 +17656,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17714,7 +17699,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 39650-2023</t>
+          <t>A 40017-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17728,10 +17713,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45167</v>
+        <v>45168</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17744,7 +17729,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17787,7 +17772,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 63029-2023</t>
+          <t>A 34279-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17801,10 +17786,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45272</v>
+        <v>45138</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17817,7 +17802,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17860,7 +17845,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 14430-2023</t>
+          <t>A 54661-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17874,10 +17859,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45012</v>
+        <v>45235</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17890,7 +17875,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17933,7 +17918,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 23692-2023</t>
+          <t>A 54646-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17947,10 +17932,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45077</v>
+        <v>45235</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17963,7 +17948,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18006,7 +17991,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 23739-2023</t>
+          <t>A 2092-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18020,10 +18005,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45077</v>
+        <v>44939</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18036,7 +18021,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18079,7 +18064,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 23740-2023</t>
+          <t>A 21023-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18093,10 +18078,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45077</v>
+        <v>45439</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18109,7 +18094,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18152,7 +18137,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 14912-2024</t>
+          <t>A 62180-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18162,14 +18147,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45398</v>
+        <v>44915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18181,8 +18166,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>0.6</v>
+        <v>7.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18225,7 +18215,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 1935-2024</t>
+          <t>A 29401-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18239,10 +18229,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45308</v>
+        <v>46203</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18255,7 +18245,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18298,7 +18288,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 72261-2021</t>
+          <t>A 29530-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18312,10 +18302,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44545</v>
+        <v>46203</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18328,7 +18318,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18371,7 +18361,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 23898-2023</t>
+          <t>A 23990-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18388,7 +18378,7 @@
         <v>45078</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18401,7 +18391,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18444,7 +18434,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 29401-2026</t>
+          <t>A 29528-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18461,7 +18451,7 @@
         <v>46203</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18474,7 +18464,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18517,7 +18507,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 14254-2023</t>
+          <t>A 29529-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18531,10 +18521,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45009</v>
+        <v>46203</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18547,7 +18537,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18590,7 +18580,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 37620-2023</t>
+          <t>A 1935-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18604,10 +18594,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45159</v>
+        <v>45308</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18620,7 +18610,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18663,7 +18653,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 29528-2026</t>
+          <t>A 52372-2021</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18677,10 +18667,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46203</v>
+        <v>44465</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18693,7 +18683,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18736,7 +18726,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 29530-2026</t>
+          <t>A 22406-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18750,10 +18740,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46203</v>
+        <v>45446</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18766,7 +18756,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18809,7 +18799,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 29529-2026</t>
+          <t>A 26179-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18823,10 +18813,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46203</v>
+        <v>45091</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18839,7 +18829,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18882,7 +18872,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 31704-2023</t>
+          <t>A 27967-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18896,10 +18886,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45117</v>
+        <v>45476</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18912,7 +18902,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>6.7</v>
+        <v>0.4</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18955,7 +18945,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 7707-2024</t>
+          <t>A 26837-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18969,10 +18959,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45349</v>
+        <v>44740</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18985,7 +18975,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19028,7 +19018,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 56460-2023</t>
+          <t>A 25967-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19042,10 +19032,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45243</v>
+        <v>45090</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19058,7 +19048,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19101,7 +19091,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 5954-2025</t>
+          <t>A 29334-2022</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19115,10 +19105,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45695</v>
+        <v>44752</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19130,8 +19120,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19174,7 +19169,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 2405-2025</t>
+          <t>A 5941-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19188,10 +19183,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45674</v>
+        <v>45695</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19204,7 +19199,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19247,7 +19242,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 25967-2023</t>
+          <t>A 34919-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19261,10 +19256,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45090</v>
+        <v>46259</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19277,7 +19272,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19320,7 +19315,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 9559-2022</t>
+          <t>A 34770-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19334,10 +19329,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44617</v>
+        <v>46258</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19350,7 +19345,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19393,7 +19388,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 34770-2026</t>
+          <t>A 33183-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19407,10 +19402,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46258</v>
+        <v>46245</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19423,7 +19418,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19466,7 +19461,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 33183-2026</t>
+          <t>A 29335-2022</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19480,10 +19475,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46245</v>
+        <v>44752</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19495,8 +19490,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I244" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19539,7 +19539,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 34919-2026</t>
+          <t>A 33180-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19553,10 +19553,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46259</v>
+        <v>46245</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19612,7 +19612,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 33182-2026</t>
+          <t>A 28980-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19626,10 +19626,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46245</v>
+        <v>46199</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19685,7 +19685,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 33180-2026</t>
+          <t>A 33182-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19702,7 +19702,7 @@
         <v>46245</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19758,7 +19758,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 28980-2026</t>
+          <t>A 44882-2022</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19772,10 +19772,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46199</v>
+        <v>44841</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19831,7 +19831,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 48966-2023</t>
+          <t>A 56460-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19845,10 +19845,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45209</v>
+        <v>45243</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19904,7 +19904,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 50304-2023</t>
+          <t>A 1783-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19914,14 +19914,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45209</v>
+        <v>45671</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>17.9</v>
+        <v>0.7</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19977,7 +19977,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 35988-2026</t>
+          <t>A 26178-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19991,10 +19991,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46266</v>
+        <v>45091</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20050,7 +20050,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 38214-2023</t>
+          <t>A 51577-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20064,10 +20064,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45161</v>
+        <v>45222</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20123,7 +20123,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 27540-2024</t>
+          <t>A 63029-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20137,10 +20137,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45474</v>
+        <v>45272</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20196,7 +20196,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 9695-2023</t>
+          <t>A 58284-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20210,10 +20210,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>44984</v>
+        <v>45250</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20269,7 +20269,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 25962-2023</t>
+          <t>A 27497-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20283,10 +20283,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45090</v>
+        <v>45474</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>7.3</v>
+        <v>2.2</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20342,7 +20342,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 1904-2023</t>
+          <t>A 35988-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20356,10 +20356,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>44939</v>
+        <v>46266</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20415,7 +20415,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 51577-2023</t>
+          <t>A 48966-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20429,10 +20429,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45222</v>
+        <v>45209</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20488,7 +20488,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 3830-2022</t>
+          <t>A 2405-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>44587</v>
+        <v>45674</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20561,7 +20561,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 17641-2023</t>
+          <t>A 27540-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20575,10 +20575,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45035</v>
+        <v>45474</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>7.3</v>
+        <v>2.7</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20634,7 +20634,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 37517-2026</t>
+          <t>A 9773-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20648,10 +20648,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>46276</v>
+        <v>45362</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20707,7 +20707,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 44882-2022</t>
+          <t>A 57795-2022</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20721,10 +20721,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>44841</v>
+        <v>44897</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20780,7 +20780,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 37912-2026</t>
+          <t>A 50279-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20794,10 +20794,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>46280</v>
+        <v>45216</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 168-2025</t>
+          <t>A 33796-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20867,10 +20867,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45659</v>
+        <v>45133</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20926,7 +20926,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 49362-2024</t>
+          <t>A 2090-2023</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20940,10 +20940,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45595</v>
+        <v>44939</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20999,7 +20999,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 22391-2024</t>
+          <t>A 57161-2022</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21013,10 +21013,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45446</v>
+        <v>44895</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21072,7 +21072,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 27486-2024</t>
+          <t>A 2086-2023</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45474</v>
+        <v>44939</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21145,7 +21145,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 25958-2023</t>
+          <t>A 50304-2023</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21155,14 +21155,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45090</v>
+        <v>45209</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.1</v>
+        <v>17.9</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21218,7 +21218,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 17458-2023</t>
+          <t>A 11126-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21232,10 +21232,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45034</v>
+        <v>45723</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21291,7 +21291,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 23469-2025</t>
+          <t>A 37620-2023</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21305,10 +21305,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45792</v>
+        <v>45159</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 54669-2023</t>
+          <t>A 9695-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21378,10 +21378,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45235</v>
+        <v>44984</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21437,7 +21437,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 11460-2025</t>
+          <t>A 2399-2025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21447,14 +21447,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45726</v>
+        <v>45672</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21510,7 +21510,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 26032-2025</t>
+          <t>A 22699-2024</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21524,10 +21524,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45804</v>
+        <v>45448</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21583,7 +21583,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 25589-2025</t>
+          <t>A 37517-2026</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21597,10 +21597,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45803</v>
+        <v>46276</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21656,7 +21656,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 26020-2025</t>
+          <t>A 20492-2024</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21670,10 +21670,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45804</v>
+        <v>45435</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21729,7 +21729,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 27523-2025</t>
+          <t>A 37912-2026</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21743,10 +21743,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45813</v>
+        <v>46280</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21802,7 +21802,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 15478-2025</t>
+          <t>A 49362-2024</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21816,10 +21816,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45747</v>
+        <v>45595</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21875,7 +21875,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 21146-2022</t>
+          <t>A 168-2025</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21889,10 +21889,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>44704</v>
+        <v>45659</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21948,7 +21948,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 28693-2025</t>
+          <t>A 25958-2023</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21962,10 +21962,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45819</v>
+        <v>45090</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -22021,7 +22021,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 29642-2025</t>
+          <t>A 27486-2024</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -22035,10 +22035,10 @@
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>45825</v>
+        <v>45474</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -22094,7 +22094,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 17270-2025</t>
+          <t>A 22391-2024</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -22108,10 +22108,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>45756</v>
+        <v>45446</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 12038-2025</t>
+          <t>A 11460-2025</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -22181,10 +22181,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>45728</v>
+        <v>45726</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -22240,7 +22240,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 32704-2025</t>
+          <t>A 17458-2023</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22254,10 +22254,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>45839</v>
+        <v>45034</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -22313,7 +22313,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 18285-2025</t>
+          <t>A 54669-2023</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22327,10 +22327,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45762</v>
+        <v>45235</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -22386,7 +22386,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 61602-2024</t>
+          <t>A 23469-2025</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -22400,10 +22400,10 @@
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>45646</v>
+        <v>45792</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -22476,7 +22476,7 @@
         <v>43957</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>S 1259-2022</t>
+          <t>S 2857-2024</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -22542,14 +22542,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>44627</v>
+        <v>45496</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -22605,7 +22605,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>S 1070-2022</t>
+          <t>S 9957-2021</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -22619,10 +22619,10 @@
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>44613</v>
+        <v>44536</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>46</v>
+        <v>26.1</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -22678,7 +22678,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>S 2857-2024</t>
+          <t>S 455-2023</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -22688,14 +22688,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>45496</v>
+        <v>44959</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>2.5</v>
+        <v>14.9</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -22751,7 +22751,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>S 9957-2021</t>
+          <t>S 5219-2022</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -22765,10 +22765,10 @@
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>44536</v>
+        <v>44820</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>26.1</v>
+        <v>22.7</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -22824,7 +22824,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>S 455-2023</t>
+          <t>S 2907-2024</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -22838,10 +22838,10 @@
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>44959</v>
+        <v>45503</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>14.9</v>
+        <v>72.5</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -22897,7 +22897,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>S 5219-2022</t>
+          <t>S 1259-2022</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -22907,14 +22907,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>44820</v>
+        <v>44627</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>22.7</v>
+        <v>0.7</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -22970,7 +22970,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>S 2907-2024</t>
+          <t>S 4069-2022</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -22984,10 +22984,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>45503</v>
+        <v>44757</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>72.5</v>
+        <v>24.7</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -23043,7 +23043,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>S 4069-2022</t>
+          <t>S 1070-2022</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -23057,10 +23057,10 @@
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>44757</v>
+        <v>44613</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>24.7</v>
+        <v>46</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -23133,7 +23133,7 @@
         <v>45484</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>44993</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45148</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>46057</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>46093</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>46097</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>46129</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>46134</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46150</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 5927-2023</t>
+          <t>A 4112-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44963</v>
+        <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1300,45 +1300,261 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>11.4</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
       </c>
       <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Gröngöling
+Utter
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 4112-2025 artfynd.xlsx", "A 4112-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 4112-2025 karta.png", "A 4112-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 4112-2025 georefererad karta.tif", "A 4112-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 4112-2025 FSC-klagomål.docx", "A 4112-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 4112-2025 FSC-klagomål mail.docx", "A 4112-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 4112-2025 tillsynsbegäran.docx", "A 4112-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 4112-2025 tillsynsbegäran mail.docx", "A 4112-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 39622-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Dvärghäxört
+Skogsödla
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 39622-2023 artfynd.xlsx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 39622-2023 karta.png", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 39622-2023 georefererad karta.tif", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 39622-2023 FSC-klagomål.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 39622-2023 FSC-klagomål mail.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 39622-2023 tillsynsbegäran.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 39622-2023 tillsynsbegäran mail.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 5927-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44963</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Hussvala
@@ -1346,248 +1562,32 @@
 Svart skogssnigel</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 5927-2023 artfynd.xlsx", "A 5927-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 5927-2023 karta.png", "A 5927-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 5927-2023 georefererad karta.tif", "A 5927-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 5927-2023 FSC-klagomål.docx", "A 5927-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 5927-2023 FSC-klagomål mail.docx", "A 5927-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 5927-2023 tillsynsbegäran.docx", "A 5927-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 5927-2023 tillsynsbegäran mail.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 39622-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Dvärghäxört
-Skogsödla
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 39622-2023 artfynd.xlsx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 39622-2023 karta.png", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 39622-2023 georefererad karta.tif", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 39622-2023 FSC-klagomål.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 39622-2023 FSC-klagomål mail.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 39622-2023 tillsynsbegäran.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 39622-2023 tillsynsbegäran mail.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 4112-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45684</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>6</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Gröngöling
-Utter
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 4112-2025 artfynd.xlsx", "A 4112-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 4112-2025 karta.png", "A 4112-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 4112-2025 georefererad karta.tif", "A 4112-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 4112-2025 FSC-klagomål.docx", "A 4112-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 4112-2025 FSC-klagomål mail.docx", "A 4112-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 4112-2025 tillsynsbegäran.docx", "A 4112-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 4112-2025 tillsynsbegäran mail.docx", "A 4112-2025")</f>
         <v/>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 31926-2024</t>
+          <t>A 25960-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45510</v>
+        <v>45090</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1768,151 +1768,151 @@
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Bokkantlav
+Guldlockmossa
+Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 25960-2023 artfynd.xlsx", "A 25960-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 25960-2023 karta.png", "A 25960-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 25960-2023 georefererad karta.tif", "A 25960-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 25960-2023 FSC-klagomål.docx", "A 25960-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 25960-2023 FSC-klagomål mail.docx", "A 25960-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 25960-2023 tillsynsbegäran.docx", "A 25960-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 25960-2023 tillsynsbegäran mail.docx", "A 25960-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 31926-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45510</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
         <v>9</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Havstulpanlav
 Klippfrullania
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 31926-2024 artfynd.xlsx", "A 31926-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 31926-2024 karta.png", "A 31926-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 31926-2024 georefererad karta.tif", "A 31926-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 31926-2024 FSC-klagomål.docx", "A 31926-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 31926-2024 FSC-klagomål mail.docx", "A 31926-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 31926-2024 tillsynsbegäran.docx", "A 31926-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 31926-2024 tillsynsbegäran mail.docx", "A 31926-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 25960-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45090</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Bokkantlav
-Guldlockmossa
-Platt fjädermossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 25960-2023 artfynd.xlsx", "A 25960-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 25960-2023 karta.png", "A 25960-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 25960-2023 georefererad karta.tif", "A 25960-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 25960-2023 FSC-klagomål.docx", "A 25960-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 25960-2023 FSC-klagomål mail.docx", "A 25960-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 25960-2023 tillsynsbegäran.docx", "A 25960-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 25960-2023 tillsynsbegäran mail.docx", "A 25960-2023")</f>
         <v/>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45945</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>46183</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45642</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 1604-2025</t>
+          <t>A 6137-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45670</v>
+        <v>45337</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2919,13 +2919,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>11.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2937,10 +2932,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2965,42 +2960,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skorpplätt</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 1604-2025 artfynd.xlsx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 6137-2024 artfynd.xlsx", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 1604-2025 karta.png", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 6137-2024 karta.png", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 1604-2025 georefererad karta.tif", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 6137-2024 georefererad karta.tif", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 1604-2025 FSC-klagomål.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 6137-2024 FSC-klagomål.docx", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 1604-2025 FSC-klagomål mail.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 6137-2024 FSC-klagomål mail.docx", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 1604-2025 tillsynsbegäran.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 6137-2024 tillsynsbegäran.docx", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 1604-2025 tillsynsbegäran mail.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 6137-2024 tillsynsbegäran mail.docx", "A 6137-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6137-2024</t>
+          <t>A 10496-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3014,10 +3009,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45337</v>
+        <v>46076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3030,10 +3025,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.7</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3045,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3054,10 +3049,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3066,39 +3061,39 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Skorpplätt</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 6137-2024 artfynd.xlsx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 10496-2026 artfynd.xlsx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 6137-2024 karta.png", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 10496-2026 karta.png", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 6137-2024 georefererad karta.tif", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 10496-2026 georefererad karta.tif", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 6137-2024 FSC-klagomål.docx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 10496-2026 FSC-klagomål.docx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 6137-2024 FSC-klagomål mail.docx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 10496-2026 FSC-klagomål mail.docx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 6137-2024 tillsynsbegäran.docx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 10496-2026 tillsynsbegäran.docx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 6137-2024 tillsynsbegäran mail.docx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 10496-2026 tillsynsbegäran mail.docx", "A 10496-2026")</f>
         <v/>
       </c>
     </row>
@@ -3122,7 +3117,7 @@
         <v>45980</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3210,7 +3205,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 10496-2026</t>
+          <t>A 22410-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3224,10 +3219,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46076</v>
+        <v>45446</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3240,7 +3235,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3280,42 +3275,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 10496-2026 artfynd.xlsx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 22410-2024 artfynd.xlsx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 10496-2026 karta.png", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 22410-2024 karta.png", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 10496-2026 georefererad karta.tif", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 22410-2024 georefererad karta.tif", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 10496-2026 FSC-klagomål.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 22410-2024 FSC-klagomål.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 10496-2026 FSC-klagomål mail.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 22410-2024 FSC-klagomål mail.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 10496-2026 tillsynsbegäran.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 22410-2024 tillsynsbegäran.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 10496-2026 tillsynsbegäran mail.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 22410-2024 tillsynsbegäran mail.docx", "A 22410-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15068-2023</t>
+          <t>A 1604-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3329,10 +3324,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45015</v>
+        <v>45670</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3344,21 +3339,26 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>9.9</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3385,42 +3385,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 15068-2023 artfynd.xlsx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 1604-2025 artfynd.xlsx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 15068-2023 karta.png", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 1604-2025 karta.png", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 15068-2023 georefererad karta.tif", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 1604-2025 georefererad karta.tif", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 15068-2023 FSC-klagomål.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 1604-2025 FSC-klagomål.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 15068-2023 FSC-klagomål mail.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 1604-2025 FSC-klagomål mail.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 15068-2023 tillsynsbegäran.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 1604-2025 tillsynsbegäran.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 15068-2023 tillsynsbegäran mail.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 1604-2025 tillsynsbegäran mail.docx", "A 1604-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22410-2024</t>
+          <t>A 15068-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45446</v>
+        <v>45015</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3450,13 +3450,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3486,39 +3486,39 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 22410-2024 artfynd.xlsx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 15068-2023 artfynd.xlsx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 22410-2024 karta.png", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 15068-2023 karta.png", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 22410-2024 georefererad karta.tif", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 15068-2023 georefererad karta.tif", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 22410-2024 FSC-klagomål.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 15068-2023 FSC-klagomål.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 22410-2024 FSC-klagomål mail.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 15068-2023 FSC-klagomål mail.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 22410-2024 tillsynsbegäran.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 15068-2023 tillsynsbegäran.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 22410-2024 tillsynsbegäran mail.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 15068-2023 tillsynsbegäran mail.docx", "A 15068-2023")</f>
         <v/>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
         <v>45784</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S 2910-2024</t>
+          <t>S 2731-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3640,14 +3640,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45503</v>
+        <v>44704</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3659,8 +3659,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>24.7</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3696,50 +3701,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2910-2024 artfynd.xlsx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2731-2022 artfynd.xlsx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2910-2024 karta.png", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2731-2022 karta.png", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2910-2024 georefererad karta.tif", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2731-2022 georefererad karta.tif", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2910-2024 FSC-klagomål.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2731-2022 FSC-klagomål.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2910-2024 FSC-klagomål mail.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2731-2022 FSC-klagomål mail.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2910-2024 tillsynsbegäran.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2731-2022 tillsynsbegäran.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2910-2024 tillsynsbegäran mail.docx", "S 2910-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/S 2910-2024 prioriterade fågelarter.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2731-2022 tillsynsbegäran mail.docx", "S 2731-2022")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S 4056-2023</t>
+          <t>S 2910-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3749,14 +3750,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45243</v>
+        <v>45503</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3769,7 +3770,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.1</v>
+        <v>0.4</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3809,42 +3810,46 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 4056-2023 artfynd.xlsx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2910-2024 artfynd.xlsx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 4056-2023 karta.png", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2910-2024 karta.png", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 4056-2023 georefererad karta.tif", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2910-2024 georefererad karta.tif", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 4056-2023 FSC-klagomål.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2910-2024 FSC-klagomål.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 4056-2023 FSC-klagomål mail.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2910-2024 FSC-klagomål mail.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 4056-2023 tillsynsbegäran.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2910-2024 tillsynsbegäran.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 4056-2023 tillsynsbegäran mail.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2910-2024 tillsynsbegäran mail.docx", "S 2910-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/S 2910-2024 prioriterade fågelarter.docx", "S 2910-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S 2731-2022</t>
+          <t>S 4056-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3858,10 +3863,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44704</v>
+        <v>45243</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3873,13 +3878,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>24.7</v>
+        <v>7.1</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3915,39 +3915,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2731-2022 artfynd.xlsx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 4056-2023 artfynd.xlsx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2731-2022 karta.png", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 4056-2023 karta.png", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2731-2022 georefererad karta.tif", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 4056-2023 georefererad karta.tif", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2731-2022 FSC-klagomål.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 4056-2023 FSC-klagomål.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2731-2022 FSC-klagomål mail.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 4056-2023 FSC-klagomål mail.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2731-2022 tillsynsbegäran.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 4056-2023 tillsynsbegäran.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2731-2022 tillsynsbegäran mail.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 4056-2023 tillsynsbegäran mail.docx", "S 4056-2023")</f>
         <v/>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44477</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44752</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44841</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6020-2022</t>
+          <t>A 26178-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44599</v>
+        <v>45091</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19390-2023</t>
+          <t>A 26179-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45048</v>
+        <v>45091</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5561,7 +5561,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 73830-2021</t>
+          <t>A 9773-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44552</v>
+        <v>45362</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 44814-2022</t>
+          <t>A 62180-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44841</v>
+        <v>44915</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5663,8 +5663,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5707,7 +5712,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9748-2024</t>
+          <t>A 24154-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5721,10 +5726,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45362</v>
+        <v>45079</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5737,7 +5742,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5780,7 +5785,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52876-2024</t>
+          <t>A 21023-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5794,10 +5799,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45610</v>
+        <v>45439</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5810,7 +5815,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5853,7 +5858,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10379-2024</t>
+          <t>A 9748-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5867,10 +5872,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45365</v>
+        <v>45362</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5883,7 +5888,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5926,7 +5931,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23740-2023</t>
+          <t>A 58130-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5940,10 +5945,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45077</v>
+        <v>44900</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5956,7 +5961,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>23.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5999,7 +6004,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 72261-2021</t>
+          <t>A 19643-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6013,10 +6018,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44545</v>
+        <v>45432</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6028,8 +6033,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6072,7 +6082,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17737-2023</t>
+          <t>A 22406-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6086,10 +6096,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45037</v>
+        <v>45446</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6102,7 +6112,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6145,7 +6155,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9359-2025</t>
+          <t>A 64091-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6159,10 +6169,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45715</v>
+        <v>45279</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6175,7 +6185,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6218,7 +6228,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47890-2022</t>
+          <t>A 26058-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6232,10 +6242,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44855</v>
+        <v>45468</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6248,7 +6258,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6291,7 +6301,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 23898-2023</t>
+          <t>A 47871-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6305,10 +6315,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45078</v>
+        <v>44855</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6321,7 +6331,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6364,7 +6374,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31704-2023</t>
+          <t>A 44880-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6378,10 +6388,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45117</v>
+        <v>44841</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6394,7 +6404,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.7</v>
+        <v>0.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6437,7 +6447,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14912-2024</t>
+          <t>A 57208-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6447,14 +6457,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45398</v>
+        <v>44895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6467,7 +6477,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6510,7 +6520,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25589-2025</t>
+          <t>A 40814-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6524,10 +6534,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45803</v>
+        <v>45171</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6540,7 +6550,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6583,7 +6593,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26032-2025</t>
+          <t>A 40017-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6597,10 +6607,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45804</v>
+        <v>45168</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6613,7 +6623,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6656,7 +6666,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26020-2025</t>
+          <t>A 2088-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6670,10 +6680,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45804</v>
+        <v>44939</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6686,7 +6696,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6729,7 +6739,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54667-2023</t>
+          <t>A 2092-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6743,10 +6753,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45235</v>
+        <v>44939</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6759,7 +6769,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6802,7 +6812,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1225-2026</t>
+          <t>A 33796-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6816,10 +6826,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46031</v>
+        <v>45133</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6832,7 +6842,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6875,7 +6885,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31399-2025</t>
+          <t>A 52528-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6889,10 +6899,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45833</v>
+        <v>44466</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6905,7 +6915,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6948,7 +6958,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 27523-2025</t>
+          <t>A 36838-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6962,10 +6972,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45813</v>
+        <v>45538</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6978,7 +6988,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7021,7 +7031,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7915-2025</t>
+          <t>A 34279-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7035,10 +7045,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45707</v>
+        <v>45138</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7051,7 +7061,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7094,7 +7104,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15478-2025</t>
+          <t>A 57795-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7108,10 +7118,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45747</v>
+        <v>44897</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7124,7 +7134,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7167,7 +7177,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 21146-2022</t>
+          <t>A 73830-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7181,10 +7191,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44704</v>
+        <v>44552</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7197,7 +7207,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7240,7 +7250,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25963-2023</t>
+          <t>A 6020-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7254,10 +7264,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45090</v>
+        <v>44599</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7270,7 +7280,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7313,7 +7323,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40814-2023</t>
+          <t>A 1783-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7327,10 +7337,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45171</v>
+        <v>45671</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7343,7 +7353,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7386,7 +7396,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32855-2023</t>
+          <t>A 21146-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7400,10 +7410,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45124</v>
+        <v>44704</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7416,7 +7426,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7459,7 +7469,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 1492-2024</t>
+          <t>A 8024-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7473,10 +7483,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45305</v>
+        <v>46063</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7488,8 +7498,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7532,7 +7547,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 1493-2024</t>
+          <t>A 28693-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7546,10 +7561,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45305</v>
+        <v>45819</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7562,7 +7577,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7605,7 +7620,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21910-2024</t>
+          <t>A 9292-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7619,10 +7634,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45443</v>
+        <v>46070</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7635,7 +7650,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7678,7 +7693,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28693-2025</t>
+          <t>A 9125-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7692,10 +7707,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45819</v>
+        <v>46069</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7708,7 +7723,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7751,7 +7766,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 29642-2025</t>
+          <t>A 9105-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7765,10 +7780,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45825</v>
+        <v>46069</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7781,7 +7796,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7824,7 +7839,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57703-2022</t>
+          <t>A 13068-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7838,10 +7853,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44897</v>
+        <v>45002</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7854,7 +7869,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7897,7 +7912,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26058-2024</t>
+          <t>A 9127-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7911,10 +7926,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45468</v>
+        <v>46069</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7927,7 +7942,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7970,7 +7985,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41912-2025</t>
+          <t>A 29642-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7984,10 +7999,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45903</v>
+        <v>45825</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8000,7 +8015,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8043,7 +8058,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41926-2025</t>
+          <t>A 31399-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8057,10 +8072,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45903</v>
+        <v>45833</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8073,7 +8088,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8116,7 +8131,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 63783-2023</t>
+          <t>A 10466-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8130,10 +8145,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45278</v>
+        <v>46077</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8146,7 +8161,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8189,7 +8204,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1397-2023</t>
+          <t>A 10473-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8203,10 +8218,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44936</v>
+        <v>46077</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8219,7 +8234,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8262,7 +8277,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42708-2025</t>
+          <t>A 10480-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8276,10 +8291,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45908</v>
+        <v>46077</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8292,7 +8307,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8335,7 +8350,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 42728-2025</t>
+          <t>A 17737-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8349,10 +8364,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45908</v>
+        <v>45037</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8365,7 +8380,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8408,7 +8423,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12038-2025</t>
+          <t>A 38897-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8422,10 +8437,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45728</v>
+        <v>45887</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8438,7 +8453,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8481,7 +8496,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 36543-2022</t>
+          <t>A 17270-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8495,10 +8510,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44804</v>
+        <v>45756</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8511,7 +8526,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8554,7 +8569,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13068-2023</t>
+          <t>A 12038-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8568,10 +8583,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45002</v>
+        <v>45728</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8584,7 +8599,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8627,7 +8642,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13797-2025</t>
+          <t>A 20492-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8641,10 +8656,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45737</v>
+        <v>45435</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8657,7 +8672,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8700,7 +8715,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17270-2025</t>
+          <t>A 22975-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8714,10 +8729,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45756</v>
+        <v>45072</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8730,7 +8745,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8773,7 +8788,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 43990-2025</t>
+          <t>A 32704-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8787,10 +8802,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45915</v>
+        <v>45839</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8803,7 +8818,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8846,7 +8861,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 5954-2025</t>
+          <t>A 7915-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8860,10 +8875,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45695</v>
+        <v>45707</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8876,7 +8891,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8919,7 +8934,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 2537-2026</t>
+          <t>A 13283-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8933,10 +8948,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46037</v>
+        <v>46093</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8949,7 +8964,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.9</v>
+        <v>8.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8992,7 +9007,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32704-2025</t>
+          <t>A 38928-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9006,10 +9021,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45839</v>
+        <v>45548</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9022,7 +9037,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9065,7 +9080,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 19643-2024</t>
+          <t>A 63783-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9079,10 +9094,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45432</v>
+        <v>45278</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9094,13 +9109,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9143,7 +9153,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44897-2025</t>
+          <t>A 9359-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9157,10 +9167,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45918</v>
+        <v>45715</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9173,7 +9183,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9216,7 +9226,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 44890-2025</t>
+          <t>A 14734-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9230,10 +9240,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45918</v>
+        <v>46101</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9246,7 +9256,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9289,7 +9299,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 23692-2023</t>
+          <t>A 18285-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9303,10 +9313,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45077</v>
+        <v>45762</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9319,7 +9329,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9362,7 +9372,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 2474-2026</t>
+          <t>A 61602-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9376,10 +9386,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46037</v>
+        <v>45646</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9392,7 +9402,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>8.6</v>
+        <v>3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9435,7 +9445,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 37501-2024</t>
+          <t>A 15236-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9449,10 +9459,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45541</v>
+        <v>46105</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9465,7 +9475,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9508,7 +9518,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 44880-2022</t>
+          <t>A 15240-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9522,10 +9532,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44841</v>
+        <v>46105</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9538,7 +9548,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9581,7 +9591,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 171-2025</t>
+          <t>A 15108-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9595,10 +9605,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45659</v>
+        <v>46105</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9611,7 +9621,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9654,7 +9664,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 18285-2025</t>
+          <t>A 52876-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9668,10 +9678,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45762</v>
+        <v>45610</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9727,7 +9737,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 61602-2024</t>
+          <t>A 16363-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9741,10 +9751,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45646</v>
+        <v>46111</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9757,7 +9767,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9800,7 +9810,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 9691-2023</t>
+          <t>A 16283-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9814,10 +9824,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44984</v>
+        <v>46111</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9830,7 +9840,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9873,7 +9883,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 48672-2025</t>
+          <t>A 42177-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9887,10 +9897,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45936</v>
+        <v>45178</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9903,7 +9913,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9946,7 +9956,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 17641-2023</t>
+          <t>A 17608-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9960,10 +9970,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45035</v>
+        <v>46121</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9976,7 +9986,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7.3</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10019,7 +10029,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 3934-2026</t>
+          <t>A 30638-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10033,10 +10043,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46043</v>
+        <v>45112</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10049,7 +10059,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10092,7 +10102,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 4989-2026</t>
+          <t>A 28221-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10106,10 +10116,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46049</v>
+        <v>45099</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10122,7 +10132,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.9</v>
+        <v>6.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10165,7 +10175,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 44925-2025</t>
+          <t>A 41912-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10179,10 +10189,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45918</v>
+        <v>45903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10195,7 +10205,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10238,7 +10248,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 5002-2026</t>
+          <t>A 171-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10252,10 +10262,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46049</v>
+        <v>45659</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10268,7 +10278,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10311,7 +10321,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 39650-2023</t>
+          <t>A 981-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10325,10 +10335,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45167</v>
+        <v>44935</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10341,7 +10351,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10384,7 +10394,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 36280-2025</t>
+          <t>A 41926-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10394,14 +10404,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45867</v>
+        <v>45903</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10414,7 +10424,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10457,7 +10467,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 24154-2023</t>
+          <t>A 42728-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10471,10 +10481,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45079</v>
+        <v>45908</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10487,7 +10497,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10530,7 +10540,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 65211-2021</t>
+          <t>A 42708-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10544,10 +10554,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44515</v>
+        <v>45908</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10560,7 +10570,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.9</v>
+        <v>0.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10603,7 +10613,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 38897-2025</t>
+          <t>A 13797-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10617,10 +10627,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45887</v>
+        <v>45737</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10633,7 +10643,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10676,7 +10686,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 24765-2023</t>
+          <t>A 45192-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10690,10 +10700,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45084</v>
+        <v>44844</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10706,7 +10716,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10749,7 +10759,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 53142-2025</t>
+          <t>A 43990-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10763,10 +10773,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45958</v>
+        <v>45915</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10779,7 +10789,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10822,7 +10832,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 7242-2026</t>
+          <t>A 44890-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10836,10 +10846,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46058</v>
+        <v>45918</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10852,7 +10862,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10895,7 +10905,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 8024-2026</t>
+          <t>A 36543-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10909,10 +10919,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46063</v>
+        <v>44804</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10924,13 +10934,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10973,7 +10978,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 9105-2026</t>
+          <t>A 44897-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10987,10 +10992,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46069</v>
+        <v>45918</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11003,7 +11008,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11046,7 +11051,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 9127-2026</t>
+          <t>A 5941-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11060,10 +11065,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46069</v>
+        <v>45695</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11076,7 +11081,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11119,7 +11124,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 9125-2026</t>
+          <t>A 35490-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11133,10 +11138,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46069</v>
+        <v>45855</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11149,7 +11154,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11192,7 +11197,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 56455-2025</t>
+          <t>A 40190-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11206,10 +11211,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45975</v>
+        <v>44820</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11222,7 +11227,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11265,7 +11270,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 9292-2026</t>
+          <t>A 44814-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11279,10 +11284,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46070</v>
+        <v>44841</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11295,7 +11300,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11338,7 +11343,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 57343-2025</t>
+          <t>A 44864-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11352,10 +11357,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45980</v>
+        <v>45918</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11368,7 +11373,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11411,7 +11416,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 57790-2025</t>
+          <t>A 43992-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11425,10 +11430,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45981</v>
+        <v>45915</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11441,7 +11446,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11484,7 +11489,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 42177-2023</t>
+          <t>A 13611-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11498,10 +11503,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45178</v>
+        <v>45736</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11514,7 +11519,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11557,7 +11562,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 58347-2025</t>
+          <t>A 1397-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11571,10 +11576,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45985</v>
+        <v>44936</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11587,7 +11592,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11630,7 +11635,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 28221-2023</t>
+          <t>A 3205-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11644,10 +11649,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45099</v>
+        <v>45679</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11657,6 +11662,11 @@
       <c r="G137" t="inlineStr">
         <is>
           <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -11703,7 +11713,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 10473-2026</t>
+          <t>A 23693-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11717,10 +11727,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46077</v>
+        <v>45077</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11733,7 +11743,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11776,7 +11786,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 11605-2023</t>
+          <t>A 23990-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11790,10 +11800,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44994</v>
+        <v>45078</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11806,7 +11816,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11849,7 +11859,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 23693-2023</t>
+          <t>A 34591-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11863,10 +11873,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45077</v>
+        <v>45140</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11879,7 +11889,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11922,7 +11932,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 10466-2026</t>
+          <t>A 52372-2021</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11936,10 +11946,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46077</v>
+        <v>44465</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11952,7 +11962,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11995,7 +12005,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 10480-2026</t>
+          <t>A 11126-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12009,10 +12019,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46077</v>
+        <v>45723</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12025,7 +12035,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12068,7 +12078,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 45192-2022</t>
+          <t>A 54667-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12082,10 +12092,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44844</v>
+        <v>45235</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12098,7 +12108,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12141,7 +12151,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 60789-2025</t>
+          <t>A 35168-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12155,10 +12165,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45999</v>
+        <v>45852</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12171,7 +12181,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.9</v>
+        <v>5.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12214,7 +12224,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 9573-2025</t>
+          <t>A 20671-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12228,10 +12238,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45715</v>
+        <v>46141</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12244,7 +12254,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12287,7 +12297,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 13283-2026</t>
+          <t>A 57703-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12301,10 +12311,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46093</v>
+        <v>44897</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12317,7 +12327,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12360,7 +12370,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 22975-2023</t>
+          <t>A 2090-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12374,10 +12384,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45072</v>
+        <v>44939</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12390,7 +12400,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12433,7 +12443,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 52243-2025</t>
+          <t>A 25963-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12447,10 +12457,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45953</v>
+        <v>45090</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12463,7 +12473,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12506,7 +12516,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 53163-2025</t>
+          <t>A 48672-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12520,10 +12530,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45958</v>
+        <v>45936</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12536,7 +12546,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12579,7 +12589,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 52246-2025</t>
+          <t>A 8204-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12593,10 +12603,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45953</v>
+        <v>44971</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12609,7 +12619,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12652,7 +12662,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 14430-2023</t>
+          <t>A 22550-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12666,10 +12676,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45012</v>
+        <v>46155</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12682,7 +12692,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12725,7 +12735,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 64091-2023</t>
+          <t>A 22552-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12739,10 +12749,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45279</v>
+        <v>46155</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12755,7 +12765,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12798,7 +12808,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 14734-2026</t>
+          <t>A 24765-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12812,10 +12822,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46101</v>
+        <v>45084</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12828,7 +12838,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12871,7 +12881,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 25962-2023</t>
+          <t>A 34631-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12885,10 +12895,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45090</v>
+        <v>45848</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12901,7 +12911,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>7.3</v>
+        <v>2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12944,7 +12954,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 15240-2026</t>
+          <t>A 9691-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12958,10 +12968,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46105</v>
+        <v>44984</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12974,7 +12984,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13017,7 +13027,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 30136-2022</t>
+          <t>A 39650-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13031,10 +13041,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44757</v>
+        <v>45167</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13046,13 +13056,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13095,7 +13100,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 38214-2023</t>
+          <t>A 44925-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13109,10 +13114,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45161</v>
+        <v>45918</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13125,7 +13130,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13168,7 +13173,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 15236-2026</t>
+          <t>A 14912-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13178,14 +13183,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46105</v>
+        <v>45398</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13198,7 +13203,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13241,7 +13246,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 15108-2026</t>
+          <t>A 53676-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13255,10 +13260,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46105</v>
+        <v>45960</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13271,7 +13276,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13314,7 +13319,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 23739-2023</t>
+          <t>A 1935-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13328,10 +13333,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45077</v>
+        <v>45308</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13344,7 +13349,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13387,7 +13392,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 16363-2026</t>
+          <t>A 44846-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13401,10 +13406,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46111</v>
+        <v>45918</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13417,7 +13422,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13460,7 +13465,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 16283-2026</t>
+          <t>A 36280-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13470,14 +13475,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46111</v>
+        <v>45867</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13490,7 +13495,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13533,7 +13538,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 34591-2023</t>
+          <t>A 72261-2021</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13547,10 +13552,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45140</v>
+        <v>44545</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13563,7 +13568,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13606,7 +13611,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 17608-2026</t>
+          <t>A 14254-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13620,10 +13625,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46121</v>
+        <v>45009</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13636,7 +13641,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13679,7 +13684,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 9559-2022</t>
+          <t>A 25501-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13693,10 +13698,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44617</v>
+        <v>46177</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13709,7 +13714,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13752,7 +13757,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 31925-2024</t>
+          <t>A 37620-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13766,10 +13771,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45510</v>
+        <v>45159</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13782,7 +13787,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13825,7 +13830,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 30638-2023</t>
+          <t>A 25778-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13839,10 +13844,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45112</v>
+        <v>46178</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13855,7 +13860,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13898,7 +13903,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 2088-2023</t>
+          <t>A 25789-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13912,10 +13917,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44939</v>
+        <v>46178</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13928,7 +13933,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13971,7 +13976,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 35490-2025</t>
+          <t>A 25674-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13985,10 +13990,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45855</v>
+        <v>46178</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14001,7 +14006,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14044,7 +14049,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 13611-2025</t>
+          <t>A 25699-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14058,10 +14063,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45736</v>
+        <v>46178</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14074,7 +14079,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14117,7 +14122,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 981-2023</t>
+          <t>A 25765-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14131,10 +14136,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44935</v>
+        <v>46178</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14147,7 +14152,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14190,7 +14195,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 44864-2025</t>
+          <t>A 25772-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14204,10 +14209,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45918</v>
+        <v>46178</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14220,7 +14225,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14263,7 +14268,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 43992-2025</t>
+          <t>A 25912-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14277,10 +14282,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45915</v>
+        <v>46178</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14293,7 +14298,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14336,7 +14341,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 52528-2021</t>
+          <t>A 25780-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14350,10 +14355,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44466</v>
+        <v>46178</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14366,7 +14371,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14409,7 +14414,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 3205-2025</t>
+          <t>A 25794-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14423,10 +14428,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45679</v>
+        <v>46178</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14438,13 +14443,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>6.7</v>
+        <v>1.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14487,7 +14487,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 36838-2024</t>
+          <t>A 26580-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14501,10 +14501,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45538</v>
+        <v>46183</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 20671-2026</t>
+          <t>A 26597-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14574,10 +14574,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46141</v>
+        <v>46183</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14633,7 +14633,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 1904-2023</t>
+          <t>A 26564-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14647,10 +14647,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44939</v>
+        <v>46183</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14706,7 +14706,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 35168-2025</t>
+          <t>A 26596-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14720,10 +14720,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45852</v>
+        <v>46183</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14779,7 +14779,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 8204-2023</t>
+          <t>A 26583-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14793,10 +14793,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44971</v>
+        <v>46183</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14852,7 +14852,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 11121-2025</t>
+          <t>A 26594-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14866,10 +14866,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45723</v>
+        <v>46183</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14925,7 +14925,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 3830-2022</t>
+          <t>A 26578-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14939,10 +14939,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44587</v>
+        <v>46183</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14998,7 +14998,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 21152-2022</t>
+          <t>A 26593-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15012,10 +15012,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44704</v>
+        <v>46183</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 58130-2022</t>
+          <t>A 31704-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15085,10 +15085,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44900</v>
+        <v>45117</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>23.2</v>
+        <v>6.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15144,7 +15144,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 2359-2023</t>
+          <t>A 7707-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15158,10 +15158,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44942</v>
+        <v>45349</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 22550-2026</t>
+          <t>A 53142-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15231,10 +15231,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46155</v>
+        <v>45958</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15290,7 +15290,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 22552-2026</t>
+          <t>A 27146-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15304,10 +15304,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46155</v>
+        <v>46188</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15363,7 +15363,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 55049-2023</t>
+          <t>A 2405-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15377,10 +15377,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45237</v>
+        <v>45674</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15436,7 +15436,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 15987-2025</t>
+          <t>A 25967-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15450,10 +15450,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45749</v>
+        <v>45090</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15509,7 +15509,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 57208-2022</t>
+          <t>A 29401-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15523,10 +15523,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44895</v>
+        <v>46203</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15582,7 +15582,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 34631-2025</t>
+          <t>A 9559-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15596,10 +15596,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45848</v>
+        <v>44617</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15655,7 +15655,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 3864-2023</t>
+          <t>A 56455-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15669,10 +15669,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44951</v>
+        <v>45975</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>6.2</v>
+        <v>0.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15728,7 +15728,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 25965-2023</t>
+          <t>A 29528-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15742,10 +15742,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45090</v>
+        <v>46203</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15801,7 +15801,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 38928-2024</t>
+          <t>A 57343-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15815,10 +15815,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45548</v>
+        <v>45980</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15874,7 +15874,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 7707-2024</t>
+          <t>A 29530-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15888,10 +15888,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45349</v>
+        <v>46203</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 14254-2023</t>
+          <t>A 29529-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15961,10 +15961,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45009</v>
+        <v>46203</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16020,7 +16020,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 53676-2025</t>
+          <t>A 57790-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16034,10 +16034,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45960</v>
+        <v>45981</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 44846-2025</t>
+          <t>A 58347-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45918</v>
+        <v>45985</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16166,7 +16166,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 25674-2026</t>
+          <t>A 48966-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16180,10 +16180,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46178</v>
+        <v>45209</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16239,7 +16239,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 25699-2026</t>
+          <t>A 50304-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16249,14 +16249,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46178</v>
+        <v>45209</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.1</v>
+        <v>17.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16312,7 +16312,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 25772-2026</t>
+          <t>A 26837-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16326,10 +16326,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46178</v>
+        <v>44740</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16385,7 +16385,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 25778-2026</t>
+          <t>A 29334-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16399,10 +16399,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46178</v>
+        <v>44752</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16414,8 +16414,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16458,7 +16463,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 25789-2026</t>
+          <t>A 27497-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16472,10 +16477,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46178</v>
+        <v>45474</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16488,7 +16493,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16531,7 +16536,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 25912-2026</t>
+          <t>A 54646-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16545,10 +16550,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46178</v>
+        <v>45235</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16561,7 +16566,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16604,7 +16609,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 25794-2026</t>
+          <t>A 21910-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16618,10 +16623,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46178</v>
+        <v>45443</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16634,7 +16639,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16677,7 +16682,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 25780-2026</t>
+          <t>A 34770-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16691,10 +16696,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46178</v>
+        <v>46258</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16707,7 +16712,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16750,7 +16755,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 25501-2026</t>
+          <t>A 21152-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16764,10 +16769,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46177</v>
+        <v>44704</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16780,7 +16785,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16823,7 +16828,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 25765-2026</t>
+          <t>A 33183-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16837,10 +16842,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46178</v>
+        <v>46245</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16853,7 +16858,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16896,7 +16901,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 47871-2022</t>
+          <t>A 34919-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16910,10 +16915,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44855</v>
+        <v>46259</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16926,7 +16931,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16969,7 +16974,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 40190-2022</t>
+          <t>A 33182-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16983,10 +16988,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44820</v>
+        <v>46245</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16999,7 +17004,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17042,7 +17047,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 26578-2026</t>
+          <t>A 33180-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17056,10 +17061,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46183</v>
+        <v>46245</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17072,7 +17077,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17115,7 +17120,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 26580-2026</t>
+          <t>A 11121-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17129,10 +17134,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46183</v>
+        <v>45723</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17145,7 +17150,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17188,7 +17193,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 26597-2026</t>
+          <t>A 28980-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17202,10 +17207,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46183</v>
+        <v>46199</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17218,7 +17223,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17261,7 +17266,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 26564-2026</t>
+          <t>A 60789-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17275,10 +17280,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46183</v>
+        <v>45999</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17291,7 +17296,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17334,7 +17339,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 26593-2026</t>
+          <t>A 1492-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17348,10 +17353,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46183</v>
+        <v>45305</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17364,7 +17369,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17407,7 +17412,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 26583-2026</t>
+          <t>A 1493-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17421,10 +17426,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46183</v>
+        <v>45305</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17437,7 +17442,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17480,7 +17485,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 26594-2026</t>
+          <t>A 9573-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17494,10 +17499,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46183</v>
+        <v>45715</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17553,7 +17558,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 26596-2026</t>
+          <t>A 55049-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17567,10 +17572,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46183</v>
+        <v>45237</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17583,7 +17588,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17626,7 +17631,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 27146-2026</t>
+          <t>A 35988-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17640,10 +17645,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46188</v>
+        <v>46266</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17656,7 +17661,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17699,7 +17704,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 40017-2023</t>
+          <t>A 10379-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17713,10 +17718,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45168</v>
+        <v>45365</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17772,7 +17777,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 34279-2023</t>
+          <t>A 54661-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17786,10 +17791,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45138</v>
+        <v>45235</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17802,7 +17807,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17845,7 +17850,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 54661-2023</t>
+          <t>A 11605-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17859,10 +17864,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45235</v>
+        <v>44994</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17875,7 +17880,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17918,7 +17923,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 54646-2023</t>
+          <t>A 37501-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17932,10 +17937,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45235</v>
+        <v>45541</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17948,7 +17953,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17991,7 +17996,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 2092-2023</t>
+          <t>A 15987-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18005,10 +18010,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44939</v>
+        <v>45749</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18021,7 +18026,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18064,7 +18069,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 21023-2024</t>
+          <t>A 50279-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18078,10 +18083,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45439</v>
+        <v>45216</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18094,7 +18099,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18137,7 +18142,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 62180-2022</t>
+          <t>A 52243-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18151,10 +18156,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44915</v>
+        <v>45953</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18166,13 +18171,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>7.5</v>
+        <v>4.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18215,7 +18215,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 29401-2026</t>
+          <t>A 53163-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18229,10 +18229,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46203</v>
+        <v>45958</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18288,7 +18288,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 29530-2026</t>
+          <t>A 52246-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18302,10 +18302,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46203</v>
+        <v>45953</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18361,7 +18361,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 23990-2023</t>
+          <t>A 30136-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18375,10 +18375,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45078</v>
+        <v>44757</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18390,8 +18390,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18434,7 +18439,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 29528-2026</t>
+          <t>A 37517-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18448,10 +18453,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46203</v>
+        <v>46276</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18464,7 +18469,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18507,7 +18512,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 29529-2026</t>
+          <t>A 37912-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18521,10 +18526,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46203</v>
+        <v>46280</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18537,7 +18542,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18580,7 +18585,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 1935-2024</t>
+          <t>A 32855-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18594,10 +18599,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45308</v>
+        <v>45124</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18610,7 +18615,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18653,7 +18658,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 52372-2021</t>
+          <t>A 3864-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18667,10 +18672,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44465</v>
+        <v>44951</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18683,7 +18688,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.4</v>
+        <v>6.2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18726,7 +18731,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 22406-2024</t>
+          <t>A 58284-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18740,10 +18745,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45446</v>
+        <v>45250</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18756,7 +18761,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18799,7 +18804,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 26179-2023</t>
+          <t>A 2086-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18813,10 +18818,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45091</v>
+        <v>44939</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18829,7 +18834,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18872,7 +18877,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 27967-2024</t>
+          <t>A 2359-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18886,10 +18891,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45476</v>
+        <v>44942</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18902,7 +18907,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18945,7 +18950,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 26837-2022</t>
+          <t>A 57161-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18959,10 +18964,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44740</v>
+        <v>44895</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18975,7 +18980,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19018,7 +19023,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 25967-2023</t>
+          <t>A 27967-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19032,10 +19037,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45090</v>
+        <v>45476</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19048,7 +19053,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>4.9</v>
+        <v>0.4</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19091,7 +19096,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 29334-2022</t>
+          <t>A 47890-2022</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19105,10 +19110,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44752</v>
+        <v>44855</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19120,13 +19125,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19169,7 +19169,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 5941-2025</t>
+          <t>A 1225-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19183,10 +19183,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45695</v>
+        <v>46031</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19242,7 +19242,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 34919-2026</t>
+          <t>A 2474-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19256,10 +19256,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46259</v>
+        <v>46037</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.1</v>
+        <v>8.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19315,7 +19315,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 34770-2026</t>
+          <t>A 2537-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19329,10 +19329,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46258</v>
+        <v>46037</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19388,7 +19388,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 33183-2026</t>
+          <t>A 31925-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19402,10 +19402,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46245</v>
+        <v>45510</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19461,7 +19461,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 29335-2022</t>
+          <t>A 2399-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19471,14 +19471,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44752</v>
+        <v>45672</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19490,13 +19490,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I244" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19539,7 +19534,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 33180-2026</t>
+          <t>A 3934-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19553,10 +19548,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46245</v>
+        <v>46043</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19569,7 +19564,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19612,7 +19607,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 28980-2026</t>
+          <t>A 29335-2022</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19626,10 +19621,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46199</v>
+        <v>44752</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19641,8 +19636,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I246" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19685,7 +19685,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 33182-2026</t>
+          <t>A 22699-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19699,10 +19699,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46245</v>
+        <v>45448</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19758,7 +19758,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 44882-2022</t>
+          <t>A 25965-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19772,10 +19772,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44841</v>
+        <v>45090</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19831,7 +19831,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 56460-2023</t>
+          <t>A 19390-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19845,10 +19845,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45243</v>
+        <v>45048</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19904,7 +19904,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 1783-2025</t>
+          <t>A 65211-2021</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19918,10 +19918,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45671</v>
+        <v>44515</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19977,7 +19977,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 26178-2023</t>
+          <t>A 5002-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19991,10 +19991,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45091</v>
+        <v>46049</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20050,7 +20050,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 51577-2023</t>
+          <t>A 4989-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20064,10 +20064,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45222</v>
+        <v>46049</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20140,7 +20140,7 @@
         <v>45272</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 58284-2023</t>
+          <t>A 7242-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20210,10 +20210,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45250</v>
+        <v>46058</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20269,7 +20269,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 27497-2024</t>
+          <t>A 14430-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20283,10 +20283,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45474</v>
+        <v>45012</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20342,7 +20342,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 35988-2026</t>
+          <t>A 23692-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20356,10 +20356,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46266</v>
+        <v>45077</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20415,7 +20415,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 48966-2023</t>
+          <t>A 23739-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20429,10 +20429,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45209</v>
+        <v>45077</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20488,7 +20488,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 2405-2025</t>
+          <t>A 23740-2023</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45674</v>
+        <v>45077</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20561,7 +20561,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 27540-2024</t>
+          <t>A 23898-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20575,10 +20575,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45474</v>
+        <v>45078</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20634,7 +20634,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 9773-2024</t>
+          <t>A 56460-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20648,10 +20648,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45362</v>
+        <v>45243</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20707,7 +20707,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 57795-2022</t>
+          <t>A 5954-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20721,10 +20721,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>44897</v>
+        <v>45695</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20780,7 +20780,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 50279-2023</t>
+          <t>A 38214-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20794,10 +20794,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45216</v>
+        <v>45161</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 33796-2023</t>
+          <t>A 27540-2024</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20867,10 +20867,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45133</v>
+        <v>45474</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20926,7 +20926,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 2090-2023</t>
+          <t>A 9695-2023</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20940,10 +20940,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44939</v>
+        <v>44984</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20999,7 +20999,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 57161-2022</t>
+          <t>A 25962-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21013,10 +21013,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44895</v>
+        <v>45090</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21072,7 +21072,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 2086-2023</t>
+          <t>A 1904-2023</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21089,7 +21089,7 @@
         <v>44939</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21145,7 +21145,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 50304-2023</t>
+          <t>A 51577-2023</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21155,14 +21155,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45209</v>
+        <v>45222</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>17.9</v>
+        <v>1.8</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21218,7 +21218,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 11126-2025</t>
+          <t>A 3830-2022</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21232,10 +21232,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45723</v>
+        <v>44587</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21291,7 +21291,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 37620-2023</t>
+          <t>A 17641-2023</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21305,10 +21305,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45159</v>
+        <v>45035</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>0.5</v>
+        <v>7.3</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21364,7 +21364,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 9695-2023</t>
+          <t>A 44882-2022</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21378,10 +21378,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>44984</v>
+        <v>44841</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21437,7 +21437,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 2399-2025</t>
+          <t>A 168-2025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21447,14 +21447,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45672</v>
+        <v>45659</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21510,7 +21510,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 22699-2024</t>
+          <t>A 49362-2024</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21524,10 +21524,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45448</v>
+        <v>45595</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21583,7 +21583,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 37517-2026</t>
+          <t>A 22391-2024</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21597,10 +21597,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>46276</v>
+        <v>45446</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21656,7 +21656,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 20492-2024</t>
+          <t>A 27486-2024</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21670,10 +21670,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45435</v>
+        <v>45474</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21729,7 +21729,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 37912-2026</t>
+          <t>A 25958-2023</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21743,10 +21743,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>46280</v>
+        <v>45090</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21802,7 +21802,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 49362-2024</t>
+          <t>A 17458-2023</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21816,10 +21816,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45595</v>
+        <v>45034</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21875,7 +21875,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 168-2025</t>
+          <t>A 23469-2025</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21889,10 +21889,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>45659</v>
+        <v>45792</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21948,7 +21948,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 25958-2023</t>
+          <t>A 54669-2023</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21962,10 +21962,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45090</v>
+        <v>45235</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -22021,7 +22021,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 27486-2024</t>
+          <t>A 11460-2025</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -22035,10 +22035,10 @@
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>45474</v>
+        <v>45726</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -22094,7 +22094,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 22391-2024</t>
+          <t>A 26032-2025</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -22108,10 +22108,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>45446</v>
+        <v>45804</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 11460-2025</t>
+          <t>A 25589-2025</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -22181,10 +22181,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>45726</v>
+        <v>45803</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -22240,7 +22240,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 17458-2023</t>
+          <t>A 26020-2025</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22254,10 +22254,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>45034</v>
+        <v>45804</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -22313,7 +22313,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 54669-2023</t>
+          <t>A 27523-2025</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22327,10 +22327,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45235</v>
+        <v>45813</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -22386,7 +22386,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 23469-2025</t>
+          <t>A 15478-2025</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -22400,10 +22400,10 @@
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>45792</v>
+        <v>45747</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -22476,7 +22476,7 @@
         <v>43957</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>S 2857-2024</t>
+          <t>S 1259-2022</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -22542,14 +22542,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>45496</v>
+        <v>44627</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -22605,7 +22605,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>S 9957-2021</t>
+          <t>S 1070-2022</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -22619,10 +22619,10 @@
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>44536</v>
+        <v>44613</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>26.1</v>
+        <v>46</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -22678,7 +22678,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>S 455-2023</t>
+          <t>S 2857-2024</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -22688,14 +22688,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>44959</v>
+        <v>45496</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>14.9</v>
+        <v>2.5</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -22751,7 +22751,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>S 5219-2022</t>
+          <t>S 9957-2021</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -22765,10 +22765,10 @@
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>44820</v>
+        <v>44536</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -22824,7 +22824,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>S 2907-2024</t>
+          <t>S 455-2023</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -22838,10 +22838,10 @@
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>45503</v>
+        <v>44959</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>72.5</v>
+        <v>14.9</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -22897,7 +22897,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>S 1259-2022</t>
+          <t>S 5219-2022</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -22907,14 +22907,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>44627</v>
+        <v>44820</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>0.7</v>
+        <v>22.7</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -22970,7 +22970,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>S 4069-2022</t>
+          <t>S 2907-2024</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -22984,10 +22984,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>44757</v>
+        <v>45503</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>24.7</v>
+        <v>72.5</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -23043,7 +23043,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>S 1070-2022</t>
+          <t>S 4069-2022</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -23057,10 +23057,10 @@
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>44613</v>
+        <v>44757</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>46</v>
+        <v>24.7</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -23133,7 +23133,7 @@
         <v>45484</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>44993</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45148</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>46057</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>46093</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>46097</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>46129</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>46134</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46150</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 4112-2025</t>
+          <t>A 5927-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45684</v>
+        <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1300,22 +1300,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>11.4</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1324,21 +1324,237 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Hussvala
+Ladusvala
+Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 5927-2023 artfynd.xlsx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 5927-2023 karta.png", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 5927-2023 georefererad karta.tif", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 5927-2023 FSC-klagomål.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 5927-2023 FSC-klagomål mail.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 5927-2023 tillsynsbegäran.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 5927-2023 tillsynsbegäran mail.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 39622-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Dvärghäxört
+Skogsödla
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 39622-2023 artfynd.xlsx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 39622-2023 karta.png", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 39622-2023 georefererad karta.tif", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 39622-2023 FSC-klagomål.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 39622-2023 FSC-klagomål mail.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 39622-2023 tillsynsbegäran.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 39622-2023 tillsynsbegäran mail.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 4112-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
         <v>6</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U10" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Gröngöling
@@ -1346,248 +1562,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 4112-2025 artfynd.xlsx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 4112-2025 karta.png", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 4112-2025 georefererad karta.tif", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 4112-2025 FSC-klagomål.docx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 4112-2025 FSC-klagomål mail.docx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 4112-2025 tillsynsbegäran.docx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 4112-2025 tillsynsbegäran mail.docx", "A 4112-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 39622-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Dvärghäxört
-Skogsödla
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 39622-2023 artfynd.xlsx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 39622-2023 karta.png", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 39622-2023 georefererad karta.tif", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 39622-2023 FSC-klagomål.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 39622-2023 FSC-klagomål mail.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 39622-2023 tillsynsbegäran.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 39622-2023 tillsynsbegäran mail.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 5927-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44963</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Hussvala
-Ladusvala
-Svart skogssnigel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 5927-2023 artfynd.xlsx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 5927-2023 karta.png", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 5927-2023 georefererad karta.tif", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 5927-2023 FSC-klagomål.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 5927-2023 FSC-klagomål mail.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 5927-2023 tillsynsbegäran.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 5927-2023 tillsynsbegäran mail.docx", "A 5927-2023")</f>
         <v/>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25960-2023</t>
+          <t>A 31926-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45090</v>
+        <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1768,151 +1768,151 @@
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Havstulpanlav
+Klippfrullania
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 31926-2024 artfynd.xlsx", "A 31926-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 31926-2024 karta.png", "A 31926-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 31926-2024 georefererad karta.tif", "A 31926-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 31926-2024 FSC-klagomål.docx", "A 31926-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 31926-2024 FSC-klagomål mail.docx", "A 31926-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 31926-2024 tillsynsbegäran.docx", "A 31926-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 31926-2024 tillsynsbegäran mail.docx", "A 31926-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 25960-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45090</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Bokkantlav
 Guldlockmossa
 Platt fjädermossa</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 25960-2023 artfynd.xlsx", "A 25960-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 25960-2023 karta.png", "A 25960-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 25960-2023 georefererad karta.tif", "A 25960-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 25960-2023 FSC-klagomål.docx", "A 25960-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 25960-2023 FSC-klagomål mail.docx", "A 25960-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 25960-2023 tillsynsbegäran.docx", "A 25960-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 25960-2023 tillsynsbegäran mail.docx", "A 25960-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 31926-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45510</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>9</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Havstulpanlav
-Klippfrullania
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 31926-2024 artfynd.xlsx", "A 31926-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 31926-2024 karta.png", "A 31926-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 31926-2024 georefererad karta.tif", "A 31926-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 31926-2024 FSC-klagomål.docx", "A 31926-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 31926-2024 FSC-klagomål mail.docx", "A 31926-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 31926-2024 tillsynsbegäran.docx", "A 31926-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 31926-2024 tillsynsbegäran mail.docx", "A 31926-2024")</f>
         <v/>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 50629-2025</t>
+          <t>A 26585-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45945</v>
+        <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>2</v>
@@ -2305,7 +2305,7 @@
         <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
@@ -2314,42 +2314,42 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 50629-2025 artfynd.xlsx", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 26585-2026 artfynd.xlsx", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 50629-2025 karta.png", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 26585-2026 karta.png", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 50629-2025 georefererad karta.tif", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 26585-2026 georefererad karta.tif", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 50629-2025 FSC-klagomål.docx", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 26585-2026 FSC-klagomål.docx", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 50629-2025 FSC-klagomål mail.docx", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 26585-2026 FSC-klagomål mail.docx", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 50629-2025 tillsynsbegäran.docx", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 26585-2026 tillsynsbegäran.docx", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 50629-2025 tillsynsbegäran mail.docx", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 26585-2026 tillsynsbegäran mail.docx", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/A 50629-2025 prioriterade fågelarter.docx", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/A 26585-2026 prioriterade fågelarter.docx", "A 26585-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26585-2026</t>
+          <t>A 50629-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46183</v>
+        <v>45945</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>6.3</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
@@ -2415,7 +2415,7 @@
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
@@ -2424,35 +2424,35 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 26585-2026 artfynd.xlsx", "A 26585-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 50629-2025 artfynd.xlsx", "A 50629-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 26585-2026 karta.png", "A 26585-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 50629-2025 karta.png", "A 50629-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 26585-2026 georefererad karta.tif", "A 26585-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 50629-2025 georefererad karta.tif", "A 50629-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 26585-2026 FSC-klagomål.docx", "A 26585-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 50629-2025 FSC-klagomål.docx", "A 50629-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 26585-2026 FSC-klagomål mail.docx", "A 26585-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 50629-2025 FSC-klagomål mail.docx", "A 50629-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 26585-2026 tillsynsbegäran.docx", "A 26585-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 50629-2025 tillsynsbegäran.docx", "A 50629-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 26585-2026 tillsynsbegäran mail.docx", "A 26585-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 50629-2025 tillsynsbegäran mail.docx", "A 50629-2025")</f>
         <v/>
       </c>
       <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/A 26585-2026 prioriterade fågelarter.docx", "A 26585-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/A 50629-2025 prioriterade fågelarter.docx", "A 50629-2025")</f>
         <v/>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
         <v>45642</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6137-2024</t>
+          <t>A 1604-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45337</v>
+        <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2919,8 +2919,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>11.7</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2932,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2960,42 +2965,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Skorpplätt</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 6137-2024 artfynd.xlsx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 1604-2025 artfynd.xlsx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 6137-2024 karta.png", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 1604-2025 karta.png", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 6137-2024 georefererad karta.tif", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 1604-2025 georefererad karta.tif", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 6137-2024 FSC-klagomål.docx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 1604-2025 FSC-klagomål.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 6137-2024 FSC-klagomål mail.docx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 1604-2025 FSC-klagomål mail.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 6137-2024 tillsynsbegäran.docx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 1604-2025 tillsynsbegäran.docx", "A 1604-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 6137-2024 tillsynsbegäran mail.docx", "A 6137-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 1604-2025 tillsynsbegäran mail.docx", "A 1604-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 10496-2026</t>
+          <t>A 6137-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3009,10 +3014,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46076</v>
+        <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3025,23 +3030,23 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>11.7</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
@@ -3049,10 +3054,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3061,46 +3066,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Skorpplätt</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 10496-2026 artfynd.xlsx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 6137-2024 artfynd.xlsx", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 10496-2026 karta.png", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 6137-2024 karta.png", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 10496-2026 georefererad karta.tif", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 6137-2024 georefererad karta.tif", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 10496-2026 FSC-klagomål.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 6137-2024 FSC-klagomål.docx", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 10496-2026 FSC-klagomål mail.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 6137-2024 FSC-klagomål mail.docx", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 10496-2026 tillsynsbegäran.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 6137-2024 tillsynsbegäran.docx", "A 6137-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 10496-2026 tillsynsbegäran mail.docx", "A 10496-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 6137-2024 tillsynsbegäran mail.docx", "A 6137-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 57429-2025</t>
+          <t>A 15068-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3114,10 +3119,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45980</v>
+        <v>45015</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3130,19 +3135,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>9.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3154,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3166,46 +3171,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 57429-2025 artfynd.xlsx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 15068-2023 artfynd.xlsx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 57429-2025 karta.png", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 15068-2023 karta.png", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 57429-2025 georefererad karta.tif", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 15068-2023 georefererad karta.tif", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 57429-2025 FSC-klagomål.docx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 15068-2023 FSC-klagomål.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 57429-2025 FSC-klagomål mail.docx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 15068-2023 FSC-klagomål mail.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 57429-2025 tillsynsbegäran.docx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 15068-2023 tillsynsbegäran.docx", "A 15068-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 57429-2025 tillsynsbegäran mail.docx", "A 57429-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 15068-2023 tillsynsbegäran mail.docx", "A 15068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22410-2024</t>
+          <t>A 57429-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3219,10 +3224,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45446</v>
+        <v>45980</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3235,20 +3240,20 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
@@ -3259,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3275,42 +3280,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 22410-2024 artfynd.xlsx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 57429-2025 artfynd.xlsx", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 22410-2024 karta.png", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 57429-2025 karta.png", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 22410-2024 georefererad karta.tif", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 57429-2025 georefererad karta.tif", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 22410-2024 FSC-klagomål.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 57429-2025 FSC-klagomål.docx", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 22410-2024 FSC-klagomål mail.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 57429-2025 FSC-klagomål mail.docx", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 22410-2024 tillsynsbegäran.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 57429-2025 tillsynsbegäran.docx", "A 57429-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 22410-2024 tillsynsbegäran mail.docx", "A 22410-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 57429-2025 tillsynsbegäran mail.docx", "A 57429-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1604-2025</t>
+          <t>A 10496-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3324,10 +3329,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45670</v>
+        <v>46076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3339,16 +3344,11 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3357,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3381,46 +3381,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 1604-2025 artfynd.xlsx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 10496-2026 artfynd.xlsx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 1604-2025 karta.png", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 10496-2026 karta.png", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 1604-2025 georefererad karta.tif", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 10496-2026 georefererad karta.tif", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 1604-2025 FSC-klagomål.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 10496-2026 FSC-klagomål.docx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 1604-2025 FSC-klagomål mail.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 10496-2026 FSC-klagomål mail.docx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 1604-2025 tillsynsbegäran.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 10496-2026 tillsynsbegäran.docx", "A 10496-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 1604-2025 tillsynsbegäran mail.docx", "A 1604-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 10496-2026 tillsynsbegäran mail.docx", "A 10496-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15068-2023</t>
+          <t>A 22410-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45015</v>
+        <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3450,13 +3450,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>9.9</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3486,39 +3486,39 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 15068-2023 artfynd.xlsx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 22410-2024 artfynd.xlsx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 15068-2023 karta.png", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 22410-2024 karta.png", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 15068-2023 georefererad karta.tif", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 22410-2024 georefererad karta.tif", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 15068-2023 FSC-klagomål.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 22410-2024 FSC-klagomål.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 15068-2023 FSC-klagomål mail.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 22410-2024 FSC-klagomål mail.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 15068-2023 tillsynsbegäran.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 22410-2024 tillsynsbegäran.docx", "A 22410-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 15068-2023 tillsynsbegäran mail.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 22410-2024 tillsynsbegäran mail.docx", "A 22410-2024")</f>
         <v/>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
         <v>45784</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S 2731-2022</t>
+          <t>S 2910-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3640,14 +3640,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44704</v>
+        <v>45503</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3659,13 +3659,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>24.7</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3701,46 +3696,50 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2731-2022 artfynd.xlsx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2910-2024 artfynd.xlsx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2731-2022 karta.png", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2910-2024 karta.png", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2731-2022 georefererad karta.tif", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2910-2024 georefererad karta.tif", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2731-2022 FSC-klagomål.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2910-2024 FSC-klagomål.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2731-2022 FSC-klagomål mail.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2910-2024 FSC-klagomål mail.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2731-2022 tillsynsbegäran.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2910-2024 tillsynsbegäran.docx", "S 2910-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2731-2022 tillsynsbegäran mail.docx", "S 2731-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2910-2024 tillsynsbegäran mail.docx", "S 2910-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/S 2910-2024 prioriterade fågelarter.docx", "S 2910-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S 2910-2024</t>
+          <t>S 4056-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3750,14 +3749,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45503</v>
+        <v>45243</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3770,7 +3769,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.4</v>
+        <v>7.1</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3810,46 +3809,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2910-2024 artfynd.xlsx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 4056-2023 artfynd.xlsx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2910-2024 karta.png", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 4056-2023 karta.png", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2910-2024 georefererad karta.tif", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 4056-2023 georefererad karta.tif", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2910-2024 FSC-klagomål.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 4056-2023 FSC-klagomål.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2910-2024 FSC-klagomål mail.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 4056-2023 FSC-klagomål mail.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2910-2024 tillsynsbegäran.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 4056-2023 tillsynsbegäran.docx", "S 4056-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2910-2024 tillsynsbegäran mail.docx", "S 2910-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/S 2910-2024 prioriterade fågelarter.docx", "S 2910-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 4056-2023 tillsynsbegäran mail.docx", "S 4056-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S 4056-2023</t>
+          <t>S 2731-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3863,10 +3858,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45243</v>
+        <v>44704</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3878,8 +3873,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>7.1</v>
+        <v>24.7</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3915,39 +3915,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 4056-2023 artfynd.xlsx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/S 2731-2022 artfynd.xlsx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 4056-2023 karta.png", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/S 2731-2022 karta.png", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 4056-2023 georefererad karta.tif", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/S 2731-2022 georefererad karta.tif", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 4056-2023 FSC-klagomål.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/S 2731-2022 FSC-klagomål.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 4056-2023 FSC-klagomål mail.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/S 2731-2022 FSC-klagomål mail.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 4056-2023 tillsynsbegäran.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/S 2731-2022 tillsynsbegäran.docx", "S 2731-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 4056-2023 tillsynsbegäran mail.docx", "S 4056-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/S 2731-2022 tillsynsbegäran mail.docx", "S 2731-2022")</f>
         <v/>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56006-2021</t>
+          <t>A 29333-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44477</v>
+        <v>44752</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 29333-2022</t>
+          <t>A 56006-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44752</v>
+        <v>44477</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44841</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26178-2023</t>
+          <t>A 6020-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45091</v>
+        <v>44599</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26179-2023</t>
+          <t>A 19390-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45091</v>
+        <v>45048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5561,7 +5561,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9773-2024</t>
+          <t>A 73830-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45362</v>
+        <v>44552</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62180-2022</t>
+          <t>A 9748-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44915</v>
+        <v>45362</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5663,13 +5663,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5712,7 +5707,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 24154-2023</t>
+          <t>A 44814-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5726,10 +5721,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45079</v>
+        <v>44841</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5742,7 +5737,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5785,7 +5780,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21023-2024</t>
+          <t>A 52876-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5799,10 +5794,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45439</v>
+        <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5815,7 +5810,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5858,7 +5853,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9748-2024</t>
+          <t>A 10379-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5872,10 +5867,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45362</v>
+        <v>45365</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5888,7 +5883,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5931,7 +5926,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 58130-2022</t>
+          <t>A 23740-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5945,10 +5940,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44900</v>
+        <v>45077</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5961,7 +5956,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>23.2</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6004,7 +5999,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19643-2024</t>
+          <t>A 72261-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6018,10 +6013,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45432</v>
+        <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6033,13 +6028,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6082,7 +6072,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22406-2024</t>
+          <t>A 9359-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6096,10 +6086,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45446</v>
+        <v>45715</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6112,7 +6102,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6155,7 +6145,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 64091-2023</t>
+          <t>A 17737-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6169,10 +6159,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45279</v>
+        <v>45037</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6185,7 +6175,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6228,7 +6218,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26058-2024</t>
+          <t>A 47890-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6242,10 +6232,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45468</v>
+        <v>44855</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6258,7 +6248,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6301,7 +6291,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47871-2022</t>
+          <t>A 23898-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6315,10 +6305,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44855</v>
+        <v>45078</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6331,7 +6321,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6374,7 +6364,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44880-2022</t>
+          <t>A 31704-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6388,10 +6378,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44841</v>
+        <v>45117</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6404,7 +6394,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.3</v>
+        <v>6.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6447,7 +6437,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 57208-2022</t>
+          <t>A 14912-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6457,14 +6447,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44895</v>
+        <v>45398</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6477,7 +6467,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6520,7 +6510,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 40814-2023</t>
+          <t>A 54667-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6534,10 +6524,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45171</v>
+        <v>45235</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6550,7 +6540,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6593,7 +6583,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40017-2023</t>
+          <t>A 40814-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6607,10 +6597,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45168</v>
+        <v>45171</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6623,7 +6613,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6666,7 +6656,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2088-2023</t>
+          <t>A 25963-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6680,10 +6670,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44939</v>
+        <v>45090</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6696,7 +6686,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6739,7 +6729,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2092-2023</t>
+          <t>A 32855-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6753,10 +6743,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44939</v>
+        <v>45124</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6769,7 +6759,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6812,7 +6802,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33796-2023</t>
+          <t>A 1492-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6826,10 +6816,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45133</v>
+        <v>45305</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6842,7 +6832,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6885,7 +6875,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52528-2021</t>
+          <t>A 1493-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6899,10 +6889,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44466</v>
+        <v>45305</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6915,7 +6905,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6958,7 +6948,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36838-2024</t>
+          <t>A 26058-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6972,10 +6962,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45538</v>
+        <v>45468</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6988,7 +6978,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7031,7 +7021,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34279-2023</t>
+          <t>A 21910-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7045,10 +7035,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45138</v>
+        <v>45443</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7061,7 +7051,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7104,7 +7094,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 57795-2022</t>
+          <t>A 57703-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7121,7 +7111,7 @@
         <v>44897</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7134,7 +7124,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7177,7 +7167,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 73830-2021</t>
+          <t>A 63783-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7191,10 +7181,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44552</v>
+        <v>45278</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7207,7 +7197,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7250,7 +7240,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6020-2022</t>
+          <t>A 1397-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7264,10 +7254,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44599</v>
+        <v>44936</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7280,7 +7270,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7323,7 +7313,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1783-2025</t>
+          <t>A 36543-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7337,10 +7327,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45671</v>
+        <v>44804</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7353,7 +7343,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7396,7 +7386,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21146-2022</t>
+          <t>A 13068-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7410,10 +7400,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44704</v>
+        <v>45002</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7426,7 +7416,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7469,7 +7459,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8024-2026</t>
+          <t>A 5954-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7483,10 +7473,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46063</v>
+        <v>45695</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7498,13 +7488,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7547,7 +7532,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 28693-2025</t>
+          <t>A 19643-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7561,10 +7546,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45819</v>
+        <v>45432</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7576,8 +7561,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7620,7 +7610,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9292-2026</t>
+          <t>A 23692-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7634,10 +7624,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46070</v>
+        <v>45077</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7650,7 +7640,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7693,7 +7683,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 9125-2026</t>
+          <t>A 37501-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7707,10 +7697,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46069</v>
+        <v>45541</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7723,7 +7713,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7766,7 +7756,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 9105-2026</t>
+          <t>A 44880-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7780,10 +7770,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46069</v>
+        <v>44841</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7796,7 +7786,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7839,7 +7829,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13068-2023</t>
+          <t>A 171-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7853,10 +7843,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45002</v>
+        <v>45659</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7869,7 +7859,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7912,7 +7902,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9127-2026</t>
+          <t>A 9691-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7926,10 +7916,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46069</v>
+        <v>44984</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7942,7 +7932,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7985,7 +7975,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 29642-2025</t>
+          <t>A 17641-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7999,10 +7989,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45825</v>
+        <v>45035</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8015,7 +8005,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8058,7 +8048,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31399-2025</t>
+          <t>A 24154-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8072,10 +8062,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45833</v>
+        <v>45079</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8131,7 +8121,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10466-2026</t>
+          <t>A 65211-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8145,10 +8135,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46077</v>
+        <v>44515</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8161,7 +8151,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8204,7 +8194,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 10473-2026</t>
+          <t>A 39650-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8218,10 +8208,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46077</v>
+        <v>45167</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8234,7 +8224,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8277,7 +8267,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10480-2026</t>
+          <t>A 24765-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8291,10 +8281,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46077</v>
+        <v>45084</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8307,7 +8297,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8350,7 +8340,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17737-2023</t>
+          <t>A 981-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8364,10 +8354,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45037</v>
+        <v>44935</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8380,7 +8370,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8423,7 +8413,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 38897-2025</t>
+          <t>A 44864-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8437,10 +8427,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45887</v>
+        <v>45918</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8453,7 +8443,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8496,7 +8486,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17270-2025</t>
+          <t>A 31399-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8510,10 +8500,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45756</v>
+        <v>45833</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8526,7 +8516,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8569,7 +8559,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 12038-2025</t>
+          <t>A 42177-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8583,10 +8573,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45728</v>
+        <v>45178</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8599,7 +8589,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8642,7 +8632,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20492-2024</t>
+          <t>A 38897-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8656,10 +8646,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45435</v>
+        <v>45887</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8715,7 +8705,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 22975-2023</t>
+          <t>A 7915-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8729,10 +8719,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45072</v>
+        <v>45707</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8745,7 +8735,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8788,7 +8778,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32704-2025</t>
+          <t>A 43992-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8802,10 +8792,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45839</v>
+        <v>45915</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8818,7 +8808,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8861,7 +8851,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7915-2025</t>
+          <t>A 28221-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8875,10 +8865,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45707</v>
+        <v>45099</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8891,7 +8881,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.9</v>
+        <v>6.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8934,7 +8924,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13283-2026</t>
+          <t>A 11605-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8948,10 +8938,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46093</v>
+        <v>44994</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8964,7 +8954,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>8.1</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9007,7 +8997,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 38928-2024</t>
+          <t>A 23693-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9021,10 +9011,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45548</v>
+        <v>45077</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9037,7 +9027,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9080,7 +9070,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 63783-2023</t>
+          <t>A 45192-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9094,10 +9084,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45278</v>
+        <v>44844</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9153,7 +9143,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 9359-2025</t>
+          <t>A 3205-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9167,10 +9157,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45715</v>
+        <v>45679</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9182,8 +9172,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.4</v>
+        <v>6.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9226,7 +9221,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 14734-2026</t>
+          <t>A 9573-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9240,10 +9235,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46101</v>
+        <v>45715</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9256,7 +9251,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9299,7 +9294,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 18285-2025</t>
+          <t>A 41912-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9313,10 +9308,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45762</v>
+        <v>45903</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9329,7 +9324,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9372,7 +9367,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61602-2024</t>
+          <t>A 41926-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9386,10 +9381,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45646</v>
+        <v>45903</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9402,7 +9397,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9445,7 +9440,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 15236-2026</t>
+          <t>A 42708-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9459,10 +9454,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46105</v>
+        <v>45908</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9475,7 +9470,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9518,7 +9513,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 15240-2026</t>
+          <t>A 42728-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9532,10 +9527,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46105</v>
+        <v>45908</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9548,7 +9543,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9591,7 +9586,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 15108-2026</t>
+          <t>A 20671-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9605,10 +9600,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46105</v>
+        <v>46141</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9621,7 +9616,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9664,7 +9659,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 52876-2024</t>
+          <t>A 13797-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9678,10 +9673,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45610</v>
+        <v>45737</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9694,7 +9689,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9737,7 +9732,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 16363-2026</t>
+          <t>A 35168-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9751,10 +9746,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46111</v>
+        <v>45852</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9767,7 +9762,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9810,7 +9805,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16283-2026</t>
+          <t>A 43990-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9824,10 +9819,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46111</v>
+        <v>45915</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9840,7 +9835,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9883,7 +9878,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 42177-2023</t>
+          <t>A 22975-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9897,10 +9892,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45178</v>
+        <v>45072</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9913,7 +9908,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9956,7 +9951,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 17608-2026</t>
+          <t>A 44897-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9970,10 +9965,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46121</v>
+        <v>45918</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9986,7 +9981,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10029,7 +10024,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 30638-2023</t>
+          <t>A 44890-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10043,10 +10038,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45112</v>
+        <v>45918</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10059,7 +10054,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10102,7 +10097,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28221-2023</t>
+          <t>A 14430-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10116,10 +10111,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45099</v>
+        <v>45012</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10132,7 +10127,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6.7</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10175,7 +10170,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 41912-2025</t>
+          <t>A 64091-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10189,10 +10184,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45903</v>
+        <v>45279</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10205,7 +10200,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10248,7 +10243,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 171-2025</t>
+          <t>A 25962-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10262,10 +10257,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45659</v>
+        <v>45090</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10278,7 +10273,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.1</v>
+        <v>7.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10321,7 +10316,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 981-2023</t>
+          <t>A 30136-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10335,10 +10330,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44935</v>
+        <v>44757</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10350,8 +10345,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10394,7 +10394,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 41926-2025</t>
+          <t>A 38214-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45903</v>
+        <v>45161</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 42728-2025</t>
+          <t>A 48672-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45908</v>
+        <v>45936</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10540,7 +10540,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 42708-2025</t>
+          <t>A 23739-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10554,10 +10554,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45908</v>
+        <v>45077</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10613,7 +10613,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 13797-2025</t>
+          <t>A 34591-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45737</v>
+        <v>45140</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 45192-2022</t>
+          <t>A 44925-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44844</v>
+        <v>45918</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10759,7 +10759,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 43990-2025</t>
+          <t>A 36280-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10769,14 +10769,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45915</v>
+        <v>45867</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10832,7 +10832,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 44890-2025</t>
+          <t>A 9559-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10846,10 +10846,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45918</v>
+        <v>44617</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10905,7 +10905,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 36543-2022</t>
+          <t>A 31925-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10919,10 +10919,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44804</v>
+        <v>45510</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10978,7 +10978,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 44897-2025</t>
+          <t>A 53142-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10992,10 +10992,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45918</v>
+        <v>45958</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11051,7 +11051,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 5941-2025</t>
+          <t>A 30638-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11065,10 +11065,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45695</v>
+        <v>45112</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11124,7 +11124,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 35490-2025</t>
+          <t>A 2088-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11138,10 +11138,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45855</v>
+        <v>44939</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11197,7 +11197,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 40190-2022</t>
+          <t>A 22550-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44820</v>
+        <v>46155</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11270,7 +11270,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 44814-2022</t>
+          <t>A 56455-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11284,10 +11284,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44841</v>
+        <v>45975</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11343,7 +11343,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 44864-2025</t>
+          <t>A 52528-2021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11357,10 +11357,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45918</v>
+        <v>44466</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11416,7 +11416,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 43992-2025</t>
+          <t>A 57343-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45915</v>
+        <v>45980</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11489,7 +11489,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 13611-2025</t>
+          <t>A 57790-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45736</v>
+        <v>45981</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11562,7 +11562,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 1397-2023</t>
+          <t>A 22552-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11576,10 +11576,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44936</v>
+        <v>46155</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 3205-2025</t>
+          <t>A 36838-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11649,10 +11649,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45679</v>
+        <v>45538</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11664,13 +11664,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11713,7 +11708,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 23693-2023</t>
+          <t>A 58347-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11727,10 +11722,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45077</v>
+        <v>45985</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11743,7 +11738,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11786,7 +11781,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 23990-2023</t>
+          <t>A 34631-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11800,10 +11795,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45078</v>
+        <v>45848</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11816,7 +11811,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11859,7 +11854,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 34591-2023</t>
+          <t>A 1904-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11873,10 +11868,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45140</v>
+        <v>44939</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11889,7 +11884,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11932,7 +11927,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 52372-2021</t>
+          <t>A 60789-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11946,10 +11941,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44465</v>
+        <v>45999</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11962,7 +11957,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12005,7 +12000,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 11126-2025</t>
+          <t>A 8204-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12019,10 +12014,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45723</v>
+        <v>44971</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12035,7 +12030,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12078,7 +12073,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 54667-2023</t>
+          <t>A 11121-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12092,10 +12087,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45235</v>
+        <v>45723</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12108,7 +12103,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12151,7 +12146,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 35168-2025</t>
+          <t>A 3830-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12165,10 +12160,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45852</v>
+        <v>44587</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12181,7 +12176,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12224,7 +12219,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 20671-2026</t>
+          <t>A 21152-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12238,10 +12233,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46141</v>
+        <v>44704</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12254,7 +12249,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12297,7 +12292,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 57703-2022</t>
+          <t>A 58130-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12311,10 +12306,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44897</v>
+        <v>44900</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12327,7 +12322,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>23.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12370,7 +12365,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 2090-2023</t>
+          <t>A 2359-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12384,10 +12379,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44939</v>
+        <v>44942</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12400,7 +12395,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12443,7 +12438,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 25963-2023</t>
+          <t>A 52243-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12457,10 +12452,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45090</v>
+        <v>45953</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12473,7 +12468,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12516,7 +12511,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 48672-2025</t>
+          <t>A 53163-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12530,10 +12525,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45936</v>
+        <v>45958</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12546,7 +12541,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12589,7 +12584,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 8204-2023</t>
+          <t>A 52246-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12603,10 +12598,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44971</v>
+        <v>45953</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12619,7 +12614,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12662,7 +12657,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 22550-2026</t>
+          <t>A 55049-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12676,10 +12671,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46155</v>
+        <v>45237</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12692,7 +12687,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12735,7 +12730,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 22552-2026</t>
+          <t>A 15987-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12749,10 +12744,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46155</v>
+        <v>45749</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12765,7 +12760,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12808,7 +12803,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 24765-2023</t>
+          <t>A 57208-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12822,10 +12817,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45084</v>
+        <v>44895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12838,7 +12833,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12881,7 +12876,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 34631-2025</t>
+          <t>A 1225-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12895,10 +12890,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45848</v>
+        <v>46031</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12911,7 +12906,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12954,7 +12949,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 9691-2023</t>
+          <t>A 53676-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12968,10 +12963,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44984</v>
+        <v>45960</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12984,7 +12979,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13027,7 +13022,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 39650-2023</t>
+          <t>A 2537-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13041,10 +13036,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45167</v>
+        <v>46037</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13057,7 +13052,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13100,7 +13095,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 44925-2025</t>
+          <t>A 3864-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13114,10 +13109,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45918</v>
+        <v>44951</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13130,7 +13125,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13173,7 +13168,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 14912-2024</t>
+          <t>A 2474-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13183,14 +13178,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45398</v>
+        <v>46037</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13203,7 +13198,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13246,7 +13241,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 53676-2025</t>
+          <t>A 25965-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13260,10 +13255,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45960</v>
+        <v>45090</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13276,7 +13271,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13319,7 +13314,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 1935-2024</t>
+          <t>A 38928-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13333,10 +13328,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45308</v>
+        <v>45548</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13349,7 +13344,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13409,7 +13404,7 @@
         <v>45918</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13465,7 +13460,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 36280-2025</t>
+          <t>A 7707-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13475,14 +13470,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45867</v>
+        <v>45349</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13495,7 +13490,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13538,7 +13533,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 72261-2021</t>
+          <t>A 3934-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13552,10 +13547,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44545</v>
+        <v>46043</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13568,7 +13563,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13611,7 +13606,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 14254-2023</t>
+          <t>A 4989-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13625,10 +13620,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45009</v>
+        <v>46049</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13641,7 +13636,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13684,7 +13679,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 25501-2026</t>
+          <t>A 5002-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13698,10 +13693,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46177</v>
+        <v>46049</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13714,7 +13709,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13757,7 +13752,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 37620-2023</t>
+          <t>A 14254-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13771,10 +13766,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45159</v>
+        <v>45009</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13830,7 +13825,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 25778-2026</t>
+          <t>A 25674-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13847,7 +13842,7 @@
         <v>46178</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13903,7 +13898,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 25789-2026</t>
+          <t>A 25699-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13920,7 +13915,7 @@
         <v>46178</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13933,7 +13928,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13976,7 +13971,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 25674-2026</t>
+          <t>A 25772-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13993,7 +13988,7 @@
         <v>46178</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14006,7 +14001,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14049,7 +14044,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 25699-2026</t>
+          <t>A 25778-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14066,7 +14061,7 @@
         <v>46178</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14079,7 +14074,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14122,7 +14117,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 25765-2026</t>
+          <t>A 25789-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14139,7 +14134,7 @@
         <v>46178</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14152,7 +14147,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14195,7 +14190,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 25772-2026</t>
+          <t>A 25912-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14212,7 +14207,7 @@
         <v>46178</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14225,7 +14220,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14268,7 +14263,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 25912-2026</t>
+          <t>A 25794-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14285,7 +14280,7 @@
         <v>46178</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14298,7 +14293,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14358,7 +14353,7 @@
         <v>46178</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14414,7 +14409,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 25794-2026</t>
+          <t>A 7242-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14428,10 +14423,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46178</v>
+        <v>46058</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14444,7 +14439,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14487,7 +14482,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 26580-2026</t>
+          <t>A 25501-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14501,10 +14496,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46183</v>
+        <v>46177</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14517,7 +14512,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14560,7 +14555,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 26597-2026</t>
+          <t>A 25765-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14574,10 +14569,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14590,7 +14585,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14633,7 +14628,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 26564-2026</t>
+          <t>A 8024-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14647,10 +14642,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46183</v>
+        <v>46063</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14660,6 +14655,11 @@
       <c r="G178" t="inlineStr">
         <is>
           <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -14706,7 +14706,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 26596-2026</t>
+          <t>A 9105-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14720,10 +14720,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46183</v>
+        <v>46069</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14779,7 +14779,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 26583-2026</t>
+          <t>A 9127-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14793,10 +14793,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46183</v>
+        <v>46069</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>8.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14852,7 +14852,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 26594-2026</t>
+          <t>A 9125-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14866,10 +14866,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46183</v>
+        <v>46069</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14925,7 +14925,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 26578-2026</t>
+          <t>A 9292-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14939,10 +14939,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46183</v>
+        <v>46070</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14998,7 +14998,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 26593-2026</t>
+          <t>A 47871-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15012,10 +15012,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46183</v>
+        <v>44855</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31704-2023</t>
+          <t>A 26578-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15085,10 +15085,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45117</v>
+        <v>46183</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15144,7 +15144,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 7707-2024</t>
+          <t>A 26580-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15158,10 +15158,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45349</v>
+        <v>46183</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 53142-2025</t>
+          <t>A 26597-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15231,10 +15231,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45958</v>
+        <v>46183</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15290,7 +15290,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 27146-2026</t>
+          <t>A 40190-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15304,10 +15304,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46188</v>
+        <v>44820</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 2405-2025</t>
+          <t>A 10473-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15377,10 +15377,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45674</v>
+        <v>46077</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15436,7 +15436,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 25967-2023</t>
+          <t>A 26564-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15450,10 +15450,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45090</v>
+        <v>46183</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15509,7 +15509,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 29401-2026</t>
+          <t>A 10466-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15523,10 +15523,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46203</v>
+        <v>46077</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15582,7 +15582,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 9559-2022</t>
+          <t>A 10480-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15596,10 +15596,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44617</v>
+        <v>46077</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15655,7 +15655,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 56455-2025</t>
+          <t>A 26593-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15669,10 +15669,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45975</v>
+        <v>46183</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15728,7 +15728,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 29528-2026</t>
+          <t>A 26583-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15742,10 +15742,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46203</v>
+        <v>46183</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15801,7 +15801,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 57343-2025</t>
+          <t>A 26594-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15815,10 +15815,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45980</v>
+        <v>46183</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15874,7 +15874,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 29530-2026</t>
+          <t>A 26596-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15888,10 +15888,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46203</v>
+        <v>46183</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 29529-2026</t>
+          <t>A 27146-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15961,10 +15961,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46203</v>
+        <v>46188</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16020,7 +16020,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 57790-2025</t>
+          <t>A 13283-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16034,10 +16034,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45981</v>
+        <v>46093</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 58347-2025</t>
+          <t>A 40017-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45985</v>
+        <v>45168</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16166,7 +16166,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 48966-2023</t>
+          <t>A 34279-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16180,10 +16180,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45209</v>
+        <v>45138</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16239,7 +16239,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 50304-2023</t>
+          <t>A 14734-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16249,14 +16249,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45209</v>
+        <v>46101</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>17.9</v>
+        <v>0.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16312,7 +16312,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 26837-2022</t>
+          <t>A 15240-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16326,10 +16326,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44740</v>
+        <v>46105</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16385,7 +16385,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 29334-2022</t>
+          <t>A 54661-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16399,10 +16399,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44752</v>
+        <v>45235</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16414,13 +16414,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16463,7 +16458,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 27497-2024</t>
+          <t>A 54646-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16477,10 +16472,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45474</v>
+        <v>45235</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16493,7 +16488,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16536,7 +16531,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 54646-2023</t>
+          <t>A 15236-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16550,10 +16545,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45235</v>
+        <v>46105</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16566,7 +16561,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16609,7 +16604,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 21910-2024</t>
+          <t>A 15108-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16623,10 +16618,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45443</v>
+        <v>46105</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16639,7 +16634,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16682,7 +16677,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 34770-2026</t>
+          <t>A 2092-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16696,10 +16691,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46258</v>
+        <v>44939</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16712,7 +16707,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16755,7 +16750,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 21152-2022</t>
+          <t>A 21023-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16769,10 +16764,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44704</v>
+        <v>45439</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16785,7 +16780,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16828,7 +16823,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 33183-2026</t>
+          <t>A 62180-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16842,10 +16837,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46245</v>
+        <v>44915</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16857,8 +16852,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>5.9</v>
+        <v>7.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 34919-2026</t>
+          <t>A 16363-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16915,10 +16915,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46259</v>
+        <v>46111</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16974,7 +16974,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 33182-2026</t>
+          <t>A 16283-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16988,10 +16988,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46245</v>
+        <v>46111</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17004,7 +17004,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17047,7 +17047,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 33180-2026</t>
+          <t>A 17608-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17061,10 +17061,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46245</v>
+        <v>46121</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17120,7 +17120,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 11121-2025</t>
+          <t>A 23990-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17134,10 +17134,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45723</v>
+        <v>45078</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17193,7 +17193,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 28980-2026</t>
+          <t>A 29401-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17207,10 +17207,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17266,7 +17266,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 60789-2025</t>
+          <t>A 29530-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17280,10 +17280,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45999</v>
+        <v>46203</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17339,7 +17339,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 1492-2024</t>
+          <t>A 1935-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17353,10 +17353,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45305</v>
+        <v>45308</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17412,7 +17412,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 1493-2024</t>
+          <t>A 52372-2021</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17426,10 +17426,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45305</v>
+        <v>44465</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17485,7 +17485,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 9573-2025</t>
+          <t>A 35490-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17499,10 +17499,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45715</v>
+        <v>45855</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17558,7 +17558,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 55049-2023</t>
+          <t>A 22406-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17572,10 +17572,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45237</v>
+        <v>45446</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 35988-2026</t>
+          <t>A 26179-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17645,10 +17645,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46266</v>
+        <v>45091</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17704,7 +17704,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 10379-2024</t>
+          <t>A 13611-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17718,10 +17718,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45365</v>
+        <v>45736</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17777,7 +17777,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 54661-2023</t>
+          <t>A 27967-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17791,10 +17791,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45235</v>
+        <v>45476</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17850,7 +17850,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 11605-2023</t>
+          <t>A 26837-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17864,10 +17864,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44994</v>
+        <v>44740</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17923,7 +17923,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 37501-2024</t>
+          <t>A 25967-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17937,10 +17937,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45541</v>
+        <v>45090</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17996,7 +17996,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 15987-2025</t>
+          <t>A 29528-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18010,10 +18010,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45749</v>
+        <v>46203</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 50279-2023</t>
+          <t>A 29334-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18083,10 +18083,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45216</v>
+        <v>44752</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18098,8 +18098,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18142,7 +18147,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 52243-2025</t>
+          <t>A 29529-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18156,10 +18161,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45953</v>
+        <v>46203</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18172,7 +18177,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18215,7 +18220,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 53163-2025</t>
+          <t>A 5941-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18229,10 +18234,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45958</v>
+        <v>45695</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18245,7 +18250,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18288,7 +18293,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 52246-2025</t>
+          <t>A 29335-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18302,10 +18307,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45953</v>
+        <v>44752</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18317,8 +18322,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18361,7 +18371,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 30136-2022</t>
+          <t>A 44882-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18375,10 +18385,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44757</v>
+        <v>44841</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18390,13 +18400,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18439,7 +18444,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 37517-2026</t>
+          <t>A 56460-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18453,10 +18458,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46276</v>
+        <v>45243</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18469,7 +18474,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18512,7 +18517,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 37912-2026</t>
+          <t>A 1783-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18526,10 +18531,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46280</v>
+        <v>45671</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18542,7 +18547,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18585,7 +18590,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 32855-2023</t>
+          <t>A 26178-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18599,10 +18604,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45124</v>
+        <v>45091</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18615,7 +18620,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18658,7 +18663,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 3864-2023</t>
+          <t>A 51577-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18672,10 +18677,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44951</v>
+        <v>45222</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18688,7 +18693,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18731,7 +18736,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 58284-2023</t>
+          <t>A 63029-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18745,10 +18750,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45250</v>
+        <v>45272</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18761,7 +18766,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18804,7 +18809,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 2086-2023</t>
+          <t>A 58284-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18818,10 +18823,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44939</v>
+        <v>45250</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18834,7 +18839,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18877,7 +18882,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 2359-2023</t>
+          <t>A 27497-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18891,10 +18896,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44942</v>
+        <v>45474</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18907,7 +18912,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18950,7 +18955,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 57161-2022</t>
+          <t>A 48966-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18964,10 +18969,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44895</v>
+        <v>45209</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18980,7 +18985,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19023,7 +19028,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 27967-2024</t>
+          <t>A 2405-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19037,10 +19042,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45476</v>
+        <v>45674</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19053,7 +19058,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19096,7 +19101,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 47890-2022</t>
+          <t>A 27540-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19110,10 +19115,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44855</v>
+        <v>45474</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19126,7 +19131,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19169,7 +19174,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 1225-2026</t>
+          <t>A 9773-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19183,10 +19188,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46031</v>
+        <v>45362</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19199,7 +19204,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19242,7 +19247,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 2474-2026</t>
+          <t>A 57795-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19256,10 +19261,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46037</v>
+        <v>44897</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19272,7 +19277,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>8.6</v>
+        <v>2.3</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19315,7 +19320,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 2537-2026</t>
+          <t>A 50279-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19329,10 +19334,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46037</v>
+        <v>45216</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19345,7 +19350,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19388,7 +19393,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 31925-2024</t>
+          <t>A 34919-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19402,10 +19407,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45510</v>
+        <v>46259</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19418,7 +19423,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19461,7 +19466,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 2399-2025</t>
+          <t>A 34770-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19471,14 +19476,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45672</v>
+        <v>46258</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19491,7 +19496,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19534,7 +19539,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 3934-2026</t>
+          <t>A 33183-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19548,10 +19553,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46043</v>
+        <v>46245</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19564,7 +19569,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19607,7 +19612,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 29335-2022</t>
+          <t>A 33796-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19621,10 +19626,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>44752</v>
+        <v>45133</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19636,13 +19641,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I246" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19685,7 +19685,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 22699-2024</t>
+          <t>A 33180-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19699,10 +19699,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45448</v>
+        <v>46245</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19758,7 +19758,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 25965-2023</t>
+          <t>A 28980-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19772,10 +19772,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45090</v>
+        <v>46199</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19831,7 +19831,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 19390-2023</t>
+          <t>A 33182-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19845,10 +19845,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45048</v>
+        <v>46245</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19904,7 +19904,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 65211-2021</t>
+          <t>A 2090-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19918,10 +19918,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44515</v>
+        <v>44939</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19977,7 +19977,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 5002-2026</t>
+          <t>A 57161-2022</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19991,10 +19991,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46049</v>
+        <v>44895</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20050,7 +20050,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 4989-2026</t>
+          <t>A 2086-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20064,10 +20064,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46049</v>
+        <v>44939</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20123,7 +20123,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 63029-2023</t>
+          <t>A 50304-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20133,14 +20133,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45272</v>
+        <v>45209</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2</v>
+        <v>17.9</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20196,7 +20196,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 7242-2026</t>
+          <t>A 11126-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20210,10 +20210,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46058</v>
+        <v>45723</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20269,7 +20269,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 14430-2023</t>
+          <t>A 37620-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20283,10 +20283,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45012</v>
+        <v>45159</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20342,7 +20342,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 23692-2023</t>
+          <t>A 9695-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20356,10 +20356,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45077</v>
+        <v>44984</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20415,7 +20415,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 23739-2023</t>
+          <t>A 2399-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20425,14 +20425,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45077</v>
+        <v>45672</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20488,7 +20488,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 23740-2023</t>
+          <t>A 22699-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45077</v>
+        <v>45448</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20561,7 +20561,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 23898-2023</t>
+          <t>A 35988-2026</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20575,10 +20575,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45078</v>
+        <v>46266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20634,7 +20634,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 56460-2023</t>
+          <t>A 20492-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20648,10 +20648,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45243</v>
+        <v>45435</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20707,7 +20707,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 5954-2025</t>
+          <t>A 49362-2024</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20721,10 +20721,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45695</v>
+        <v>45595</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20780,7 +20780,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 38214-2023</t>
+          <t>A 168-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20794,10 +20794,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45161</v>
+        <v>45659</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>3.6</v>
+        <v>6.9</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 27540-2024</t>
+          <t>A 37517-2026</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20867,10 +20867,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45474</v>
+        <v>46276</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20926,7 +20926,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 9695-2023</t>
+          <t>A 25958-2023</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20940,10 +20940,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44984</v>
+        <v>45090</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20999,7 +20999,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 25962-2023</t>
+          <t>A 27486-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21013,10 +21013,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45090</v>
+        <v>45474</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>7.3</v>
+        <v>2.2</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21072,7 +21072,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 1904-2023</t>
+          <t>A 22391-2024</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44939</v>
+        <v>45446</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21145,7 +21145,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 51577-2023</t>
+          <t>A 37912-2026</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21159,10 +21159,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45222</v>
+        <v>46280</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21218,7 +21218,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 3830-2022</t>
+          <t>A 11460-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21232,10 +21232,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>44587</v>
+        <v>45726</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21291,7 +21291,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 17641-2023</t>
+          <t>A 17458-2023</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21305,10 +21305,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45035</v>
+        <v>45034</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>7.3</v>
+        <v>1.5</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21364,7 +21364,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 44882-2022</t>
+          <t>A 54669-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21378,10 +21378,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>44841</v>
+        <v>45235</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21437,7 +21437,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 168-2025</t>
+          <t>A 23469-2025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21451,10 +21451,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45659</v>
+        <v>45792</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21510,7 +21510,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 49362-2024</t>
+          <t>A 25589-2025</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21524,10 +21524,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45595</v>
+        <v>45803</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21583,7 +21583,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 22391-2024</t>
+          <t>A 26032-2025</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21597,10 +21597,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45446</v>
+        <v>45804</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21656,7 +21656,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 27486-2024</t>
+          <t>A 26020-2025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21670,10 +21670,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45474</v>
+        <v>45804</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21729,7 +21729,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 25958-2023</t>
+          <t>A 27523-2025</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21743,10 +21743,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45090</v>
+        <v>45813</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21802,7 +21802,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 17458-2023</t>
+          <t>A 15478-2025</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21816,10 +21816,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45034</v>
+        <v>45747</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21875,7 +21875,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 23469-2025</t>
+          <t>A 21146-2022</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21889,10 +21889,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>45792</v>
+        <v>44704</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>0.5</v>
+        <v>7.4</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21948,7 +21948,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 54669-2023</t>
+          <t>A 28693-2025</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21962,10 +21962,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45235</v>
+        <v>45819</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -22021,7 +22021,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 11460-2025</t>
+          <t>A 29642-2025</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -22035,10 +22035,10 @@
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>45726</v>
+        <v>45825</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -22094,7 +22094,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 26032-2025</t>
+          <t>A 12038-2025</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -22108,10 +22108,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>45804</v>
+        <v>45728</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 25589-2025</t>
+          <t>A 17270-2025</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -22181,10 +22181,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>45803</v>
+        <v>45756</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -22240,7 +22240,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 26020-2025</t>
+          <t>A 32704-2025</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22254,10 +22254,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>45804</v>
+        <v>45839</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -22313,7 +22313,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 27523-2025</t>
+          <t>A 18285-2025</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22327,10 +22327,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45813</v>
+        <v>45762</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -22386,7 +22386,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 15478-2025</t>
+          <t>A 61602-2024</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -22400,10 +22400,10 @@
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>45747</v>
+        <v>45646</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -22476,7 +22476,7 @@
         <v>43957</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>S 1259-2022</t>
+          <t>S 2857-2024</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -22542,14 +22542,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>44627</v>
+        <v>45496</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -22605,7 +22605,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>S 1070-2022</t>
+          <t>S 9957-2021</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -22619,10 +22619,10 @@
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>44613</v>
+        <v>44536</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>46</v>
+        <v>26.1</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -22678,7 +22678,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>S 2857-2024</t>
+          <t>S 455-2023</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -22688,14 +22688,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>45496</v>
+        <v>44959</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>2.5</v>
+        <v>14.9</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -22751,7 +22751,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>S 9957-2021</t>
+          <t>S 5219-2022</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -22765,10 +22765,10 @@
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>44536</v>
+        <v>44820</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>26.1</v>
+        <v>22.7</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -22824,7 +22824,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>S 455-2023</t>
+          <t>S 2907-2024</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -22838,10 +22838,10 @@
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>44959</v>
+        <v>45503</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>14.9</v>
+        <v>72.5</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -22897,7 +22897,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>S 5219-2022</t>
+          <t>S 1259-2022</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -22907,14 +22907,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>44820</v>
+        <v>44627</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>22.7</v>
+        <v>0.7</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -22970,7 +22970,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>S 2907-2024</t>
+          <t>S 4069-2022</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -22984,10 +22984,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>45503</v>
+        <v>44757</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>72.5</v>
+        <v>24.7</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -23043,7 +23043,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>S 4069-2022</t>
+          <t>S 1070-2022</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -23057,10 +23057,10 @@
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>44757</v>
+        <v>44613</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>24.7</v>
+        <v>46</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -23133,7 +23133,7 @@
         <v>45484</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>44993</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45148</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>46057</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>46093</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>46097</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>46129</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>46134</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46150</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45163</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>45945</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45642</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>45015</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45980</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>46076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45784</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45503</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45243</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>44704</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44752</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44477</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44841</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44599</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44552</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45362</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>44841</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45365</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45077</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45715</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45037</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44855</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45078</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45117</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>45398</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45235</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45171</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45090</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>45124</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>45305</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>45305</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>45468</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45443</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44897</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45278</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44936</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>44804</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>45002</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45695</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>45432</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45077</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>45541</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44841</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>45659</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>44984</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45035</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>45079</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>44515</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>45167</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>45084</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44935</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45918</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>45833</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>45178</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45887</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>45707</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>45915</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>45099</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>44994</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>45077</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44844</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>45679</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>45715</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45903</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>45903</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>45908</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>45908</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>46141</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>45737</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>45852</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>45915</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45072</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>45918</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>45918</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45012</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45279</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>45090</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44757</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>45161</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45936</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>45077</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45140</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>45918</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>45867</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>44617</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45510</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45958</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45112</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>44939</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>46155</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45975</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>44466</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>45980</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>45981</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>46155</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>45538</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45985</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>45848</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>44939</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45999</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44971</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45723</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44587</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>44704</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>44900</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44942</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>45953</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>45958</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45953</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45237</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45749</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>46031</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45960</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>46037</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44951</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>46037</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>45090</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>45548</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>45918</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45349</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>46043</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>46049</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>46049</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>45009</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>46178</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>46178</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>46178</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>46178</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>46178</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>46178</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>46178</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>46178</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>46058</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>46177</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46178</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>46063</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>46069</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>46069</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>46069</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>46070</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44855</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>46183</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>46183</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>46183</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44820</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>46077</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>46183</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>46077</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>46077</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>46183</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46183</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>46183</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>46183</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>46188</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46093</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>45168</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45138</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>46101</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>46105</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>45235</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45235</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>46105</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>46105</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44939</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45439</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>44915</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>46111</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>46111</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>46121</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45078</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>46203</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>46203</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45308</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>44465</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45855</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45446</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45091</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>45736</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45476</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>44740</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>45090</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>46203</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>44752</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>46203</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45695</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>44752</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>44841</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45243</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45671</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45091</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45222</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45272</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45250</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45474</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45209</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45674</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45474</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45362</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44897</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45216</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>46259</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>46258</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>46245</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45133</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>46245</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>46199</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>46245</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44939</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>44895</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>44939</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45209</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45723</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>45159</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44984</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45672</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45448</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>46266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45435</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45595</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45659</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46276</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45090</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45474</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45446</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>46280</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45726</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45034</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45235</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45792</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45803</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45804</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45804</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45813</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45747</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44704</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45819</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45825</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45728</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45756</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45839</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45762</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45646</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>43957</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45496</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>44536</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44959</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44820</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>45503</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>44627</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44757</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44613</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>45484</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>44993</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45148</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>46057</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>46093</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>46097</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>46129</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>46134</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46150</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE302"/>
+  <dimension ref="A1:AE306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45163</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>45945</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45642</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>45015</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45980</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>46076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45784</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45503</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45243</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>44704</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 29333-2022</t>
+          <t>A 56006-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44752</v>
+        <v>44477</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56006-2021</t>
+          <t>A 29333-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44477</v>
+        <v>44752</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44841</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44599</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44552</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9748-2024</t>
+          <t>A 44814-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45362</v>
+        <v>44841</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 44814-2022</t>
+          <t>A 9748-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44841</v>
+        <v>45362</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5780,7 +5780,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52876-2024</t>
+          <t>A 10379-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45610</v>
+        <v>45365</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5853,7 +5853,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10379-2024</t>
+          <t>A 52876-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45365</v>
+        <v>45610</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5943,7 +5943,7 @@
         <v>45077</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45715</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45037</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44855</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45078</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45117</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>45398</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 54667-2023</t>
+          <t>A 40814-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45235</v>
+        <v>45171</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6583,7 +6583,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40814-2023</t>
+          <t>A 25963-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45171</v>
+        <v>45090</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6656,7 +6656,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 25963-2023</t>
+          <t>A 32855-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45090</v>
+        <v>45124</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6729,7 +6729,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32855-2023</t>
+          <t>A 1492-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45124</v>
+        <v>45305</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6802,7 +6802,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1492-2024</t>
+          <t>A 1493-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6819,7 +6819,7 @@
         <v>45305</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1493-2024</t>
+          <t>A 21910-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45305</v>
+        <v>45443</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6965,7 +6965,7 @@
         <v>45468</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 21910-2024</t>
+          <t>A 57703-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7035,10 +7035,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45443</v>
+        <v>44897</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7094,7 +7094,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 57703-2022</t>
+          <t>A 63783-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7108,10 +7108,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44897</v>
+        <v>45278</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 63783-2023</t>
+          <t>A 36543-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7181,10 +7181,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45278</v>
+        <v>44804</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 1397-2023</t>
+          <t>A 13068-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44936</v>
+        <v>45002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7313,7 +7313,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36543-2022</t>
+          <t>A 1397-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7327,10 +7327,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44804</v>
+        <v>44936</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7386,7 +7386,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13068-2023</t>
+          <t>A 5954-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7400,10 +7400,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45002</v>
+        <v>45695</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7459,7 +7459,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 5954-2025</t>
+          <t>A 19643-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45695</v>
+        <v>45432</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7488,8 +7488,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7532,7 +7537,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 19643-2024</t>
+          <t>A 23692-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7546,10 +7551,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45432</v>
+        <v>45077</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7561,13 +7566,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7610,7 +7610,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 23692-2023</t>
+          <t>A 54667-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45077</v>
+        <v>45235</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7683,7 +7683,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37501-2024</t>
+          <t>A 171-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45541</v>
+        <v>45659</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44880-2022</t>
+          <t>A 37501-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44841</v>
+        <v>45541</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7829,7 +7829,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 171-2025</t>
+          <t>A 44880-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45659</v>
+        <v>44841</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7919,7 +7919,7 @@
         <v>44984</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45035</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24154-2023</t>
+          <t>A 39650-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8062,10 +8062,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45079</v>
+        <v>45167</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8121,7 +8121,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 65211-2021</t>
+          <t>A 24154-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44515</v>
+        <v>45079</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 39650-2023</t>
+          <t>A 65211-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45167</v>
+        <v>44515</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8284,7 +8284,7 @@
         <v>45084</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 981-2023</t>
+          <t>A 35490-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44935</v>
+        <v>45855</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8413,7 +8413,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 44864-2025</t>
+          <t>A 31399-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45918</v>
+        <v>45833</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 31399-2025</t>
+          <t>A 7915-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45833</v>
+        <v>45707</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8559,7 +8559,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 42177-2023</t>
+          <t>A 13611-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8573,10 +8573,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45178</v>
+        <v>45736</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38897-2025</t>
+          <t>A 981-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45887</v>
+        <v>44935</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7915-2025</t>
+          <t>A 44864-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45707</v>
+        <v>45918</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 43992-2025</t>
+          <t>A 38897-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8792,10 +8792,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45915</v>
+        <v>45887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28221-2023</t>
+          <t>A 43992-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45099</v>
+        <v>45915</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6.7</v>
+        <v>1.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11605-2023</t>
+          <t>A 41912-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44994</v>
+        <v>45903</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23693-2023</t>
+          <t>A 41926-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45077</v>
+        <v>45903</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 45192-2022</t>
+          <t>A 3205-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44844</v>
+        <v>45679</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9099,8 +9099,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>6.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9143,7 +9148,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 3205-2025</t>
+          <t>A 42708-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9157,10 +9162,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45679</v>
+        <v>45908</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9172,13 +9177,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>6.7</v>
+        <v>0.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9221,7 +9221,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9573-2025</t>
+          <t>A 42728-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45715</v>
+        <v>45908</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9294,7 +9294,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 41912-2025</t>
+          <t>A 13797-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45903</v>
+        <v>45737</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9367,7 +9367,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 41926-2025</t>
+          <t>A 43990-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45903</v>
+        <v>45915</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 42708-2025</t>
+          <t>A 42177-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9454,10 +9454,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45908</v>
+        <v>45178</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9513,7 +9513,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 42728-2025</t>
+          <t>A 44897-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45908</v>
+        <v>45918</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9586,7 +9586,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 20671-2026</t>
+          <t>A 44890-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46141</v>
+        <v>45918</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9659,7 +9659,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 13797-2025</t>
+          <t>A 28221-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45737</v>
+        <v>45099</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>6.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9732,7 +9732,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 35168-2025</t>
+          <t>A 11605-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9746,10 +9746,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45852</v>
+        <v>44994</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9805,7 +9805,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 43990-2025</t>
+          <t>A 23693-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9819,10 +9819,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45915</v>
+        <v>45077</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 22975-2023</t>
+          <t>A 45192-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45072</v>
+        <v>44844</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9951,7 +9951,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 44897-2025</t>
+          <t>A 20671-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9965,10 +9965,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45918</v>
+        <v>46141</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 44890-2025</t>
+          <t>A 9573-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10038,10 +10038,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45918</v>
+        <v>45715</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10097,7 +10097,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 14430-2023</t>
+          <t>A 48672-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10111,10 +10111,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45012</v>
+        <v>45936</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10170,7 +10170,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 64091-2023</t>
+          <t>A 35168-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10184,10 +10184,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45279</v>
+        <v>45852</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10243,7 +10243,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 25962-2023</t>
+          <t>A 22550-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10257,10 +10257,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45090</v>
+        <v>46155</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>7.3</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30136-2022</t>
+          <t>A 44925-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44757</v>
+        <v>45918</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10345,13 +10345,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10394,7 +10389,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 38214-2023</t>
+          <t>A 22552-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10408,10 +10403,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45161</v>
+        <v>46155</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10424,7 +10419,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10467,7 +10462,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 48672-2025</t>
+          <t>A 36280-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10477,14 +10472,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45936</v>
+        <v>45867</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10497,7 +10492,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10540,7 +10535,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 23739-2023</t>
+          <t>A 22975-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10554,10 +10549,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45077</v>
+        <v>45072</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10570,7 +10565,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10613,7 +10608,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 34591-2023</t>
+          <t>A 34631-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10627,10 +10622,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45140</v>
+        <v>45848</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10643,7 +10638,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10686,7 +10681,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 44925-2025</t>
+          <t>A 14430-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10700,10 +10695,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45918</v>
+        <v>45012</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10716,7 +10711,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10759,7 +10754,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 36280-2025</t>
+          <t>A 64091-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10769,14 +10764,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45867</v>
+        <v>45279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10832,7 +10827,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 9559-2022</t>
+          <t>A 53142-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10846,10 +10841,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44617</v>
+        <v>45958</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10862,7 +10857,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10905,7 +10900,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 31925-2024</t>
+          <t>A 25962-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10919,10 +10914,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45510</v>
+        <v>45090</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10935,7 +10930,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.9</v>
+        <v>7.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10978,7 +10973,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 53142-2025</t>
+          <t>A 30136-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10992,10 +10987,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45958</v>
+        <v>44757</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11007,8 +11002,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11051,7 +11051,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 30638-2023</t>
+          <t>A 38214-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11065,10 +11065,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45112</v>
+        <v>45161</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11124,7 +11124,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 2088-2023</t>
+          <t>A 56455-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11138,10 +11138,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44939</v>
+        <v>45975</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11197,7 +11197,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 22550-2026</t>
+          <t>A 23739-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46155</v>
+        <v>45077</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11270,7 +11270,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 56455-2025</t>
+          <t>A 57343-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11284,10 +11284,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45975</v>
+        <v>45980</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11343,7 +11343,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 52528-2021</t>
+          <t>A 57790-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11357,10 +11357,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44466</v>
+        <v>45981</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11416,7 +11416,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 57343-2025</t>
+          <t>A 34591-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45980</v>
+        <v>45140</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11489,7 +11489,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 57790-2025</t>
+          <t>A 58347-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11562,7 +11562,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 22552-2026</t>
+          <t>A 9559-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11576,10 +11576,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46155</v>
+        <v>44617</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11635,7 +11635,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 36838-2024</t>
+          <t>A 31925-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11649,10 +11649,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45538</v>
+        <v>45510</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 58347-2025</t>
+          <t>A 53676-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11722,10 +11722,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45985</v>
+        <v>45960</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11781,7 +11781,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 34631-2025</t>
+          <t>A 60789-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11795,10 +11795,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45848</v>
+        <v>45999</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11854,7 +11854,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 1904-2023</t>
+          <t>A 44846-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11868,10 +11868,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44939</v>
+        <v>45918</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11927,7 +11927,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 60789-2025</t>
+          <t>A 30638-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11941,10 +11941,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45999</v>
+        <v>45112</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8204-2023</t>
+          <t>A 2088-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12014,10 +12014,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44971</v>
+        <v>44939</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12073,7 +12073,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 11121-2025</t>
+          <t>A 25674-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12087,10 +12087,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45723</v>
+        <v>46178</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12146,7 +12146,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 3830-2022</t>
+          <t>A 25699-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12160,10 +12160,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44587</v>
+        <v>46178</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12219,7 +12219,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 21152-2022</t>
+          <t>A 25772-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12233,10 +12233,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44704</v>
+        <v>46178</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12292,7 +12292,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 58130-2022</t>
+          <t>A 25778-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12306,10 +12306,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44900</v>
+        <v>46178</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>23.2</v>
+        <v>1.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12365,7 +12365,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 2359-2023</t>
+          <t>A 25789-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12379,10 +12379,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44942</v>
+        <v>46178</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12438,7 +12438,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 52243-2025</t>
+          <t>A 25912-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12452,10 +12452,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45953</v>
+        <v>46178</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12511,7 +12511,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 53163-2025</t>
+          <t>A 25794-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12525,10 +12525,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45958</v>
+        <v>46178</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12584,7 +12584,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 52246-2025</t>
+          <t>A 25780-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12598,10 +12598,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45953</v>
+        <v>46178</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12657,7 +12657,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 55049-2023</t>
+          <t>A 25501-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12671,10 +12671,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45237</v>
+        <v>46177</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12730,7 +12730,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 15987-2025</t>
+          <t>A 25765-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12744,10 +12744,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45749</v>
+        <v>46178</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12803,7 +12803,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 57208-2022</t>
+          <t>A 52243-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12817,10 +12817,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44895</v>
+        <v>45953</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12876,7 +12876,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 1225-2026</t>
+          <t>A 53163-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12890,10 +12890,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46031</v>
+        <v>45958</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12949,7 +12949,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 53676-2025</t>
+          <t>A 52246-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12963,10 +12963,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45960</v>
+        <v>45953</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13022,7 +13022,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 2537-2026</t>
+          <t>A 52528-2021</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13036,10 +13036,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46037</v>
+        <v>44466</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13095,7 +13095,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 3864-2023</t>
+          <t>A 36838-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13109,10 +13109,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44951</v>
+        <v>45538</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13168,7 +13168,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 2474-2026</t>
+          <t>A 1225-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13182,10 +13182,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13241,7 +13241,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 25965-2023</t>
+          <t>A 26578-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13255,10 +13255,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45090</v>
+        <v>46183</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13314,7 +13314,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 38928-2024</t>
+          <t>A 26580-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13328,10 +13328,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45548</v>
+        <v>46183</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13387,7 +13387,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 44846-2025</t>
+          <t>A 26597-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13401,10 +13401,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45918</v>
+        <v>46183</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13460,7 +13460,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 7707-2024</t>
+          <t>A 26564-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13474,10 +13474,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45349</v>
+        <v>46183</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 3934-2026</t>
+          <t>A 26593-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13547,10 +13547,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46043</v>
+        <v>46183</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13606,7 +13606,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 4989-2026</t>
+          <t>A 26583-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13620,10 +13620,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46049</v>
+        <v>46183</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13679,7 +13679,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 5002-2026</t>
+          <t>A 26594-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13693,10 +13693,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46049</v>
+        <v>46183</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13752,7 +13752,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 14254-2023</t>
+          <t>A 26596-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45009</v>
+        <v>46183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 25674-2026</t>
+          <t>A 2537-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13839,10 +13839,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46178</v>
+        <v>46037</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13898,7 +13898,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 25699-2026</t>
+          <t>A 2474-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13912,10 +13912,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46178</v>
+        <v>46037</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.1</v>
+        <v>8.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13971,7 +13971,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 25772-2026</t>
+          <t>A 27146-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13985,10 +13985,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46178</v>
+        <v>46188</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14044,7 +14044,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 25778-2026</t>
+          <t>A 3934-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14058,10 +14058,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46178</v>
+        <v>46043</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14117,7 +14117,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 25789-2026</t>
+          <t>A 4989-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14131,10 +14131,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46178</v>
+        <v>46049</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14190,7 +14190,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 25912-2026</t>
+          <t>A 1904-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14204,10 +14204,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46178</v>
+        <v>44939</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14263,7 +14263,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 25794-2026</t>
+          <t>A 5002-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46178</v>
+        <v>46049</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14336,7 +14336,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 25780-2026</t>
+          <t>A 8204-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14350,10 +14350,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46178</v>
+        <v>44971</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14409,7 +14409,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 7242-2026</t>
+          <t>A 11121-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14423,10 +14423,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46058</v>
+        <v>45723</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14482,7 +14482,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 25501-2026</t>
+          <t>A 3830-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14496,10 +14496,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46177</v>
+        <v>44587</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14555,7 +14555,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 25765-2026</t>
+          <t>A 7242-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14569,10 +14569,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46178</v>
+        <v>46058</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14628,7 +14628,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 8024-2026</t>
+          <t>A 21152-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14642,10 +14642,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46063</v>
+        <v>44704</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14657,13 +14657,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14706,7 +14701,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 9105-2026</t>
+          <t>A 58130-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14720,10 +14715,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46069</v>
+        <v>44900</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14736,7 +14731,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>23.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14779,7 +14774,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 9127-2026</t>
+          <t>A 8024-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14793,10 +14788,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46069</v>
+        <v>46063</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14808,8 +14803,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14852,7 +14852,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 9125-2026</t>
+          <t>A 9105-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14869,7 +14869,7 @@
         <v>46069</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14925,7 +14925,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 9292-2026</t>
+          <t>A 9127-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14939,10 +14939,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14998,7 +14998,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 47871-2022</t>
+          <t>A 9125-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15012,10 +15012,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44855</v>
+        <v>46069</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 26578-2026</t>
+          <t>A 9292-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15085,10 +15085,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46183</v>
+        <v>46070</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15144,7 +15144,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 26580-2026</t>
+          <t>A 10473-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15158,10 +15158,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46183</v>
+        <v>46077</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 26597-2026</t>
+          <t>A 10466-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15231,10 +15231,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46183</v>
+        <v>46077</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15290,7 +15290,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 40190-2022</t>
+          <t>A 10480-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15304,10 +15304,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44820</v>
+        <v>46077</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15363,7 +15363,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 10473-2026</t>
+          <t>A 2359-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15377,10 +15377,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46077</v>
+        <v>44942</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15436,7 +15436,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 26564-2026</t>
+          <t>A 55049-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15450,10 +15450,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46183</v>
+        <v>45237</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15509,7 +15509,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 10466-2026</t>
+          <t>A 15987-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15523,10 +15523,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46077</v>
+        <v>45749</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15582,7 +15582,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 10480-2026</t>
+          <t>A 57208-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15596,10 +15596,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46077</v>
+        <v>44895</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15655,7 +15655,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 26593-2026</t>
+          <t>A 13283-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15669,10 +15669,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46183</v>
+        <v>46093</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.6</v>
+        <v>8.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15728,7 +15728,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 26583-2026</t>
+          <t>A 29401-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15742,10 +15742,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46183</v>
+        <v>46203</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>8.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15801,7 +15801,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 26594-2026</t>
+          <t>A 29530-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15815,10 +15815,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46183</v>
+        <v>46203</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15874,7 +15874,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 26596-2026</t>
+          <t>A 3864-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15888,10 +15888,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46183</v>
+        <v>44951</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 27146-2026</t>
+          <t>A 25965-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15961,10 +15961,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46188</v>
+        <v>45090</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16020,7 +16020,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 13283-2026</t>
+          <t>A 14734-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16034,10 +16034,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46093</v>
+        <v>46101</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>8.1</v>
+        <v>0.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 40017-2023</t>
+          <t>A 38928-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45168</v>
+        <v>45548</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16166,7 +16166,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 34279-2023</t>
+          <t>A 15240-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16180,10 +16180,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45138</v>
+        <v>46105</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16239,7 +16239,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 14734-2026</t>
+          <t>A 7707-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16253,10 +16253,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46101</v>
+        <v>45349</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16312,7 +16312,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 15240-2026</t>
+          <t>A 15236-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16329,7 +16329,7 @@
         <v>46105</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16385,7 +16385,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 54661-2023</t>
+          <t>A 15108-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16399,10 +16399,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45235</v>
+        <v>46105</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16458,7 +16458,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 54646-2023</t>
+          <t>A 29528-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16472,10 +16472,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45235</v>
+        <v>46203</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16531,7 +16531,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 15236-2026</t>
+          <t>A 16363-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16545,10 +16545,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16604,7 +16604,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 15108-2026</t>
+          <t>A 16283-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16618,10 +16618,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16677,7 +16677,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 2092-2023</t>
+          <t>A 29529-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16691,10 +16691,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44939</v>
+        <v>46203</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16750,7 +16750,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 21023-2024</t>
+          <t>A 14254-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16764,10 +16764,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45439</v>
+        <v>45009</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 62180-2022</t>
+          <t>A 17608-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16837,10 +16837,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44915</v>
+        <v>46121</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16852,13 +16852,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>7.5</v>
+        <v>1.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16901,7 +16896,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 16363-2026</t>
+          <t>A 47871-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16915,10 +16910,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46111</v>
+        <v>44855</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16931,7 +16926,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16974,7 +16969,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 16283-2026</t>
+          <t>A 40190-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16988,10 +16983,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46111</v>
+        <v>44820</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17004,7 +16999,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17047,7 +17042,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 17608-2026</t>
+          <t>A 40017-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17061,10 +17056,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46121</v>
+        <v>45168</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17077,7 +17072,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17120,7 +17115,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 23990-2023</t>
+          <t>A 34279-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17134,10 +17129,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45078</v>
+        <v>45138</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17150,7 +17145,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17193,7 +17188,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 29401-2026</t>
+          <t>A 34919-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17207,10 +17202,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46203</v>
+        <v>46259</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17223,7 +17218,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17266,7 +17261,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 29530-2026</t>
+          <t>A 34770-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17280,10 +17275,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46203</v>
+        <v>46258</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17296,7 +17291,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17339,7 +17334,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 1935-2024</t>
+          <t>A 54661-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17353,10 +17348,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45308</v>
+        <v>45235</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17369,7 +17364,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17412,7 +17407,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 52372-2021</t>
+          <t>A 54646-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17426,10 +17421,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44465</v>
+        <v>45235</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17442,7 +17437,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.4</v>
+        <v>5.3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17485,7 +17480,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 35490-2025</t>
+          <t>A 33183-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17499,10 +17494,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45855</v>
+        <v>46245</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17515,7 +17510,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17558,7 +17553,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 22406-2024</t>
+          <t>A 33180-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17572,10 +17567,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45446</v>
+        <v>46245</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17588,7 +17583,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17631,7 +17626,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 26179-2023</t>
+          <t>A 2092-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17645,10 +17640,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45091</v>
+        <v>44939</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17661,7 +17656,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17704,7 +17699,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 13611-2025</t>
+          <t>A 21023-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17718,10 +17713,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45736</v>
+        <v>45439</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17734,7 +17729,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17777,7 +17772,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 27967-2024</t>
+          <t>A 62180-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17791,10 +17786,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45476</v>
+        <v>44915</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17806,8 +17801,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>0.4</v>
+        <v>7.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17850,7 +17850,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 26837-2022</t>
+          <t>A 28980-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17864,10 +17864,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44740</v>
+        <v>46199</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17923,7 +17923,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 25967-2023</t>
+          <t>A 33182-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17937,10 +17937,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45090</v>
+        <v>46245</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17996,7 +17996,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 29528-2026</t>
+          <t>A 23990-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18010,10 +18010,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46203</v>
+        <v>45078</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 29334-2022</t>
+          <t>A 1935-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18083,10 +18083,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44752</v>
+        <v>45308</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18098,13 +18098,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18147,7 +18142,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 29529-2026</t>
+          <t>A 52372-2021</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18161,10 +18156,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46203</v>
+        <v>44465</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18177,7 +18172,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18220,7 +18215,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 5941-2025</t>
+          <t>A 22406-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18234,10 +18229,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45695</v>
+        <v>45446</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18250,7 +18245,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18293,7 +18288,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 29335-2022</t>
+          <t>A 26179-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18307,10 +18302,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44752</v>
+        <v>45091</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18322,13 +18317,8 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18371,7 +18361,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 44882-2022</t>
+          <t>A 27967-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18385,10 +18375,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44841</v>
+        <v>45476</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18401,7 +18391,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18444,7 +18434,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 56460-2023</t>
+          <t>A 26837-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18458,10 +18448,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45243</v>
+        <v>44740</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18474,7 +18464,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18517,7 +18507,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 1783-2025</t>
+          <t>A 25967-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18531,10 +18521,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45671</v>
+        <v>45090</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18547,7 +18537,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18590,7 +18580,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 26178-2023</t>
+          <t>A 29334-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18604,10 +18594,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45091</v>
+        <v>44752</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18619,8 +18609,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18663,7 +18658,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 51577-2023</t>
+          <t>A 5941-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18677,10 +18672,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45222</v>
+        <v>45695</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18693,7 +18688,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18736,7 +18731,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 63029-2023</t>
+          <t>A 29335-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18750,10 +18745,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45272</v>
+        <v>44752</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18765,8 +18760,13 @@
           <t>ÖRKELLJUNGA</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18809,7 +18809,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 58284-2023</t>
+          <t>A 37517-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18823,10 +18823,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45250</v>
+        <v>46276</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18882,7 +18882,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 27497-2024</t>
+          <t>A 44882-2022</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18896,10 +18896,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45474</v>
+        <v>44841</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18955,7 +18955,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 48966-2023</t>
+          <t>A 56460-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18969,10 +18969,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45209</v>
+        <v>45243</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19028,7 +19028,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 2405-2025</t>
+          <t>A 1783-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19042,10 +19042,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45674</v>
+        <v>45671</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19101,7 +19101,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 27540-2024</t>
+          <t>A 26178-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19115,10 +19115,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45474</v>
+        <v>45091</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19174,7 +19174,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 9773-2024</t>
+          <t>A 51577-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19188,10 +19188,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45362</v>
+        <v>45222</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19247,7 +19247,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 57795-2022</t>
+          <t>A 37912-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19261,10 +19261,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44897</v>
+        <v>46280</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19320,7 +19320,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 50279-2023</t>
+          <t>A 63029-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19334,10 +19334,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45216</v>
+        <v>45272</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19393,7 +19393,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 34919-2026</t>
+          <t>A 58284-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19407,10 +19407,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46259</v>
+        <v>45250</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19466,7 +19466,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 34770-2026</t>
+          <t>A 27497-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19480,10 +19480,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46258</v>
+        <v>45474</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19539,7 +19539,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 33183-2026</t>
+          <t>A 48966-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19553,10 +19553,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46245</v>
+        <v>45209</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19612,7 +19612,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 33796-2023</t>
+          <t>A 2405-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19626,10 +19626,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45133</v>
+        <v>45674</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19685,7 +19685,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 33180-2026</t>
+          <t>A 27540-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19699,10 +19699,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46245</v>
+        <v>45474</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>6.5</v>
+        <v>2.7</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19758,7 +19758,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 28980-2026</t>
+          <t>A 9773-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19772,10 +19772,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46199</v>
+        <v>45362</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19831,7 +19831,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 33182-2026</t>
+          <t>A 57795-2022</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19845,10 +19845,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46245</v>
+        <v>44897</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19904,7 +19904,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 2090-2023</t>
+          <t>A 50279-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19918,10 +19918,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44939</v>
+        <v>45216</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19977,7 +19977,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 57161-2022</t>
+          <t>A 33796-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19991,10 +19991,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44895</v>
+        <v>45133</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20050,7 +20050,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 2086-2023</t>
+          <t>A 35988-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20064,10 +20064,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>44939</v>
+        <v>46266</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20123,7 +20123,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 50304-2023</t>
+          <t>A 2090-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20133,14 +20133,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45209</v>
+        <v>44939</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>17.9</v>
+        <v>1.6</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20196,7 +20196,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 11126-2025</t>
+          <t>A 39212-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20210,10 +20210,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45723</v>
+        <v>46287</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20269,7 +20269,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 37620-2023</t>
+          <t>A 57161-2022</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20283,10 +20283,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45159</v>
+        <v>44895</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20342,7 +20342,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 9695-2023</t>
+          <t>A 2086-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20356,10 +20356,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>44984</v>
+        <v>44939</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20415,7 +20415,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 2399-2025</t>
+          <t>A 50304-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20429,10 +20429,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45672</v>
+        <v>45209</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.9</v>
+        <v>17.9</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20488,7 +20488,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 22699-2024</t>
+          <t>A 11126-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45448</v>
+        <v>45723</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20561,7 +20561,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 35988-2026</t>
+          <t>A 37620-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20575,10 +20575,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46266</v>
+        <v>45159</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20634,7 +20634,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 20492-2024</t>
+          <t>A 9695-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20648,10 +20648,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45435</v>
+        <v>44984</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20707,7 +20707,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 49362-2024</t>
+          <t>A 2399-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20717,14 +20717,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45595</v>
+        <v>45672</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20780,7 +20780,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 168-2025</t>
+          <t>A 38065-2026</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20794,10 +20794,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45659</v>
+        <v>46280</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>6.9</v>
+        <v>2.2</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 37517-2026</t>
+          <t>A 38954-2026</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20867,10 +20867,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20926,7 +20926,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 25958-2023</t>
+          <t>A 22699-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20940,10 +20940,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45090</v>
+        <v>45448</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20999,7 +20999,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 27486-2024</t>
+          <t>A 39228-2026</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21013,10 +21013,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45474</v>
+        <v>46287</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21072,7 +21072,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 22391-2024</t>
+          <t>A 20492-2024</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45446</v>
+        <v>45435</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21145,7 +21145,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 37912-2026</t>
+          <t>A 49362-2024</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21159,10 +21159,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>46280</v>
+        <v>45595</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21218,7 +21218,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 11460-2025</t>
+          <t>A 168-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21232,10 +21232,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45726</v>
+        <v>45659</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21291,7 +21291,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 17458-2023</t>
+          <t>A 25958-2023</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21305,10 +21305,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45034</v>
+        <v>45090</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21364,7 +21364,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 54669-2023</t>
+          <t>A 27486-2024</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21378,10 +21378,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45235</v>
+        <v>45474</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21437,7 +21437,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 23469-2025</t>
+          <t>A 22391-2024</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21451,10 +21451,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45792</v>
+        <v>45446</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21510,7 +21510,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 25589-2025</t>
+          <t>A 11460-2025</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21524,10 +21524,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45803</v>
+        <v>45726</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21583,7 +21583,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 26032-2025</t>
+          <t>A 17458-2023</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21597,10 +21597,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45804</v>
+        <v>45034</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21656,7 +21656,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 26020-2025</t>
+          <t>A 54669-2023</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21670,10 +21670,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45804</v>
+        <v>45235</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21729,7 +21729,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 27523-2025</t>
+          <t>A 23469-2025</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21743,10 +21743,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45813</v>
+        <v>45792</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21802,7 +21802,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 15478-2025</t>
+          <t>A 25589-2025</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21816,10 +21816,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45747</v>
+        <v>45803</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21875,7 +21875,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 21146-2022</t>
+          <t>A 26032-2025</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21889,10 +21889,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>44704</v>
+        <v>45804</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>7.4</v>
+        <v>0.5</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21948,7 +21948,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 28693-2025</t>
+          <t>A 26020-2025</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21962,10 +21962,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45819</v>
+        <v>45804</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 29642-2025</t>
+          <t>A 27523-2025</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -22035,10 +22035,10 @@
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>45825</v>
+        <v>45813</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -22094,7 +22094,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 12038-2025</t>
+          <t>A 15478-2025</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -22108,10 +22108,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>45728</v>
+        <v>45747</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 17270-2025</t>
+          <t>A 21146-2022</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -22181,10 +22181,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>45756</v>
+        <v>44704</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>0.7</v>
+        <v>7.4</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -22240,7 +22240,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 32704-2025</t>
+          <t>A 28693-2025</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22254,10 +22254,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>45839</v>
+        <v>45819</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -22313,7 +22313,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 18285-2025</t>
+          <t>A 29642-2025</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22327,10 +22327,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45762</v>
+        <v>45825</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -22386,7 +22386,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 61602-2024</t>
+          <t>A 12038-2025</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -22400,10 +22400,10 @@
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>45646</v>
+        <v>45728</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -22459,24 +22459,24 @@
     <row r="285" ht="15" customHeight="1">
       <c r="A285" t="inlineStr">
         <is>
-          <t>S 1016-2020</t>
+          <t>A 17270-2025</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D285" s="1" t="n">
-        <v>43957</v>
+        <v>45756</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         </is>
       </c>
       <c r="I285" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -22532,24 +22532,24 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>S 2857-2024</t>
+          <t>A 32704-2025</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>45496</v>
+        <v>45839</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -22605,24 +22605,24 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>S 9957-2021</t>
+          <t>A 18285-2025</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>44536</v>
+        <v>45762</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>26.1</v>
+        <v>1.2</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -22678,24 +22678,24 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>S 455-2023</t>
+          <t>A 61602-2024</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>44959</v>
+        <v>45646</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>14.9</v>
+        <v>3</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -22751,7 +22751,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>S 5219-2022</t>
+          <t>S 1016-2020</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -22761,14 +22761,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>44820</v>
+        <v>43957</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>22.7</v>
+        <v>1.4</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -22824,7 +22824,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>S 2907-2024</t>
+          <t>S 2857-2024</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -22834,14 +22834,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>45503</v>
+        <v>45496</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>72.5</v>
+        <v>2.5</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -22897,7 +22897,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>S 1259-2022</t>
+          <t>S 9957-2021</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -22907,14 +22907,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>44627</v>
+        <v>44536</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>0.7</v>
+        <v>26.1</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -22970,7 +22970,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>S 4069-2022</t>
+          <t>S 455-2023</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -22984,10 +22984,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>44757</v>
+        <v>44959</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>24.7</v>
+        <v>14.9</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -23043,7 +23043,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>S 1070-2022</t>
+          <t>S 5219-2022</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -23057,10 +23057,10 @@
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>44613</v>
+        <v>44820</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>46</v>
+        <v>22.7</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -23116,7 +23116,7 @@
     <row r="294" ht="15" customHeight="1">
       <c r="A294" t="inlineStr">
         <is>
-          <t>S 2756-2024</t>
+          <t>S 2907-2024</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -23126,14 +23126,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Dikesrensning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D294" s="1" t="n">
-        <v>45484</v>
+        <v>45503</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>2.9</v>
+        <v>72.5</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -23189,7 +23189,7 @@
     <row r="295" ht="15" customHeight="1">
       <c r="A295" t="inlineStr">
         <is>
-          <t>S 856-2023</t>
+          <t>S 1259-2022</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -23199,14 +23199,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D295" s="1" t="n">
-        <v>44993</v>
+        <v>44627</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         </is>
       </c>
       <c r="I295" t="n">
-        <v>20.8</v>
+        <v>0.7</v>
       </c>
       <c r="J295" t="n">
         <v>0</v>
@@ -23262,7 +23262,7 @@
     <row r="296" ht="15" customHeight="1">
       <c r="A296" t="inlineStr">
         <is>
-          <t>S 2633-2023</t>
+          <t>S 4069-2022</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -23276,10 +23276,10 @@
         </is>
       </c>
       <c r="D296" s="1" t="n">
-        <v>45148</v>
+        <v>44757</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="I296" t="n">
-        <v>9</v>
+        <v>24.7</v>
       </c>
       <c r="J296" t="n">
         <v>0</v>
@@ -23335,7 +23335,7 @@
     <row r="297" ht="15" customHeight="1">
       <c r="A297" t="inlineStr">
         <is>
-          <t>S 293-2026</t>
+          <t>S 1070-2022</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -23349,10 +23349,10 @@
         </is>
       </c>
       <c r="D297" s="1" t="n">
-        <v>46057</v>
+        <v>44613</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>40.7</v>
+        <v>46</v>
       </c>
       <c r="J297" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
     <row r="298" ht="15" customHeight="1">
       <c r="A298" t="inlineStr">
         <is>
-          <t>S 718-2026</t>
+          <t>S 2756-2024</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -23418,14 +23418,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Dikesrensning</t>
         </is>
       </c>
       <c r="D298" s="1" t="n">
-        <v>46093</v>
+        <v>45484</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         </is>
       </c>
       <c r="I298" t="n">
-        <v>8.699999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J298" t="n">
         <v>0</v>
@@ -23481,7 +23481,7 @@
     <row r="299" ht="15" customHeight="1">
       <c r="A299" t="inlineStr">
         <is>
-          <t>S 755-2026</t>
+          <t>S 856-2023</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -23495,10 +23495,10 @@
         </is>
       </c>
       <c r="D299" s="1" t="n">
-        <v>46097</v>
+        <v>44993</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         </is>
       </c>
       <c r="I299" t="n">
-        <v>14.3</v>
+        <v>20.8</v>
       </c>
       <c r="J299" t="n">
         <v>0</v>
@@ -23554,7 +23554,7 @@
     <row r="300" ht="15" customHeight="1">
       <c r="A300" t="inlineStr">
         <is>
-          <t>S 1079-2026</t>
+          <t>S 2633-2023</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -23568,10 +23568,10 @@
         </is>
       </c>
       <c r="D300" s="1" t="n">
-        <v>46129</v>
+        <v>45148</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         </is>
       </c>
       <c r="I300" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J300" t="n">
         <v>0</v>
@@ -23627,148 +23627,440 @@
     <row r="301" ht="15" customHeight="1">
       <c r="A301" t="inlineStr">
         <is>
+          <t>S 293-2026</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="n">
+        <v>46057</v>
+      </c>
+      <c r="E301" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I301" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" t="n">
+        <v>0</v>
+      </c>
+      <c r="M301" t="n">
+        <v>0</v>
+      </c>
+      <c r="N301" t="n">
+        <v>0</v>
+      </c>
+      <c r="O301" t="n">
+        <v>0</v>
+      </c>
+      <c r="P301" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>0</v>
+      </c>
+      <c r="R301" t="n">
+        <v>0</v>
+      </c>
+      <c r="S301" t="n">
+        <v>0</v>
+      </c>
+      <c r="T301" t="n">
+        <v>0</v>
+      </c>
+      <c r="U301" t="n">
+        <v>0</v>
+      </c>
+      <c r="V301" s="2" t="inlineStr"/>
+    </row>
+    <row r="302" ht="15" customHeight="1">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>S 718-2026</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D302" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E302" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I302" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0</v>
+      </c>
+      <c r="L302" t="n">
+        <v>0</v>
+      </c>
+      <c r="M302" t="n">
+        <v>0</v>
+      </c>
+      <c r="N302" t="n">
+        <v>0</v>
+      </c>
+      <c r="O302" t="n">
+        <v>0</v>
+      </c>
+      <c r="P302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>0</v>
+      </c>
+      <c r="R302" t="n">
+        <v>0</v>
+      </c>
+      <c r="S302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U302" t="n">
+        <v>0</v>
+      </c>
+      <c r="V302" s="2" t="inlineStr"/>
+    </row>
+    <row r="303" ht="15" customHeight="1">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>S 755-2026</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D303" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="E303" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I303" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J303" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" t="n">
+        <v>0</v>
+      </c>
+      <c r="L303" t="n">
+        <v>0</v>
+      </c>
+      <c r="M303" t="n">
+        <v>0</v>
+      </c>
+      <c r="N303" t="n">
+        <v>0</v>
+      </c>
+      <c r="O303" t="n">
+        <v>0</v>
+      </c>
+      <c r="P303" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>0</v>
+      </c>
+      <c r="R303" t="n">
+        <v>0</v>
+      </c>
+      <c r="S303" t="n">
+        <v>0</v>
+      </c>
+      <c r="T303" t="n">
+        <v>0</v>
+      </c>
+      <c r="U303" t="n">
+        <v>0</v>
+      </c>
+      <c r="V303" s="2" t="inlineStr"/>
+    </row>
+    <row r="304" ht="15" customHeight="1">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>S 1079-2026</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D304" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="E304" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I304" t="n">
+        <v>11</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" t="n">
+        <v>0</v>
+      </c>
+      <c r="L304" t="n">
+        <v>0</v>
+      </c>
+      <c r="M304" t="n">
+        <v>0</v>
+      </c>
+      <c r="N304" t="n">
+        <v>0</v>
+      </c>
+      <c r="O304" t="n">
+        <v>0</v>
+      </c>
+      <c r="P304" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>0</v>
+      </c>
+      <c r="R304" t="n">
+        <v>0</v>
+      </c>
+      <c r="S304" t="n">
+        <v>0</v>
+      </c>
+      <c r="T304" t="n">
+        <v>0</v>
+      </c>
+      <c r="U304" t="n">
+        <v>0</v>
+      </c>
+      <c r="V304" s="2" t="inlineStr"/>
+    </row>
+    <row r="305" ht="15" customHeight="1">
+      <c r="A305" t="inlineStr">
+        <is>
           <t>S 1124-2026</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
+      <c r="C305" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D301" s="1" t="n">
+      <c r="D305" s="1" t="n">
         <v>46134</v>
       </c>
-      <c r="E301" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I301" t="n">
+      <c r="E305" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I305" t="n">
         <v>30</v>
       </c>
-      <c r="J301" t="n">
-        <v>0</v>
-      </c>
-      <c r="K301" t="n">
-        <v>0</v>
-      </c>
-      <c r="L301" t="n">
-        <v>0</v>
-      </c>
-      <c r="M301" t="n">
-        <v>0</v>
-      </c>
-      <c r="N301" t="n">
-        <v>0</v>
-      </c>
-      <c r="O301" t="n">
-        <v>0</v>
-      </c>
-      <c r="P301" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
-      <c r="R301" t="n">
-        <v>0</v>
-      </c>
-      <c r="S301" t="n">
-        <v>0</v>
-      </c>
-      <c r="T301" t="n">
-        <v>0</v>
-      </c>
-      <c r="U301" t="n">
-        <v>0</v>
-      </c>
-      <c r="V301" s="2" t="inlineStr"/>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="n">
+        <v>0</v>
+      </c>
+      <c r="L305" t="n">
+        <v>0</v>
+      </c>
+      <c r="M305" t="n">
+        <v>0</v>
+      </c>
+      <c r="N305" t="n">
+        <v>0</v>
+      </c>
+      <c r="O305" t="n">
+        <v>0</v>
+      </c>
+      <c r="P305" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>0</v>
+      </c>
+      <c r="R305" t="n">
+        <v>0</v>
+      </c>
+      <c r="S305" t="n">
+        <v>0</v>
+      </c>
+      <c r="T305" t="n">
+        <v>0</v>
+      </c>
+      <c r="U305" t="n">
+        <v>0</v>
+      </c>
+      <c r="V305" s="2" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
         <is>
           <t>S 1336-2026</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
+      <c r="C306" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D302" s="1" t="n">
+      <c r="D306" s="1" t="n">
         <v>46150</v>
       </c>
-      <c r="E302" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I302" t="n">
+      <c r="E306" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I306" t="n">
         <v>35.2</v>
       </c>
-      <c r="J302" t="n">
-        <v>0</v>
-      </c>
-      <c r="K302" t="n">
-        <v>0</v>
-      </c>
-      <c r="L302" t="n">
-        <v>0</v>
-      </c>
-      <c r="M302" t="n">
-        <v>0</v>
-      </c>
-      <c r="N302" t="n">
-        <v>0</v>
-      </c>
-      <c r="O302" t="n">
-        <v>0</v>
-      </c>
-      <c r="P302" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
-      <c r="R302" t="n">
-        <v>0</v>
-      </c>
-      <c r="S302" t="n">
-        <v>0</v>
-      </c>
-      <c r="T302" t="n">
-        <v>0</v>
-      </c>
-      <c r="U302" t="n">
-        <v>0</v>
-      </c>
-      <c r="V302" s="2" t="inlineStr"/>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" t="n">
+        <v>0</v>
+      </c>
+      <c r="L306" t="n">
+        <v>0</v>
+      </c>
+      <c r="M306" t="n">
+        <v>0</v>
+      </c>
+      <c r="N306" t="n">
+        <v>0</v>
+      </c>
+      <c r="O306" t="n">
+        <v>0</v>
+      </c>
+      <c r="P306" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>0</v>
+      </c>
+      <c r="R306" t="n">
+        <v>0</v>
+      </c>
+      <c r="S306" t="n">
+        <v>0</v>
+      </c>
+      <c r="T306" t="n">
+        <v>0</v>
+      </c>
+      <c r="U306" t="n">
+        <v>0</v>
+      </c>
+      <c r="V306" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45163</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>44963</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45090</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45510</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45945</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>46183</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45642</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45337</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>46076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>45980</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>45446</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45670</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45015</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45784</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>44704</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45503</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>45243</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44477</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44752</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44841</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45091</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45091</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45362</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45362</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>44915</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>45079</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>45439</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44900</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45432</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>45446</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45953</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45468</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45958</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45953</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>44855</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>44841</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>44895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>45279</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>45171</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45168</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>45833</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>46031</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>45887</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>45133</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>45707</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44939</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>44939</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44466</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>46037</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>46037</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>46043</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45538</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>46049</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>45138</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45903</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>46049</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45903</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45908</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45908</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>46058</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45737</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>44897</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45671</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45915</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>45918</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>44552</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>44599</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45918</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>46063</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45804</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>46070</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>46069</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>46069</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45803</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>46069</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>45804</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>46077</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>46077</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>46077</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45002</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45936</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45037</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>46093</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45435</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>45072</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45918</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>46101</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45867</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>46105</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>46105</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>46105</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45548</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>46111</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>46111</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45278</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45715</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>46121</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45610</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>45813</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45178</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45112</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>45975</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>45980</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>45981</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>44935</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45985</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>45099</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>45659</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45855</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>45918</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45999</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45915</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45736</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45747</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44844</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44704</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>44804</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45695</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45679</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44820</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45819</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>44841</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>44936</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>45077</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45825</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45078</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>45140</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>44465</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45723</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>45852</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>46141</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45235</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>44897</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>46155</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>46155</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>44939</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>45756</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45848</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>45090</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>45728</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45839</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>44971</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45084</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45762</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45646</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45960</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45918</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>44984</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>45167</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>46177</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>45398</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>46178</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>46178</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>46178</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>46178</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>46178</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>45308</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>46178</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>46178</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>46178</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46178</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>44545</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>46183</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>46183</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46183</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>46183</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>46183</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>46183</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>46183</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>46183</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45009</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45159</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>46188</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45117</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45349</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46203</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>46203</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>46203</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46203</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45674</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45090</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44617</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>46258</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45209</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>45209</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>46259</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>46199</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44740</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44752</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45474</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>45235</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>45443</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>44704</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45723</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45305</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45305</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45715</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45237</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>45365</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>45235</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44994</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45541</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>46276</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45749</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>46280</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45216</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>46282</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44757</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>45124</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>46287</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>46245</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>44951</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>46280</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>46245</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>46287</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>46266</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>46288</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>45250</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>44939</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44942</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>46290</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>44895</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>45476</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>46245</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44855</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>45510</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45672</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>44752</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45448</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45090</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45048</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44515</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45272</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45012</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45077</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45077</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45077</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45078</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45243</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45695</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45161</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45474</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44984</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45090</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44939</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45222</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>44587</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45035</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>44841</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45659</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45595</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45446</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45474</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45090</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45034</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45792</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45235</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>45726</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>43957</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44627</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44613</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>45496</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>44536</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>44959</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44820</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>45503</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>44757</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45484</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>44993</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45148</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>46057</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>46093</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>46097</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>46129</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>46134</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>46150</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45163</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>44963</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45090</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45510</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45945</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>46183</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45642</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45337</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>46076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>45980</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>45446</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45670</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45015</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45784</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>44704</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45503</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>45243</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44477</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44752</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44841</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45091</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45091</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45362</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45362</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>44915</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>45079</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>45439</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44900</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45432</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>45446</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45953</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45468</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45958</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45953</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>44855</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>44841</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>44895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>45279</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>45171</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45168</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>45833</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>46031</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>45887</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>45133</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>45707</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44939</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>44939</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44466</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>46037</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>46037</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>46043</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45538</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>46049</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>45138</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45903</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>46049</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45903</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45908</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45908</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>46058</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45737</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>44897</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45671</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45915</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>45918</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>44552</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>44599</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45918</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>46063</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45804</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>46070</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>46069</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>46069</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45803</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>46069</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>45804</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>46077</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>46077</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>46077</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45002</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45936</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45037</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>46093</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45435</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>45072</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45918</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>46101</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45867</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>46105</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>46105</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>46105</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45548</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>46111</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>46111</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45278</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45715</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>46121</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45610</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>45813</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45178</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45112</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>45975</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>45980</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>45981</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>44935</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45985</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>45099</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>45659</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45855</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>45918</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45999</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45915</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45736</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45747</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44844</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44704</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>44804</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45695</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45679</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44820</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45819</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>44841</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>44936</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>45077</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45825</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45078</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>45140</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>44465</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45723</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>45852</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>46141</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45235</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>44897</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>46155</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>46155</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>44939</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>45756</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45848</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>45090</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>45728</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45839</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>44971</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45084</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45762</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45646</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45960</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45918</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>44984</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>45167</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>46177</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>45398</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>46178</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>46178</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>46178</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>46178</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>46178</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>45308</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>46178</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>46178</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>46178</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46178</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>44545</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>46183</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>46183</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46183</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>46183</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>46183</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>46183</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>46183</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>46183</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45009</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45159</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>46188</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45117</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45349</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46203</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>46203</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>46203</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46203</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45674</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45090</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44617</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>46258</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45209</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>45209</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>46259</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>46199</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44740</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44752</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45474</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>45235</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>45443</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>44704</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45723</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45305</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45305</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45715</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45237</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>45365</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>45235</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44994</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45541</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>46276</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45749</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>46280</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45216</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>46282</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44757</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>45124</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>46287</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>46245</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>44951</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>46280</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>46245</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>46287</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>46266</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>46288</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>45250</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>44939</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44942</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>46290</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>44895</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>45476</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>46245</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44855</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>45510</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45672</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>44752</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45448</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45090</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45048</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44515</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45272</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45012</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45077</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45077</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45077</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45078</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45243</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45695</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45161</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45474</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44984</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45090</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44939</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45222</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>44587</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45035</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>44841</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45659</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45595</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45446</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45474</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45090</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45034</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45792</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45235</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>45726</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>43957</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44627</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44613</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>45496</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>44536</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>44959</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44820</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>45503</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>44757</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45484</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>44993</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45148</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>46057</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>46093</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>46097</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>46129</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>46134</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>46150</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45163</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45642</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45945</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46183</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>46076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45980</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45015</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45784</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45503</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45243</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>44704</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44477</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44752</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44841</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44599</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44552</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>44841</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45365</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45362</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45077</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45610</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45474</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45446</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44545</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>45037</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45715</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45833</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>44855</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45726</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45707</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45078</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>45953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>45958</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>45953</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>45034</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45235</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>45117</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>46031</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>45398</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>45903</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>45903</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>46037</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>46037</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>45908</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>45908</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45235</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>45792</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>45737</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>46043</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45915</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>46049</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>46049</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>45803</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>45918</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>45804</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>45918</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>45804</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>45090</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>45171</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>45124</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>45305</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>45305</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>45443</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>44897</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         <v>46058</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>45468</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>45278</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>46063</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>46069</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>44936</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>45936</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>46069</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>46069</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>46070</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44804</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>45695</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>45432</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45918</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>46077</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>46077</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>45077</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>46077</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45867</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45541</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44841</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45659</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>45813</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>45958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>44984</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>45035</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>46093</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45747</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>45167</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>45079</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44515</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>46101</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45975</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45084</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>44704</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46105</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46105</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>46105</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45980</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>45981</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>46111</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>46111</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>45985</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>45819</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45825</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>46121</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>45999</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>45178</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>45099</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>44994</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45077</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>45728</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44844</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>45855</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45756</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>45839</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>45736</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>45715</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>44935</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45918</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45915</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45762</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45072</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45679</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45012</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45279</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45646</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45090</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>44757</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45161</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>46141</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45852</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45077</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45140</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>44617</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45510</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45112</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>44939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>46155</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>46155</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45848</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45538</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>45960</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45918</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>46178</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>46178</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>45887</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>46178</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>46178</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46178</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>46178</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>46178</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44939</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46178</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>46177</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>46178</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>46183</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>46183</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>46183</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>46183</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>46183</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44971</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>46183</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>46183</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46183</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45723</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>44587</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46188</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>44704</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44900</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44942</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45237</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45749</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>44895</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>46203</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>46203</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>46203</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46203</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>44951</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45090</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45548</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45349</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46259</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>46258</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>46199</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45009</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44855</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44820</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>46276</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45168</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45138</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>46266</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>45235</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>45235</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>46287</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44939</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45439</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>44915</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>46282</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>46287</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>46245</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>46245</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>46288</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>46245</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45078</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>46293</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>46290</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45308</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45446</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45091</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>46280</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45476</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>44740</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45090</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>44752</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45695</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>44752</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>46280</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44841</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45243</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45671</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45091</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45222</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45272</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45250</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45474</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45209</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45674</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45474</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45362</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>44897</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45216</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45133</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44939</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44895</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>44939</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45209</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45723</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45159</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44984</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45672</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45448</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45435</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45595</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45659</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45090</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>43957</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45496</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44536</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44959</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>44820</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45503</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>44627</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44757</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>44613</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>45484</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>44993</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45148</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46057</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>46093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>46097</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>46129</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>46134</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>46150</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45163</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45642</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45945</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46183</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>46076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45980</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45015</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45784</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45503</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45243</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>44704</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44477</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44752</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44841</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44599</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44552</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>44841</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45365</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45362</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45077</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45610</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45474</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45446</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44545</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>45037</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45715</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45833</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>44855</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45726</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45707</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45078</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>45953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>45958</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>45953</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>45034</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45235</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>45117</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>46031</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>45398</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>45903</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>45903</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>46037</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>46037</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>45908</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>45908</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45235</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>45792</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>45737</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>46043</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45915</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>46049</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>46049</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>45803</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>45918</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>45804</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>45918</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>45804</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>45090</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>45171</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>45124</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>45305</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>45305</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>45443</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>44897</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         <v>46058</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>45468</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>45278</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>46063</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>46069</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>44936</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>45936</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>46069</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>46069</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>46070</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44804</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>45695</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>45432</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45918</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>46077</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>46077</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>45077</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>46077</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45867</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45541</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44841</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45659</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>45813</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>45958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>44984</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>45035</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>46093</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45747</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>45167</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>45079</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44515</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>46101</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45975</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45084</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>44704</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46105</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46105</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>46105</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45980</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>45981</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>46111</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>46111</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>45985</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>45819</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45825</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>46121</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>45999</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>45178</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>45099</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>44994</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45077</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>45728</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44844</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>45855</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45756</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>45839</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>45736</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>45715</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>44935</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45918</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45915</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45762</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45072</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45679</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45012</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45279</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45646</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45090</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>44757</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45161</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>46141</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45852</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45077</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45140</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>44617</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45510</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45112</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>44939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>46155</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>46155</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45848</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45538</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>45960</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45918</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>46178</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>46178</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>45887</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>46178</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>46178</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46178</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>46178</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>46178</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44939</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46178</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>46177</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>46178</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>46183</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>46183</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>46183</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>46183</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>46183</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44971</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>46183</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>46183</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46183</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45723</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>44587</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46188</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>44704</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44900</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44942</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45237</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45749</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>44895</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>46203</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>46203</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>46203</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46203</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>44951</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45090</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45548</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45349</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46259</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>46258</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>46199</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45009</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44855</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44820</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>46276</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45168</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45138</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>46266</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>45235</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>45235</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>46287</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44939</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45439</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>44915</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>46282</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>46287</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>46245</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>46245</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>46288</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>46245</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45078</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>46293</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>46290</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45308</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45446</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45091</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>46280</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45476</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>44740</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45090</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>44752</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45695</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>44752</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>46280</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44841</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45243</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45671</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45091</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45222</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45272</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45250</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45474</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45209</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45674</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45474</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45362</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>44897</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45216</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45133</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44939</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44895</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>44939</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45209</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45723</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45159</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44984</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45672</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45448</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45435</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45595</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45659</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45090</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>43957</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45496</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44536</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44959</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>44820</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45503</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>44627</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44757</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>44613</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>45484</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>44993</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45148</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46057</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>46093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>46097</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>46129</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>46134</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>46150</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45163</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44963</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>45090</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>45853</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45510</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45642</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45945</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46183</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45015</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>45337</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45784</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45446</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45980</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>46076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>44704</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45503</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>45243</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44752</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>44537</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44543</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>44636</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>44799</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44526</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45077</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>45077</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45077</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>44841</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44897</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45091</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45091</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45079</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45439</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45078</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44939</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45362</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45090</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>45243</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45695</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>44971</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>44915</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45084</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44900</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45362</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45161</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45432</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>45446</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>45474</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44984</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>45090</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>45468</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44855</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>44841</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>45833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44939</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45279</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45222</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>44587</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45707</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45171</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45168</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>44984</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45133</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44939</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44939</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>45167</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45035</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45903</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>45903</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45908</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45908</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45398</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>44841</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45538</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>45308</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45138</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>45737</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44545</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>45659</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>45595</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>45009</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>45915</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>45446</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>45918</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>45159</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>44897</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>45474</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>45090</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45918</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45671</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44552</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44599</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>45117</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>45349</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45034</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45792</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>45235</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45726</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>45002</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>45037</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>45804</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>45803</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45804</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45435</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>45072</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>45674</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>45090</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44617</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45918</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45548</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>45813</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>45278</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45867</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45747</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>44704</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45819</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>45209</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>45610</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>45825</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45209</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45958</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>44740</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>45178</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>45112</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>45756</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>44752</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45728</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45839</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45474</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>45235</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>45099</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>45659</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>45443</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45762</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45646</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>44704</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>44844</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>45723</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44804</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45975</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45305</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45305</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45715</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>45695</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44820</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45237</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>44841</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45980</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>45365</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45235</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>44994</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>44936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>45981</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45541</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>45749</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45077</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45216</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>46101</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>45078</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45140</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>46105</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>46105</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>46105</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>45723</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>46111</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>46111</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>45235</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>46121</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44757</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>45999</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45124</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>44951</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>44935</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>45250</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>44939</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>44942</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44895</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45476</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45953</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>44855</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45958</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>45953</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45855</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45918</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45915</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45736</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45510</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45679</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45672</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>46031</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>44752</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45448</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45090</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>46037</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45048</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>46043</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44515</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45272</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>46049</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45012</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45852</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>46141</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>46063</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>46070</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>46069</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>46069</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>46069</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>46077</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>46077</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>46077</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>46155</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>46155</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45848</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>46093</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45960</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45918</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>46177</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>46178</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>46178</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>46178</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>46178</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>46178</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>46178</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>46178</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>46178</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>46183</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>46183</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>46183</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>46183</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>46183</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>46183</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>46183</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>46183</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>46188</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46203</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>46203</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>46203</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>46276</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>46282</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>46287</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>46245</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>46245</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>46287</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46266</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>46288</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>46290</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>46245</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>46280</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>46293</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>46280</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>46203</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>46199</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>46258</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>46178</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>46301</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>46301</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>46259</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>43957</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>44627</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44613</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45496</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44536</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>44959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44820</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>45503</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>44757</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45484</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>44993</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45148</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>46057</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>46093</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>46097</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>46129</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46134</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>46150</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45163</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44963</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>45090</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>45853</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45510</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45642</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45945</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46183</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45015</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>45337</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45784</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45446</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45980</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>46076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>44704</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45503</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>45243</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44752</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>44537</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44543</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>44636</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>44799</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44526</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45077</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>45077</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45077</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>44841</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44897</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45091</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45091</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45079</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45439</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45078</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44939</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45362</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45090</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>45243</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45695</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>44971</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>44915</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45084</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44900</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45362</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45161</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45432</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>45446</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>45474</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44984</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>45090</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>45468</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44855</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>44841</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>45833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44939</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45279</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45222</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>44587</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45707</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45171</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45168</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>44984</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45133</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44939</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44939</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>45167</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45035</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45903</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>45903</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45908</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45908</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45398</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>44841</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45538</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>45308</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45138</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>45737</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44545</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>45659</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>45595</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>45009</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>45915</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>45446</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>45918</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>45159</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>44897</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>45474</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>45090</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45918</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45671</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44552</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44599</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>45117</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>45349</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45034</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45792</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>45235</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45726</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>45002</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>45037</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>45804</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>45803</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45804</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45435</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>45072</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>45674</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>45090</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44617</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45918</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45548</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>45813</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>45278</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45867</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45747</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>44704</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45819</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>45209</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>45610</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>45825</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45209</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45958</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>44740</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>45178</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>45112</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>45756</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>44752</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45728</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45839</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45474</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>45235</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>45099</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>45659</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>45443</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45762</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45646</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>44704</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>44844</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>45723</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44804</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45975</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45305</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45305</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45715</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>45695</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44820</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45237</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>44841</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45980</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>45365</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45235</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>44994</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>44936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>45981</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45541</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>45749</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45077</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45216</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>46101</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>45078</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45140</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>46105</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>46105</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>46105</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>45723</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>46111</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>46111</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>45235</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>46121</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44757</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>45999</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45124</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>44951</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>44935</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>45250</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>44939</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>44942</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44895</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45476</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45953</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>44855</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45958</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>45953</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45855</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45918</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45915</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45736</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45510</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45679</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45672</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>46031</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>44752</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45448</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45090</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>46037</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45048</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>46043</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44515</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45272</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>46049</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45012</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45852</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>46141</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>46063</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>46070</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>46069</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>46069</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>46069</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>46077</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>46077</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>46077</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>46155</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>46155</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45848</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>46093</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45960</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45918</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>46177</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>46178</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>46178</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>46178</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>46178</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>46178</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>46178</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>46178</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>46178</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>46183</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>46183</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>46183</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>46183</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>46183</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>46183</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>46183</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>46183</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>46188</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46203</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>46203</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>46203</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>46276</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>46282</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>46287</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>46245</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>46245</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>46287</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46266</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>46288</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>46290</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>46245</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>46280</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>46293</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>46280</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>46203</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>46199</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>46258</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>46178</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>46301</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>46301</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>46259</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>43957</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>44627</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44613</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45496</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44536</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>44959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44820</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>45503</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>44757</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45484</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>44993</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45148</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>46057</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>46093</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>46097</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>46129</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46134</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>46150</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45163</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>45945</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45642</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>45015</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45980</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>46076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45784</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45503</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45243</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>44704</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44752</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>44537</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44799</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44526</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44813</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44543</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44636</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44841</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44599</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44552</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44841</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45362</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45365</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45077</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45037</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45715</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44545</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45078</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44855</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45117</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45398</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>45235</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45171</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45090</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45124</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>45305</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>45305</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>45468</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>45443</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44897</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44804</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45002</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44936</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>45432</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45695</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45077</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45278</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45541</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44841</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45659</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44984</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>45035</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45167</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>45079</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>44515</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>45084</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>44935</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>45918</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45915</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>45887</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>45833</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45707</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>45679</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45178</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45099</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>44994</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45077</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>46141</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45852</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>44844</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45903</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>45903</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>45908</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>45908</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>45737</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>45715</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>45915</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>45918</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>45072</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>45012</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45279</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>46155</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>45918</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>45090</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44757</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45161</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>45867</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>46155</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>45077</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>45958</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45848</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45140</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>44617</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45975</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45510</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>45980</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45112</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45981</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>44939</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>45999</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>45538</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>45960</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45918</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>44939</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>45953</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45958</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>45953</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>46031</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44971</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45723</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>44587</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>46178</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>46037</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>46178</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>46178</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>46178</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>46178</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>46178</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>46178</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>44704</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>46178</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>46177</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>44900</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>46043</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>46049</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>46183</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>46183</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>46183</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>46183</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>44942</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>46183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>46183</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>46183</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>46063</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>46183</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>46069</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>46069</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>46069</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>46070</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45237</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>46188</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45749</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>44895</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>46077</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>46077</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>46077</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>44951</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>45090</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45548</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45349</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>46093</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>46101</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>45009</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>46105</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>46105</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>46105</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>46111</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46111</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>46121</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44855</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44820</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46203</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>45855</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>46203</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>46203</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45736</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>45168</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45138</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45235</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>45235</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44939</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45439</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>44915</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45078</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>46276</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45308</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45446</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45091</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45476</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>44740</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45090</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>44752</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45695</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44752</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>44841</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45243</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45671</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>46287</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45091</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45222</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>46282</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45272</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45250</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>46287</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45474</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>46245</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>46245</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>46288</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45209</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45674</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>46245</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45474</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45362</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44897</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45216</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45133</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>46293</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>46290</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>44939</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44895</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>44939</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45209</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>45723</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>45159</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44984</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45672</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>46280</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45448</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>46280</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>45435</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>46199</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>46203</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>46178</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>46301</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>46258</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45595</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45659</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46301</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45090</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>46259</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45474</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45446</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45726</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45034</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45235</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45792</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45803</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45804</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45804</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>46266</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45813</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45747</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44704</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45819</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45825</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45728</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45756</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45839</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45762</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45646</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>43957</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45496</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44536</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44959</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44820</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45503</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44627</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44757</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>44613</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45484</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>44993</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45148</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>46057</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>46093</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>46097</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>46129</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46134</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>46150</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45163</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45510</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>45945</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45642</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>45015</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45980</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>46076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45784</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45503</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45243</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>44704</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44788</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44676</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44752</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>44537</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44799</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44526</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44813</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44543</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44636</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44841</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44599</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44552</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44841</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45362</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45365</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45077</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45037</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45715</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44545</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45078</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44855</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45117</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45398</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>45235</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45171</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45090</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45124</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>45305</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>45305</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>45468</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>45443</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44897</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44804</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45002</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44936</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>45432</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45695</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45077</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45278</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45541</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44841</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45659</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44984</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>45035</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45167</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>45079</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>44515</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>45084</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>44935</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>45918</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45915</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>45887</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>45833</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45707</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>45679</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45178</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45099</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>44994</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45077</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>46141</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45852</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>44844</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45903</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>45903</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>45908</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>45908</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>45737</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>45715</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>45915</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>45918</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>45072</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>45012</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45279</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>46155</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>45918</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>45090</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44757</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45161</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>45867</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>46155</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>45077</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>45958</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45848</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45140</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>44617</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45975</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45510</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>45980</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45112</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45981</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>44939</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>45999</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>45538</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>45960</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45918</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>44939</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>45953</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45958</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>45953</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>46031</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44971</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45723</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>44587</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>46178</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>46037</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>46178</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>46178</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>46178</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>46178</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>46178</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>46178</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>44704</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>46178</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>46177</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>44900</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>46043</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>46049</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>46183</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>46183</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>46183</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>46183</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>44942</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>46183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>46183</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>46183</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>46063</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>46183</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>46069</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>46069</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>46069</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>46070</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45237</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>46188</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45749</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>44895</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>46077</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>46077</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>46077</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>44951</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>45090</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45548</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45349</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>46093</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>46101</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>45009</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>46105</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>46105</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>46105</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>46111</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46111</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>46121</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44855</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44820</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46203</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>45855</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>46203</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>46203</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45736</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>45168</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45138</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45235</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>45235</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44939</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45439</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>44915</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45078</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>46276</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45308</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45446</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45091</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45476</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>44740</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45090</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>44752</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45695</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44752</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>44841</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45243</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45671</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>46287</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45091</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45222</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>46282</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45272</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45250</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>46287</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45474</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>46245</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>46245</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>46288</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45209</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45674</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>46245</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45474</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45362</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44897</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45216</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45133</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>46293</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>46290</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>44939</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44895</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>44939</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45209</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>45723</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>45159</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44984</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45672</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>46280</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45448</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>46280</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>45435</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>46199</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>46203</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>46178</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>46301</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>46258</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45595</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45659</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46301</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45090</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>46259</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45474</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45446</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45726</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45034</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45235</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45792</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45803</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45804</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45804</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>46266</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45813</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45747</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44704</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45819</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45825</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45728</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45756</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45839</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45762</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45646</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>43957</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45496</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44536</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44959</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44820</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45503</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44627</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44757</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>44613</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45484</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>44993</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45148</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>46057</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>46093</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>46097</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>46129</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46134</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>46150</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44963</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45163</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>45510</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>45853</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>45642</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45945</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45015</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>45980</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45784</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>46076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45337</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>46318</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45446</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44704</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45503</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45243</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>45582</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>46057</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44788</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44820</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44788</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44676</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44813</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44546</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44846</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>44752</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>44537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>44799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>44813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>44543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>45833</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>44841</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>45887</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45250</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>45091</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45091</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>44939</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>45707</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>45362</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>44942</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44915</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>45476</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45362</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>44855</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>45903</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45903</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45908</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>45908</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>45737</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>45510</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>45915</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>45918</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>45672</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>44752</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>45918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>45448</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>45090</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>45048</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>44515</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>45960</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>45272</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>45012</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>45918</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>45077</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>45077</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>45077</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>45079</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>45439</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>46177</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>45918</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>46178</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>46178</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>46178</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>45867</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>46178</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>46178</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>45078</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>46178</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>46178</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>46178</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>46183</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>46183</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>46183</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>46183</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>46183</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>46183</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>46183</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>46183</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>45958</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>45243</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45695</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>44900</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>46188</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>45161</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45474</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>44984</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>45090</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45975</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>45980</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>46203</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44939</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>46203</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45981</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>46203</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>45222</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>44587</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>45432</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45446</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>45035</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>45999</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>44841</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>45659</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45595</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>45446</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>45474</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>45090</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>45468</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>45953</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44855</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>45958</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44841</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>44895</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>45953</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>45034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>45792</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45235</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>46031</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>46282</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>45726</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>46037</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>46043</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>46287</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>46245</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>46245</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>46287</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>46288</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>46049</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>45804</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>45803</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>46290</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>45804</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>46245</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45279</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>46280</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>46063</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45813</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>46293</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>46070</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>46069</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>46069</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>45747</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>46069</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44704</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>45819</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>46077</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>46077</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>46077</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45825</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>46280</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>46203</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>45171</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45756</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45728</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45168</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45839</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>46199</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>46093</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>46258</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>46178</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>46101</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>46301</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>46105</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>46105</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>46105</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>46301</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45133</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45762</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45646</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>46259</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>46111</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>46111</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>44939</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>44939</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>46121</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45538</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>44935</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>45138</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>46266</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>44897</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45671</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45855</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>45918</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>44552</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>44599</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45915</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45736</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>45679</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45002</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>46276</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45037</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45852</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>46141</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45435</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45072</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45548</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>46155</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>46155</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45278</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45715</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45848</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45610</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45178</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45112</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>45099</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45659</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44844</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44804</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45695</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>44820</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44841</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>44936</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45077</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>45078</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45140</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45723</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45235</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>44897</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>44939</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45090</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>44971</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45084</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>44984</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45167</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45398</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45308</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44545</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45009</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>45159</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45117</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45349</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45674</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>45090</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>44617</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45209</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>45209</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>44740</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>44752</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45474</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45235</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45443</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>44704</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>45723</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>45305</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45305</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>45715</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>45237</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21992,7 +21992,7 @@
         <v>45365</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>45235</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44994</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>45541</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>45749</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>45216</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44757</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>45124</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44951</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>43957</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>44627</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>44613</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45496</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44536</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>44959</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>44820</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45503</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>44757</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45484</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44993</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45148</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>46057</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>46093</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>46097</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>46129</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>46134</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>46150</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44963</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45163</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>45510</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>45853</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>45090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>45642</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45945</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45015</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>45980</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45784</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>46076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45337</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>46318</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45446</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44704</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45503</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45243</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>45582</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>46057</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44788</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44820</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44788</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44676</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44813</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44546</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44846</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>44752</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>44537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>44799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>44813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>44543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>45833</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>44841</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>45887</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45250</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>45091</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45091</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>44939</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>45707</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>45362</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>44942</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44915</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>45476</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45362</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>44855</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>45903</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45903</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45908</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>45908</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>45737</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>45510</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>45915</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>45918</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>45672</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>44752</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>45918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>45448</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>45090</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>45048</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>44515</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>45960</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>45272</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>45012</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>45918</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>45077</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>45077</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>45077</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>45079</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>45439</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>46177</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>45918</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>46178</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>46178</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>46178</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>45867</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>46178</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>46178</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>45078</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>46178</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>46178</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>46178</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>46183</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>46183</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>46183</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>46183</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>46183</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>46183</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>46183</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>46183</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>45958</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>45243</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45695</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>44900</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>46188</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>45161</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45474</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>44984</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>45090</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45975</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>45980</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>46203</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44939</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>46203</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45981</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>46203</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>45222</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>44587</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>45432</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45446</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>45035</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>45999</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>44841</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>45659</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45595</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>45446</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>45474</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>45090</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>45468</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>45953</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44855</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>45958</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44841</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>44895</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>45953</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>45034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>45792</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45235</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>46031</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>46282</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>45726</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>46037</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>46043</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>46287</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>46245</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>46245</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>46287</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>46288</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>46049</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>45804</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>45803</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>46290</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>45804</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>46245</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45279</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>46280</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>46063</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45813</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>46293</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>46070</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>46069</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>46069</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>45747</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>46069</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44704</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>45819</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>46077</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>46077</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>46077</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45825</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>46280</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>46203</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>45171</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45756</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45728</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45168</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45839</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>46199</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>46093</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>46258</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>46178</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>46101</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>46301</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>46105</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>46105</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>46105</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>46301</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45133</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45762</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45646</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>46259</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>46111</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>46111</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>44939</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>44939</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>46121</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45538</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>44935</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>45138</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>46266</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>44897</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45671</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45855</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>45918</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>44552</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>44599</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45915</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45736</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>45679</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45002</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>46276</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45037</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45852</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>46141</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45435</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45072</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45548</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>46155</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>46155</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45278</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45715</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45848</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45610</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45178</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45112</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>45099</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45659</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44844</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44804</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45695</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>44820</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44841</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>44936</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45077</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>45078</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45140</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45723</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45235</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>44897</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>44939</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45090</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>44971</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45084</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>44984</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45167</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45398</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45308</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44545</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45009</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>45159</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45117</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45349</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45674</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>45090</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>44617</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45209</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>45209</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>44740</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>44752</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45474</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45235</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45443</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>44704</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>45723</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>45305</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45305</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>45715</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>45237</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21992,7 +21992,7 @@
         <v>45365</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>45235</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44994</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>45541</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>45749</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>45216</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44757</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>45124</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44951</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>43957</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>44627</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>44613</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45496</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44536</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>44959</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>44820</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45503</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>44757</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45484</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44993</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45148</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>46057</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>46093</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>46097</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>46129</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>46134</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>46150</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>

--- a/Översikt ÖRKELLJUNGA.xlsx
+++ b/Översikt ÖRKELLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45496</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44852</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>45916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44649</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 4112-2025</t>
+          <t>A 5927-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45684</v>
+        <v>44963</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1300,22 +1300,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>11.4</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1324,21 +1324,237 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Hussvala
+Ladusvala
+Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 5927-2023 artfynd.xlsx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 5927-2023 karta.png", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 5927-2023 georefererad karta.tif", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 5927-2023 FSC-klagomål.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 5927-2023 FSC-klagomål mail.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 5927-2023 tillsynsbegäran.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 5927-2023 tillsynsbegäran mail.docx", "A 5927-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 39622-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Dvärghäxört
+Skogsödla
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 39622-2023 artfynd.xlsx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 39622-2023 karta.png", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 39622-2023 georefererad karta.tif", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 39622-2023 FSC-klagomål.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 39622-2023 FSC-klagomål mail.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 39622-2023 tillsynsbegäran.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 39622-2023 tillsynsbegäran mail.docx", "A 39622-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 4112-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
         <v>6</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U10" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Gröngöling
@@ -1346,255 +1562,39 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 4112-2025 artfynd.xlsx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 4112-2025 karta.png", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 4112-2025 georefererad karta.tif", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 4112-2025 FSC-klagomål.docx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 4112-2025 FSC-klagomål mail.docx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 4112-2025 tillsynsbegäran.docx", "A 4112-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 4112-2025 tillsynsbegäran mail.docx", "A 4112-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 5927-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44963</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Hussvala
-Ladusvala
-Svart skogssnigel</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 5927-2023 artfynd.xlsx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 5927-2023 karta.png", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 5927-2023 georefererad karta.tif", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 5927-2023 FSC-klagomål.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 5927-2023 FSC-klagomål mail.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 5927-2023 tillsynsbegäran.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 5927-2023 tillsynsbegäran mail.docx", "A 5927-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 39622-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Dvärghäxört
-Skogsödla
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 39622-2023 artfynd.xlsx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 39622-2023 karta.png", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 39622-2023 georefererad karta.tif", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 39622-2023 FSC-klagomål.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 39622-2023 FSC-klagomål mail.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 39622-2023 tillsynsbegäran.docx", "A 39622-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 39622-2023 tillsynsbegäran mail.docx", "A 39622-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 31926-2024</t>
+          <t>A 35245-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45510</v>
+        <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1624,16 +1624,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1657,155 +1657,155 @@
         <v>3</v>
       </c>
       <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Talltita
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 35245-2025 artfynd.xlsx", "A 35245-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 35245-2025 karta.png", "A 35245-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 35245-2025 georefererad karta.tif", "A 35245-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 35245-2025 FSC-klagomål.docx", "A 35245-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 35245-2025 FSC-klagomål mail.docx", "A 35245-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 35245-2025 tillsynsbegäran.docx", "A 35245-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 35245-2025 tillsynsbegäran mail.docx", "A 35245-2025")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/A 35245-2025 prioriterade fågelarter.docx", "A 35245-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31926-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45510</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
         <v>9</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Havstulpanlav
 Klippfrullania
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 31926-2024 artfynd.xlsx", "A 31926-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 31926-2024 karta.png", "A 31926-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 31926-2024 georefererad karta.tif", "A 31926-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 31926-2024 FSC-klagomål.docx", "A 31926-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 31926-2024 FSC-klagomål mail.docx", "A 31926-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 31926-2024 tillsynsbegäran.docx", "A 31926-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 31926-2024 tillsynsbegäran mail.docx", "A 31926-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 35245-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45853</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Talltita
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 35245-2025 artfynd.xlsx", "A 35245-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 35245-2025 karta.png", "A 35245-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 35245-2025 georefererad karta.tif", "A 35245-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 35245-2025 FSC-klagomål.docx", "A 35245-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 35245-2025 FSC-klagomål mail.docx", "A 35245-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 35245-2025 tillsynsbegäran.docx", "A 35245-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 35245-2025 tillsynsbegäran mail.docx", "A 35245-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/A 35245-2025 prioriterade fågelarter.docx", "A 35245-2025")</f>
         <v/>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
         <v>45090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46150</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26585-2026</t>
+          <t>A 60271-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46183</v>
+        <v>45642</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>2</v>
@@ -2309,153 +2309,153 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
+          <t>Vanlig padda
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 60271-2024 artfynd.xlsx", "A 60271-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 60271-2024 karta.png", "A 60271-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 60271-2024 georefererad karta.tif", "A 60271-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 60271-2024 FSC-klagomål.docx", "A 60271-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 60271-2024 FSC-klagomål mail.docx", "A 60271-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 60271-2024 tillsynsbegäran.docx", "A 60271-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 60271-2024 tillsynsbegäran mail.docx", "A 60271-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 50629-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ÖRKELLJUNGA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>Spillkråka
 Röd glada</t>
         </is>
       </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 26585-2026 artfynd.xlsx", "A 26585-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 26585-2026 karta.png", "A 26585-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 26585-2026 georefererad karta.tif", "A 26585-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 26585-2026 FSC-klagomål.docx", "A 26585-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 26585-2026 FSC-klagomål mail.docx", "A 26585-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 26585-2026 tillsynsbegäran.docx", "A 26585-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 26585-2026 tillsynsbegäran mail.docx", "A 26585-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/A 26585-2026 prioriterade fågelarter.docx", "A 26585-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 60271-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ÖRKELLJUNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda
-Vanlig snok</t>
-        </is>
-      </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 60271-2024 artfynd.xlsx", "A 60271-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 50629-2025 artfynd.xlsx", "A 50629-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 60271-2024 karta.png", "A 60271-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 50629-2025 karta.png", "A 50629-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 60271-2024 georefererad karta.tif", "A 60271-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 50629-2025 georefererad karta.tif", "A 50629-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 60271-2024 FSC-klagomål.docx", "A 60271-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 50629-2025 FSC-klagomål.docx", "A 50629-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 60271-2024 FSC-klagomål mail.docx", "A 60271-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 50629-2025 FSC-klagomål mail.docx", "A 50629-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 60271-2024 tillsynsbegäran.docx", "A 60271-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 50629-2025 tillsynsbegäran.docx", "A 50629-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 60271-2024 tillsynsbegäran mail.docx", "A 60271-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 50629-2025 tillsynsbegäran mail.docx", "A 50629-2025")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/A 50629-2025 prioriterade fågelarter.docx", "A 50629-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50629-2025</t>
+          <t>A 26585-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45945</v>
+        <v>46183</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>2</v>
@@ -2521,7 +2521,7 @@
         <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
@@ -2530,35 +2530,35 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 50629-2025 artfynd.xlsx", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 26585-2026 artfynd.xlsx", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 50629-2025 karta.png", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 26585-2026 karta.png", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 50629-2025 georefererad karta.tif", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 26585-2026 georefererad karta.tif", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 50629-2025 FSC-klagomål.docx", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 26585-2026 FSC-klagomål.docx", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 50629-2025 FSC-klagomål mail.docx", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 26585-2026 FSC-klagomål mail.docx", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 50629-2025 tillsynsbegäran.docx", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsyn/A 26585-2026 tillsynsbegäran.docx", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 50629-2025 tillsynsbegäran mail.docx", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/tillsynsmail/A 26585-2026 tillsynsbegäran mail.docx", "A 26585-2026")</f>
         <v/>
       </c>
       <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/A 50629-2025 prioriterade fågelarter.docx", "A 50629-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/fåglar/A 26585-2026 prioriterade fågelarter.docx", "A 26585-2026")</f>
         <v/>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
         <v>45139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44516</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15068-2023</t>
+          <t>A 21867-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45015</v>
+        <v>45784</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3030,17 +3030,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>9.9</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3066,39 +3066,39 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Källkvicklöpare</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 15068-2023 artfynd.xlsx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/artfynd/A 21867-2025 artfynd.xlsx", "A 21867-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 15068-2023 karta.png", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor/A 21867-2025 karta.png", "A 21867-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 15068-2023 georefererad karta.tif", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/kartor_geotiff/A 21867-2025 georefererad karta.tif", "A 21867-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 15068-2023 FSC-klagomål.docx", "A 15068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomål/A 21867-2025 FSC-klagomål.docx", "A 21867-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1257/klagomålsmail/A 15068-2023 FSC-klagomål mail.docx", "A 15068-2023")</f>
+        <f>HYP